--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -2134,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755786</v>
+        <v>125737958</v>
       </c>
       <c r="B17" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523474</v>
+        <v>523967</v>
       </c>
       <c r="R17" t="n">
-        <v>6845244</v>
+        <v>6845175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755785</v>
+        <v>125733598</v>
       </c>
       <c r="B18" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,37 +2242,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523467</v>
+        <v>523483</v>
       </c>
       <c r="R18" t="n">
-        <v>6845333</v>
+        <v>6845118</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2316,22 +2316,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125737958</v>
+        <v>125755786</v>
       </c>
       <c r="B19" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523967</v>
+        <v>523474</v>
       </c>
       <c r="R19" t="n">
-        <v>6845175</v>
+        <v>6845244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2413,22 +2413,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125733598</v>
+        <v>125755785</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523483</v>
+        <v>523467</v>
       </c>
       <c r="R20" t="n">
-        <v>6845118</v>
+        <v>6845333</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2510,12 +2510,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755565</v>
+        <v>125755695</v>
       </c>
       <c r="B36" t="n">
-        <v>91240</v>
+        <v>78967</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523551</v>
+        <v>523990</v>
       </c>
       <c r="R36" t="n">
-        <v>6845103</v>
+        <v>6845162</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755695</v>
+        <v>125755565</v>
       </c>
       <c r="B37" t="n">
-        <v>78967</v>
+        <v>91240</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523990</v>
+        <v>523551</v>
       </c>
       <c r="R37" t="n">
-        <v>6845162</v>
+        <v>6845103</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125734860</v>
+        <v>125755787</v>
       </c>
       <c r="B39" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,37 +4289,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523673</v>
+        <v>523457</v>
       </c>
       <c r="R39" t="n">
-        <v>6845294</v>
+        <v>6845237</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125734662</v>
+        <v>125734860</v>
       </c>
       <c r="B40" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523492</v>
+        <v>523673</v>
       </c>
       <c r="R40" t="n">
-        <v>6845165</v>
+        <v>6845294</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125735540</v>
+        <v>125734662</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78725</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523479</v>
+        <v>523492</v>
       </c>
       <c r="R41" t="n">
-        <v>6845406</v>
+        <v>6845165</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4557,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755787</v>
+        <v>125735540</v>
       </c>
       <c r="B42" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523457</v>
+        <v>523479</v>
       </c>
       <c r="R42" t="n">
-        <v>6845237</v>
+        <v>6845406</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,12 +4654,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5738,58 +5738,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125736061</v>
+        <v>125755636</v>
       </c>
       <c r="B54" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523643</v>
+        <v>523511</v>
       </c>
       <c r="R54" t="n">
-        <v>6845391</v>
+        <v>6845102</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5833,19 +5823,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125732709</v>
+        <v>125755627</v>
       </c>
       <c r="B55" t="n">
         <v>78726</v>
@@ -5876,17 +5866,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523548</v>
+        <v>523755</v>
       </c>
       <c r="R55" t="n">
-        <v>6845076</v>
+        <v>6845251</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5930,22 +5920,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755542</v>
+        <v>125755628</v>
       </c>
       <c r="B56" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5953,21 +5943,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5977,10 +5967,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523670</v>
+        <v>523728</v>
       </c>
       <c r="R56" t="n">
-        <v>6845353</v>
+        <v>6845279</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6039,10 +6029,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755543</v>
+        <v>125732709</v>
       </c>
       <c r="B57" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6050,37 +6040,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523460</v>
+        <v>523548</v>
       </c>
       <c r="R57" t="n">
-        <v>6845221</v>
+        <v>6845076</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6124,60 +6114,70 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755636</v>
+        <v>125736061</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523511</v>
+        <v>523643</v>
       </c>
       <c r="R58" t="n">
-        <v>6845102</v>
+        <v>6845391</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6221,22 +6221,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755627</v>
+        <v>125755542</v>
       </c>
       <c r="B59" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523755</v>
+        <v>523670</v>
       </c>
       <c r="R59" t="n">
-        <v>6845251</v>
+        <v>6845353</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755628</v>
+        <v>125755543</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523728</v>
+        <v>523460</v>
       </c>
       <c r="R60" t="n">
-        <v>6845279</v>
+        <v>6845221</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7998,49 +7998,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125735686</v>
+        <v>125755701</v>
       </c>
       <c r="B77" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523418</v>
+        <v>523839</v>
       </c>
       <c r="R77" t="n">
-        <v>6845349</v>
+        <v>6845286</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8087,19 +8083,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B78" t="n">
         <v>78967</v>
@@ -8134,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R78" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,10 +8192,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755707</v>
+        <v>125755541</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8207,21 +8203,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8231,10 +8227,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523644</v>
+        <v>523757</v>
       </c>
       <c r="R79" t="n">
-        <v>6845389</v>
+        <v>6845248</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8293,32 +8289,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755541</v>
+        <v>125755794</v>
       </c>
       <c r="B80" t="n">
-        <v>79585</v>
+        <v>91627</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8324,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523757</v>
+        <v>523385</v>
       </c>
       <c r="R80" t="n">
-        <v>6845248</v>
+        <v>6845416</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8364,6 +8360,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8390,32 +8391,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755794</v>
+        <v>125755714</v>
       </c>
       <c r="B81" t="n">
-        <v>91627</v>
+        <v>78967</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8425,10 +8426,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523385</v>
+        <v>523383</v>
       </c>
       <c r="R81" t="n">
-        <v>6845416</v>
+        <v>6845391</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8461,11 +8462,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8492,45 +8488,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755714</v>
+        <v>125735686</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>98324</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523383</v>
+        <v>523418</v>
       </c>
       <c r="R82" t="n">
-        <v>6845391</v>
+        <v>6845349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,22 +8577,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755789</v>
+        <v>125732736</v>
       </c>
       <c r="B83" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,37 +8600,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523480</v>
+        <v>523551</v>
       </c>
       <c r="R83" t="n">
-        <v>6845112</v>
+        <v>6845080</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,22 +8674,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125737510</v>
+        <v>125755702</v>
       </c>
       <c r="B84" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8697,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523957</v>
+        <v>523829</v>
       </c>
       <c r="R84" t="n">
-        <v>6845190</v>
+        <v>6845308</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8771,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125732736</v>
+        <v>125755789</v>
       </c>
       <c r="B85" t="n">
-        <v>78725</v>
+        <v>78634</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,37 +8794,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523551</v>
+        <v>523480</v>
       </c>
       <c r="R85" t="n">
-        <v>6845080</v>
+        <v>6845112</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8868,22 +8868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755702</v>
+        <v>125755621</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523829</v>
+        <v>523920</v>
       </c>
       <c r="R86" t="n">
-        <v>6845308</v>
+        <v>6845217</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755621</v>
+        <v>125737510</v>
       </c>
       <c r="B87" t="n">
         <v>78726</v>
@@ -9008,17 +9008,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523920</v>
+        <v>523957</v>
       </c>
       <c r="R87" t="n">
-        <v>6845217</v>
+        <v>6845190</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125736529</v>
+        <v>125734476</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523524</v>
+        <v>523492</v>
       </c>
       <c r="R2" t="n">
-        <v>6845323</v>
+        <v>6845165</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125737411</v>
+        <v>125755703</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523825</v>
+        <v>523783</v>
       </c>
       <c r="R3" t="n">
-        <v>6845311</v>
+        <v>6845289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125734228</v>
+        <v>125755705</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523467</v>
+        <v>523728</v>
       </c>
       <c r="R4" t="n">
-        <v>6845121</v>
+        <v>6845268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125734476</v>
+        <v>125755643</v>
       </c>
       <c r="B5" t="n">
-        <v>79585</v>
+        <v>80070</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523492</v>
+        <v>523816</v>
       </c>
       <c r="R5" t="n">
-        <v>6845165</v>
+        <v>6845298</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755703</v>
+        <v>125737411</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523783</v>
+        <v>523825</v>
       </c>
       <c r="R6" t="n">
-        <v>6845289</v>
+        <v>6845311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755705</v>
+        <v>125734228</v>
       </c>
       <c r="B7" t="n">
         <v>78967</v>
@@ -1191,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523728</v>
+        <v>523467</v>
       </c>
       <c r="R7" t="n">
-        <v>6845268</v>
+        <v>6845121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755643</v>
+        <v>125736529</v>
       </c>
       <c r="B8" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523816</v>
+        <v>523524</v>
       </c>
       <c r="R8" t="n">
-        <v>6845298</v>
+        <v>6845323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,60 +1342,64 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125734647</v>
+        <v>125735595</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523611</v>
+        <v>523492</v>
       </c>
       <c r="R9" t="n">
-        <v>6845275</v>
+        <v>6845165</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,19 +1443,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125736051</v>
+        <v>125755708</v>
       </c>
       <c r="B10" t="n">
         <v>78967</v>
@@ -1482,14 +1486,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523418</v>
+        <v>523626</v>
       </c>
       <c r="R10" t="n">
-        <v>6845349</v>
+        <v>6845380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1540,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755632</v>
+        <v>125755716</v>
       </c>
       <c r="B11" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523621</v>
+        <v>523477</v>
       </c>
       <c r="R11" t="n">
-        <v>6845375</v>
+        <v>6845219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1649,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755708</v>
+        <v>125736051</v>
       </c>
       <c r="B12" t="n">
         <v>78967</v>
@@ -1676,14 +1680,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523626</v>
+        <v>523418</v>
       </c>
       <c r="R12" t="n">
-        <v>6845380</v>
+        <v>6845349</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,19 +1734,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755716</v>
+        <v>125734647</v>
       </c>
       <c r="B13" t="n">
         <v>78967</v>
@@ -1773,17 +1777,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523477</v>
+        <v>523611</v>
       </c>
       <c r="R13" t="n">
-        <v>6845219</v>
+        <v>6845275</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,12 +1831,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2033,49 +2037,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125735595</v>
+        <v>125755632</v>
       </c>
       <c r="B16" t="n">
-        <v>98324</v>
+        <v>78726</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523492</v>
+        <v>523621</v>
       </c>
       <c r="R16" t="n">
-        <v>6845165</v>
+        <v>6845375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,12 +2122,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755786</v>
+        <v>125755693</v>
       </c>
       <c r="B19" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523474</v>
+        <v>523993</v>
       </c>
       <c r="R19" t="n">
-        <v>6845244</v>
+        <v>6845158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755785</v>
+        <v>125755786</v>
       </c>
       <c r="B20" t="n">
         <v>78634</v>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523467</v>
+        <v>523474</v>
       </c>
       <c r="R20" t="n">
-        <v>6845333</v>
+        <v>6845244</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755693</v>
+        <v>125755785</v>
       </c>
       <c r="B21" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523993</v>
+        <v>523467</v>
       </c>
       <c r="R21" t="n">
-        <v>6845158</v>
+        <v>6845333</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755790</v>
+        <v>125755719</v>
       </c>
       <c r="B23" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523486</v>
+        <v>523554</v>
       </c>
       <c r="R23" t="n">
-        <v>6845100</v>
+        <v>6845068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755719</v>
+        <v>125755790</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,21 +2824,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2848,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523554</v>
+        <v>523486</v>
       </c>
       <c r="R24" t="n">
-        <v>6845068</v>
+        <v>6845100</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3117,7 +3117,7 @@
         <v>125733851</v>
       </c>
       <c r="B27" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3502,48 +3502,48 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755657</v>
+        <v>125735113</v>
       </c>
       <c r="B31" t="n">
-        <v>91380</v>
+        <v>78726</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523463</v>
+        <v>523630</v>
       </c>
       <c r="R31" t="n">
-        <v>6845211</v>
+        <v>6845423</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,19 +3587,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755545</v>
+        <v>125755549</v>
       </c>
       <c r="B32" t="n">
         <v>79585</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523465</v>
+        <v>523541</v>
       </c>
       <c r="R32" t="n">
-        <v>6845109</v>
+        <v>6845054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755549</v>
+        <v>125755545</v>
       </c>
       <c r="B33" t="n">
         <v>79585</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523541</v>
+        <v>523465</v>
       </c>
       <c r="R33" t="n">
-        <v>6845054</v>
+        <v>6845109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755634</v>
+        <v>125755657</v>
       </c>
       <c r="B34" t="n">
-        <v>78726</v>
+        <v>91387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523498</v>
+        <v>523463</v>
       </c>
       <c r="R34" t="n">
-        <v>6845404</v>
+        <v>6845211</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735113</v>
+        <v>125755634</v>
       </c>
       <c r="B35" t="n">
         <v>78726</v>
@@ -3921,17 +3921,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523630</v>
+        <v>523498</v>
       </c>
       <c r="R35" t="n">
-        <v>6845423</v>
+        <v>6845404</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,12 +3975,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4087,7 +4087,7 @@
         <v>125755565</v>
       </c>
       <c r="B37" t="n">
-        <v>91240</v>
+        <v>91247</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755787</v>
+        <v>125755544</v>
       </c>
       <c r="B39" t="n">
-        <v>78634</v>
+        <v>79585</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,21 +4289,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4313,10 +4313,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523457</v>
+        <v>523483</v>
       </c>
       <c r="R39" t="n">
-        <v>6845237</v>
+        <v>6845181</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4375,10 +4375,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125734860</v>
+        <v>125755539</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523673</v>
+        <v>523924</v>
       </c>
       <c r="R40" t="n">
-        <v>6845294</v>
+        <v>6845215</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,12 +4460,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4569,7 +4569,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125735540</v>
+        <v>125734860</v>
       </c>
       <c r="B42" t="n">
         <v>78967</v>
@@ -4604,10 +4604,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523479</v>
+        <v>523673</v>
       </c>
       <c r="R42" t="n">
-        <v>6845406</v>
+        <v>6845294</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755539</v>
+        <v>125735540</v>
       </c>
       <c r="B43" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523924</v>
+        <v>523479</v>
       </c>
       <c r="R43" t="n">
-        <v>6845215</v>
+        <v>6845406</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755544</v>
+        <v>125755787</v>
       </c>
       <c r="B44" t="n">
-        <v>79585</v>
+        <v>78634</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523483</v>
+        <v>523457</v>
       </c>
       <c r="R44" t="n">
-        <v>6845181</v>
+        <v>6845237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4860,48 +4860,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125735128</v>
+        <v>125755658</v>
       </c>
       <c r="B45" t="n">
-        <v>79585</v>
+        <v>91387</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523627</v>
+        <v>523487</v>
       </c>
       <c r="R45" t="n">
-        <v>6845420</v>
+        <v>6845098</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125736099</v>
+        <v>125755792</v>
       </c>
       <c r="B46" t="n">
-        <v>78967</v>
+        <v>92503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,34 +4968,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523514</v>
+        <v>523992</v>
       </c>
       <c r="R46" t="n">
-        <v>6845340</v>
+        <v>6845170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5030,6 +5030,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5042,19 +5047,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125734241</v>
+        <v>125755717</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5085,14 +5090,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523492</v>
+        <v>523466</v>
       </c>
       <c r="R47" t="n">
-        <v>6845165</v>
+        <v>6845180</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5139,44 +5144,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755658</v>
+        <v>125755552</v>
       </c>
       <c r="B48" t="n">
-        <v>91380</v>
+        <v>91192</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5186,10 +5191,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523487</v>
+        <v>523424</v>
       </c>
       <c r="R48" t="n">
-        <v>6845098</v>
+        <v>6845383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755792</v>
+        <v>125735128</v>
       </c>
       <c r="B49" t="n">
-        <v>92496</v>
+        <v>79585</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5259,37 +5264,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523992</v>
+        <v>523627</v>
       </c>
       <c r="R49" t="n">
-        <v>6845170</v>
+        <v>6845420</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5319,11 +5324,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5338,19 +5338,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755717</v>
+        <v>125734241</v>
       </c>
       <c r="B50" t="n">
         <v>78967</v>
@@ -5381,14 +5381,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523466</v>
+        <v>523492</v>
       </c>
       <c r="R50" t="n">
-        <v>6845180</v>
+        <v>6845165</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5435,57 +5435,57 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755552</v>
+        <v>125736099</v>
       </c>
       <c r="B51" t="n">
-        <v>91185</v>
+        <v>78967</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523424</v>
+        <v>523514</v>
       </c>
       <c r="R51" t="n">
-        <v>6845383</v>
+        <v>6845340</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5532,12 +5532,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5738,48 +5738,58 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755636</v>
+        <v>125736061</v>
       </c>
       <c r="B54" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523511</v>
+        <v>523643</v>
       </c>
       <c r="R54" t="n">
-        <v>6845102</v>
+        <v>6845391</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5823,22 +5833,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755627</v>
+        <v>125755542</v>
       </c>
       <c r="B55" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5846,21 +5856,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5870,10 +5880,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523755</v>
+        <v>523670</v>
       </c>
       <c r="R55" t="n">
-        <v>6845251</v>
+        <v>6845353</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5932,10 +5942,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755628</v>
+        <v>125755543</v>
       </c>
       <c r="B56" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5943,21 +5953,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5967,10 +5977,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523728</v>
+        <v>523460</v>
       </c>
       <c r="R56" t="n">
-        <v>6845279</v>
+        <v>6845221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6126,58 +6136,48 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125736061</v>
+        <v>125755636</v>
       </c>
       <c r="B58" t="n">
-        <v>56843</v>
+        <v>78726</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523643</v>
+        <v>523511</v>
       </c>
       <c r="R58" t="n">
-        <v>6845391</v>
+        <v>6845102</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6221,22 +6221,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755542</v>
+        <v>125755627</v>
       </c>
       <c r="B59" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523670</v>
+        <v>523755</v>
       </c>
       <c r="R59" t="n">
-        <v>6845353</v>
+        <v>6845251</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755543</v>
+        <v>125755628</v>
       </c>
       <c r="B60" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6341,21 +6341,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523460</v>
+        <v>523728</v>
       </c>
       <c r="R60" t="n">
-        <v>6845221</v>
+        <v>6845279</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6430,7 +6430,7 @@
         <v>125735892</v>
       </c>
       <c r="B61" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6621,57 +6621,48 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755647</v>
+        <v>125735337</v>
       </c>
       <c r="B63" t="n">
-        <v>98324</v>
+        <v>78726</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523408</v>
+        <v>523593</v>
       </c>
       <c r="R63" t="n">
-        <v>6845401</v>
+        <v>6845417</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6715,19 +6706,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125735337</v>
+        <v>125734655</v>
       </c>
       <c r="B64" t="n">
         <v>78726</v>
@@ -6758,17 +6749,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523593</v>
+        <v>523492</v>
       </c>
       <c r="R64" t="n">
-        <v>6845417</v>
+        <v>6845165</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6812,19 +6803,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734655</v>
+        <v>125734972</v>
       </c>
       <c r="B65" t="n">
         <v>78726</v>
@@ -6855,17 +6846,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523492</v>
+        <v>523675</v>
       </c>
       <c r="R65" t="n">
-        <v>6845165</v>
+        <v>6845339</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6909,60 +6900,69 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125734972</v>
+        <v>125755647</v>
       </c>
       <c r="B66" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523675</v>
+        <v>523408</v>
       </c>
       <c r="R66" t="n">
-        <v>6845339</v>
+        <v>6845401</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,12 +7006,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
         <v>125755598</v>
       </c>
       <c r="B67" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125734739</v>
+        <v>125733520</v>
       </c>
       <c r="B70" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7320,37 +7320,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523608</v>
+        <v>523552</v>
       </c>
       <c r="R70" t="n">
-        <v>6845309</v>
+        <v>6845072</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7394,12 +7394,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7503,10 +7503,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125733520</v>
+        <v>125755761</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7514,34 +7514,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523552</v>
+        <v>523387</v>
       </c>
       <c r="R72" t="n">
-        <v>6845072</v>
+        <v>6845410</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7588,19 +7593,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755761</v>
+        <v>125738012</v>
       </c>
       <c r="B73" t="n">
         <v>57651</v>
@@ -7640,10 +7645,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523387</v>
+        <v>523967</v>
       </c>
       <c r="R73" t="n">
-        <v>6845410</v>
+        <v>6845175</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,22 +7695,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755788</v>
+        <v>125734739</v>
       </c>
       <c r="B74" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,37 +7718,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523460</v>
+        <v>523608</v>
       </c>
       <c r="R74" t="n">
-        <v>6845221</v>
+        <v>6845309</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7787,12 +7792,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7896,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125738012</v>
+        <v>125755788</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>78634</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7907,39 +7912,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523967</v>
+        <v>523460</v>
       </c>
       <c r="R76" t="n">
-        <v>6845175</v>
+        <v>6845221</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7986,19 +7986,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B77" t="n">
         <v>78967</v>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R77" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8095,32 +8095,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755707</v>
+        <v>125755794</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>91634</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523644</v>
+        <v>523385</v>
       </c>
       <c r="R78" t="n">
-        <v>6845389</v>
+        <v>6845416</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8166,6 +8166,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8192,45 +8197,49 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755541</v>
+        <v>125735686</v>
       </c>
       <c r="B79" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523757</v>
+        <v>523418</v>
       </c>
       <c r="R79" t="n">
-        <v>6845248</v>
+        <v>6845349</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8277,44 +8286,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755794</v>
+        <v>125755541</v>
       </c>
       <c r="B80" t="n">
-        <v>91627</v>
+        <v>79585</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>6453</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8324,10 +8333,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523385</v>
+        <v>523757</v>
       </c>
       <c r="R80" t="n">
-        <v>6845416</v>
+        <v>6845248</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8360,11 +8369,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8391,7 +8395,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755714</v>
+        <v>125755701</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8426,10 +8430,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523383</v>
+        <v>523839</v>
       </c>
       <c r="R81" t="n">
-        <v>6845391</v>
+        <v>6845286</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8488,49 +8492,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125735686</v>
+        <v>125755714</v>
       </c>
       <c r="B82" t="n">
-        <v>98324</v>
+        <v>78967</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523418</v>
+        <v>523383</v>
       </c>
       <c r="R82" t="n">
-        <v>6845349</v>
+        <v>6845391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,12 +8577,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755702</v>
+        <v>125755789</v>
       </c>
       <c r="B84" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523829</v>
+        <v>523480</v>
       </c>
       <c r="R84" t="n">
-        <v>6845308</v>
+        <v>6845112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755789</v>
+        <v>125755621</v>
       </c>
       <c r="B85" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523480</v>
+        <v>523920</v>
       </c>
       <c r="R85" t="n">
-        <v>6845112</v>
+        <v>6845217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755621</v>
+        <v>125737510</v>
       </c>
       <c r="B86" t="n">
         <v>78726</v>
@@ -8911,17 +8911,17 @@
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523920</v>
+        <v>523957</v>
       </c>
       <c r="R86" t="n">
-        <v>6845217</v>
+        <v>6845190</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125737510</v>
+        <v>125755702</v>
       </c>
       <c r="B87" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8988,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523957</v>
+        <v>523829</v>
       </c>
       <c r="R87" t="n">
-        <v>6845190</v>
+        <v>6845308</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,22 +9062,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755783</v>
+        <v>125755700</v>
       </c>
       <c r="B88" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9085,21 +9085,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523644</v>
+        <v>523859</v>
       </c>
       <c r="R88" t="n">
-        <v>6845379</v>
+        <v>6845221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,54 +9171,45 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755654</v>
+        <v>125755783</v>
       </c>
       <c r="B89" t="n">
-        <v>98324</v>
+        <v>78634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523428</v>
+        <v>523644</v>
       </c>
       <c r="R89" t="n">
-        <v>6845361</v>
+        <v>6845379</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9277,10 +9268,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755553</v>
+        <v>125755697</v>
       </c>
       <c r="B90" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9288,21 +9279,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9312,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523626</v>
+        <v>523948</v>
       </c>
       <c r="R90" t="n">
-        <v>6845383</v>
+        <v>6845177</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9374,10 +9365,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125732728</v>
+        <v>125755775</v>
       </c>
       <c r="B91" t="n">
-        <v>92502</v>
+        <v>92509</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9402,21 +9393,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523590</v>
+        <v>523541</v>
       </c>
       <c r="R91" t="n">
-        <v>6845030</v>
+        <v>6845044</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9463,22 +9450,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755700</v>
+        <v>125755553</v>
       </c>
       <c r="B92" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9486,21 +9473,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9510,10 +9497,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523859</v>
+        <v>523626</v>
       </c>
       <c r="R92" t="n">
-        <v>6845221</v>
+        <v>6845383</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9572,45 +9559,49 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755697</v>
+        <v>125732728</v>
       </c>
       <c r="B93" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523948</v>
+        <v>523590</v>
       </c>
       <c r="R93" t="n">
-        <v>6845177</v>
+        <v>6845030</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9657,57 +9648,66 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755775</v>
+        <v>125755654</v>
       </c>
       <c r="B94" t="n">
-        <v>92502</v>
+        <v>98331</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523541</v>
+        <v>523428</v>
       </c>
       <c r="R94" t="n">
-        <v>6845044</v>
+        <v>6845361</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,50 +9766,45 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755610</v>
+        <v>125737769</v>
       </c>
       <c r="B95" t="n">
-        <v>8447</v>
+        <v>79585</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523527</v>
+        <v>523967</v>
       </c>
       <c r="R95" t="n">
-        <v>6845375</v>
+        <v>6845175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,22 +9851,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755624</v>
+        <v>125755694</v>
       </c>
       <c r="B96" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9879,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9903,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523853</v>
+        <v>523979</v>
       </c>
       <c r="R96" t="n">
-        <v>6845279</v>
+        <v>6845154</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9965,45 +9960,50 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125737769</v>
+        <v>125755610</v>
       </c>
       <c r="B97" t="n">
-        <v>79585</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523967</v>
+        <v>523527</v>
       </c>
       <c r="R97" t="n">
-        <v>6845175</v>
+        <v>6845375</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,44 +10050,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755774</v>
+        <v>125755624</v>
       </c>
       <c r="B98" t="n">
-        <v>92502</v>
+        <v>78726</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10097,10 +10097,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523526</v>
+        <v>523853</v>
       </c>
       <c r="R98" t="n">
-        <v>6845095</v>
+        <v>6845279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10159,32 +10159,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755694</v>
+        <v>125755774</v>
       </c>
       <c r="B99" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523979</v>
+        <v>523526</v>
       </c>
       <c r="R99" t="n">
-        <v>6845154</v>
+        <v>6845095</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125736651</v>
+        <v>125737335</v>
       </c>
       <c r="B101" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10364,37 +10364,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523722</v>
+        <v>523835</v>
       </c>
       <c r="R101" t="n">
-        <v>6845318</v>
+        <v>6845199</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,22 +10438,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125737335</v>
+        <v>125736651</v>
       </c>
       <c r="B102" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,37 +10461,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523835</v>
+        <v>523722</v>
       </c>
       <c r="R102" t="n">
-        <v>6845199</v>
+        <v>6845318</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10535,12 +10535,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755550</v>
+        <v>125755712</v>
       </c>
       <c r="B104" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523604</v>
+        <v>523428</v>
       </c>
       <c r="R104" t="n">
-        <v>6845013</v>
+        <v>6845361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755712</v>
+        <v>125755550</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523428</v>
+        <v>523604</v>
       </c>
       <c r="R105" t="n">
-        <v>6845361</v>
+        <v>6845013</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11032,7 +11032,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755713</v>
+        <v>125736699</v>
       </c>
       <c r="B108" t="n">
         <v>78967</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523332</v>
+        <v>523766</v>
       </c>
       <c r="R108" t="n">
-        <v>6845377</v>
+        <v>6845303</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,22 +11117,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755706</v>
+        <v>125737839</v>
       </c>
       <c r="B109" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523655</v>
+        <v>523967</v>
       </c>
       <c r="R109" t="n">
-        <v>6845374</v>
+        <v>6845175</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11214,22 +11214,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755617</v>
+        <v>125755713</v>
       </c>
       <c r="B110" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523972</v>
+        <v>523332</v>
       </c>
       <c r="R110" t="n">
-        <v>6845173</v>
+        <v>6845377</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11323,10 +11323,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125737839</v>
+        <v>125755706</v>
       </c>
       <c r="B111" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11334,21 +11334,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523967</v>
+        <v>523655</v>
       </c>
       <c r="R111" t="n">
-        <v>6845175</v>
+        <v>6845374</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,22 +11408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125736699</v>
+        <v>125755617</v>
       </c>
       <c r="B112" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523766</v>
+        <v>523972</v>
       </c>
       <c r="R112" t="n">
-        <v>6845303</v>
+        <v>6845173</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11505,57 +11505,66 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B113" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R113" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11614,54 +11623,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B114" t="n">
-        <v>98324</v>
+        <v>78726</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R114" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125736623</v>
+        <v>125755555</v>
       </c>
       <c r="B115" t="n">
-        <v>78967</v>
+        <v>90265</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,34 +11731,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523689</v>
+        <v>523480</v>
       </c>
       <c r="R115" t="n">
-        <v>6845339</v>
+        <v>6845111</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11805,62 +11805,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755608</v>
+        <v>125755601</v>
       </c>
       <c r="B116" t="n">
-        <v>8447</v>
+        <v>92707</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523745</v>
+        <v>523463</v>
       </c>
       <c r="R116" t="n">
-        <v>6845284</v>
+        <v>6845230</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11919,10 +11914,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125732643</v>
+        <v>125755784</v>
       </c>
       <c r="B117" t="n">
-        <v>79556</v>
+        <v>78634</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11930,34 +11925,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523617</v>
+        <v>523606</v>
       </c>
       <c r="R117" t="n">
-        <v>6845031</v>
+        <v>6845378</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12004,57 +11999,66 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755784</v>
+        <v>125755563</v>
       </c>
       <c r="B118" t="n">
-        <v>78634</v>
+        <v>56843</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523606</v>
+        <v>523483</v>
       </c>
       <c r="R118" t="n">
-        <v>6845378</v>
+        <v>6845365</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12113,45 +12117,50 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755555</v>
+        <v>125755608</v>
       </c>
       <c r="B119" t="n">
-        <v>90258</v>
+        <v>8447</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>106545</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523480</v>
+        <v>523745</v>
       </c>
       <c r="R119" t="n">
-        <v>6845111</v>
+        <v>6845284</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12210,10 +12219,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755601</v>
+        <v>125736623</v>
       </c>
       <c r="B120" t="n">
-        <v>92700</v>
+        <v>78967</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12221,34 +12230,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523463</v>
+        <v>523689</v>
       </c>
       <c r="R120" t="n">
-        <v>6845230</v>
+        <v>6845339</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12295,66 +12304,57 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755563</v>
+        <v>125732643</v>
       </c>
       <c r="B121" t="n">
-        <v>56843</v>
+        <v>79556</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523483</v>
+        <v>523617</v>
       </c>
       <c r="R121" t="n">
-        <v>6845365</v>
+        <v>6845031</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12401,12 +12401,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755704</v>
+        <v>125732670</v>
       </c>
       <c r="B124" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,34 +12618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523760</v>
+        <v>523617</v>
       </c>
       <c r="R124" t="n">
-        <v>6845283</v>
+        <v>6845031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12692,19 +12692,19 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755715</v>
+        <v>125755704</v>
       </c>
       <c r="B125" t="n">
         <v>78967</v>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523450</v>
+        <v>523760</v>
       </c>
       <c r="R125" t="n">
-        <v>6845349</v>
+        <v>6845283</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125732670</v>
+        <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>79585</v>
+        <v>91227</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,34 +12812,34 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523617</v>
+        <v>523340</v>
       </c>
       <c r="R126" t="n">
-        <v>6845031</v>
+        <v>6845392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12886,22 +12886,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125734818</v>
+        <v>125755715</v>
       </c>
       <c r="B127" t="n">
-        <v>91240</v>
+        <v>78967</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,37 +12909,37 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523643</v>
+        <v>523450</v>
       </c>
       <c r="R127" t="n">
-        <v>6845282</v>
+        <v>6845349</v>
       </c>
       <c r="S127" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -12983,22 +12983,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755557</v>
+        <v>125755780</v>
       </c>
       <c r="B128" t="n">
-        <v>91220</v>
+        <v>78634</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523340</v>
+        <v>523584</v>
       </c>
       <c r="R128" t="n">
-        <v>6845392</v>
+        <v>6845361</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125755780</v>
+        <v>125734818</v>
       </c>
       <c r="B129" t="n">
-        <v>78634</v>
+        <v>91247</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523584</v>
+        <v>523643</v>
       </c>
       <c r="R129" t="n">
-        <v>6845361</v>
+        <v>6845282</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125734476</v>
+        <v>125736529</v>
       </c>
       <c r="B2" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523492</v>
+        <v>523524</v>
       </c>
       <c r="R2" t="n">
-        <v>6845165</v>
+        <v>6845323</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755703</v>
+        <v>125737411</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523783</v>
+        <v>523825</v>
       </c>
       <c r="R3" t="n">
-        <v>6845289</v>
+        <v>6845311</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755705</v>
+        <v>125734228</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523728</v>
+        <v>523467</v>
       </c>
       <c r="R4" t="n">
-        <v>6845268</v>
+        <v>6845121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,22 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755643</v>
+        <v>125755703</v>
       </c>
       <c r="B5" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523816</v>
+        <v>523783</v>
       </c>
       <c r="R5" t="n">
-        <v>6845298</v>
+        <v>6845289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125737411</v>
+        <v>125755705</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523825</v>
+        <v>523728</v>
       </c>
       <c r="R6" t="n">
-        <v>6845311</v>
+        <v>6845268</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734228</v>
+        <v>125755643</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523467</v>
+        <v>523816</v>
       </c>
       <c r="R7" t="n">
-        <v>6845121</v>
+        <v>6845298</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125736529</v>
+        <v>125734476</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523524</v>
+        <v>523492</v>
       </c>
       <c r="R8" t="n">
-        <v>6845323</v>
+        <v>6845165</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,49 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B9" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R9" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1455,45 +1451,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755708</v>
+        <v>125735595</v>
       </c>
       <c r="B10" t="n">
-        <v>78967</v>
+        <v>98331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523626</v>
+        <v>523492</v>
       </c>
       <c r="R10" t="n">
-        <v>6845380</v>
+        <v>6845165</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,19 +1540,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B11" t="n">
         <v>78967</v>
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R11" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,7 +1649,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125736051</v>
+        <v>125755711</v>
       </c>
       <c r="B12" t="n">
         <v>78967</v>
@@ -1680,14 +1680,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523418</v>
+        <v>523443</v>
       </c>
       <c r="R12" t="n">
-        <v>6845349</v>
+        <v>6845363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,22 +1734,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125734647</v>
+        <v>125755632</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,37 +1757,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523611</v>
+        <v>523621</v>
       </c>
       <c r="R13" t="n">
-        <v>6845275</v>
+        <v>6845375</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1831,19 +1831,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755698</v>
+        <v>125734647</v>
       </c>
       <c r="B14" t="n">
         <v>78967</v>
@@ -1874,17 +1874,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523867</v>
+        <v>523611</v>
       </c>
       <c r="R14" t="n">
-        <v>6845227</v>
+        <v>6845275</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,19 +1928,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755711</v>
+        <v>125755708</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523443</v>
+        <v>523626</v>
       </c>
       <c r="R15" t="n">
-        <v>6845363</v>
+        <v>6845380</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755632</v>
+        <v>125755716</v>
       </c>
       <c r="B16" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523621</v>
+        <v>523477</v>
       </c>
       <c r="R16" t="n">
-        <v>6845375</v>
+        <v>6845219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125737958</v>
+        <v>125755786</v>
       </c>
       <c r="B17" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523967</v>
+        <v>523474</v>
       </c>
       <c r="R17" t="n">
-        <v>6845175</v>
+        <v>6845244</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125733598</v>
+        <v>125755785</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,37 +2242,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523483</v>
+        <v>523467</v>
       </c>
       <c r="R18" t="n">
-        <v>6845118</v>
+        <v>6845333</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2316,19 +2316,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755693</v>
+        <v>125755710</v>
       </c>
       <c r="B19" t="n">
         <v>78967</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523993</v>
+        <v>523572</v>
       </c>
       <c r="R19" t="n">
-        <v>6845158</v>
+        <v>6845367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755786</v>
+        <v>125733598</v>
       </c>
       <c r="B20" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523474</v>
+        <v>523483</v>
       </c>
       <c r="R20" t="n">
-        <v>6845244</v>
+        <v>6845118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2510,22 +2510,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755785</v>
+        <v>125737958</v>
       </c>
       <c r="B21" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523467</v>
+        <v>523967</v>
       </c>
       <c r="R21" t="n">
-        <v>6845333</v>
+        <v>6845175</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2607,19 +2607,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755710</v>
+        <v>125755693</v>
       </c>
       <c r="B22" t="n">
         <v>78967</v>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523572</v>
+        <v>523993</v>
       </c>
       <c r="R22" t="n">
-        <v>6845367</v>
+        <v>6845158</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,10 +2716,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755719</v>
+        <v>125736021</v>
       </c>
       <c r="B23" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,34 +2727,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523554</v>
+        <v>523418</v>
       </c>
       <c r="R23" t="n">
-        <v>6845068</v>
+        <v>6845349</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2801,22 +2801,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755790</v>
+        <v>125735304</v>
       </c>
       <c r="B24" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,37 +2824,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523486</v>
+        <v>523580</v>
       </c>
       <c r="R24" t="n">
-        <v>6845100</v>
+        <v>6845417</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2898,22 +2898,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755593</v>
+        <v>125733851</v>
       </c>
       <c r="B25" t="n">
-        <v>57651</v>
+        <v>91247</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,42 +2921,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523520</v>
+        <v>523470</v>
       </c>
       <c r="R25" t="n">
-        <v>6845094</v>
+        <v>6845106</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2986,11 +2981,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3005,22 +2995,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125735304</v>
+        <v>125755790</v>
       </c>
       <c r="B26" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,37 +3018,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523580</v>
+        <v>523486</v>
       </c>
       <c r="R26" t="n">
-        <v>6845417</v>
+        <v>6845100</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3102,22 +3092,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125733851</v>
+        <v>125755593</v>
       </c>
       <c r="B27" t="n">
-        <v>91247</v>
+        <v>57651</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,37 +3115,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523470</v>
+        <v>523520</v>
       </c>
       <c r="R27" t="n">
-        <v>6845106</v>
+        <v>6845094</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3185,6 +3180,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3199,22 +3199,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125736021</v>
+        <v>125755719</v>
       </c>
       <c r="B28" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,34 +3222,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523418</v>
+        <v>523554</v>
       </c>
       <c r="R28" t="n">
-        <v>6845349</v>
+        <v>6845068</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3296,12 +3296,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755549</v>
+        <v>125755634</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523541</v>
+        <v>523498</v>
       </c>
       <c r="R32" t="n">
-        <v>6845054</v>
+        <v>6845404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755545</v>
+        <v>125755549</v>
       </c>
       <c r="B33" t="n">
         <v>79585</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523465</v>
+        <v>523541</v>
       </c>
       <c r="R33" t="n">
-        <v>6845109</v>
+        <v>6845054</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755657</v>
+        <v>125755545</v>
       </c>
       <c r="B34" t="n">
-        <v>91387</v>
+        <v>79585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523463</v>
+        <v>523465</v>
       </c>
       <c r="R34" t="n">
-        <v>6845211</v>
+        <v>6845109</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,32 +3890,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755634</v>
+        <v>125755657</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>91387</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523498</v>
+        <v>523463</v>
       </c>
       <c r="R35" t="n">
-        <v>6845404</v>
+        <v>6845211</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755544</v>
+        <v>125734662</v>
       </c>
       <c r="B39" t="n">
-        <v>79585</v>
+        <v>78725</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,34 +4289,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523483</v>
+        <v>523492</v>
       </c>
       <c r="R39" t="n">
-        <v>6845181</v>
+        <v>6845165</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755539</v>
+        <v>125734860</v>
       </c>
       <c r="B40" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523924</v>
+        <v>523673</v>
       </c>
       <c r="R40" t="n">
-        <v>6845215</v>
+        <v>6845294</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125734662</v>
+        <v>125735540</v>
       </c>
       <c r="B41" t="n">
-        <v>78725</v>
+        <v>78967</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523492</v>
+        <v>523479</v>
       </c>
       <c r="R41" t="n">
-        <v>6845165</v>
+        <v>6845406</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4557,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734860</v>
+        <v>125755544</v>
       </c>
       <c r="B42" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523673</v>
+        <v>523483</v>
       </c>
       <c r="R42" t="n">
-        <v>6845294</v>
+        <v>6845181</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B43" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R43" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,12 +4751,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4860,48 +4860,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755658</v>
+        <v>125737014</v>
       </c>
       <c r="B45" t="n">
-        <v>91387</v>
+        <v>78726</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523487</v>
+        <v>523854</v>
       </c>
       <c r="R45" t="n">
-        <v>6845098</v>
+        <v>6845289</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755792</v>
+        <v>125735128</v>
       </c>
       <c r="B46" t="n">
-        <v>92503</v>
+        <v>79585</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523992</v>
+        <v>523627</v>
       </c>
       <c r="R46" t="n">
-        <v>6845170</v>
+        <v>6845420</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5028,11 +5028,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5047,19 +5042,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755717</v>
+        <v>125734241</v>
       </c>
       <c r="B47" t="n">
         <v>78967</v>
@@ -5090,14 +5085,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523466</v>
+        <v>523492</v>
       </c>
       <c r="R47" t="n">
-        <v>6845180</v>
+        <v>6845165</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,57 +5139,57 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755552</v>
+        <v>125736099</v>
       </c>
       <c r="B48" t="n">
-        <v>91192</v>
+        <v>78967</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523424</v>
+        <v>523514</v>
       </c>
       <c r="R48" t="n">
-        <v>6845383</v>
+        <v>6845340</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5241,60 +5236,60 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125735128</v>
+        <v>125755658</v>
       </c>
       <c r="B49" t="n">
-        <v>79585</v>
+        <v>91387</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523627</v>
+        <v>523487</v>
       </c>
       <c r="R49" t="n">
-        <v>6845420</v>
+        <v>6845098</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5338,22 +5333,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125734241</v>
+        <v>125755792</v>
       </c>
       <c r="B50" t="n">
-        <v>78967</v>
+        <v>92503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5361,34 +5356,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523492</v>
+        <v>523992</v>
       </c>
       <c r="R50" t="n">
-        <v>6845165</v>
+        <v>6845170</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5423,6 +5418,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -5435,19 +5435,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125736099</v>
+        <v>125755717</v>
       </c>
       <c r="B51" t="n">
         <v>78967</v>
@@ -5478,14 +5478,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523514</v>
+        <v>523466</v>
       </c>
       <c r="R51" t="n">
-        <v>6845340</v>
+        <v>6845180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5532,60 +5532,60 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125737014</v>
+        <v>125755552</v>
       </c>
       <c r="B52" t="n">
-        <v>78726</v>
+        <v>91192</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523854</v>
+        <v>523424</v>
       </c>
       <c r="R52" t="n">
-        <v>6845289</v>
+        <v>6845383</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7018,45 +7018,50 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755598</v>
+        <v>125738012</v>
       </c>
       <c r="B67" t="n">
-        <v>97209</v>
+        <v>57651</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523351</v>
+        <v>523967</v>
       </c>
       <c r="R67" t="n">
-        <v>6845393</v>
+        <v>6845175</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7103,44 +7108,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755630</v>
+        <v>125755598</v>
       </c>
       <c r="B68" t="n">
-        <v>78726</v>
+        <v>97209</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7155,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523671</v>
+        <v>523351</v>
       </c>
       <c r="R68" t="n">
-        <v>6845353</v>
+        <v>6845393</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,10 +7217,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755629</v>
+        <v>125733520</v>
       </c>
       <c r="B69" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,34 +7228,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523679</v>
+        <v>523552</v>
       </c>
       <c r="R69" t="n">
-        <v>6845347</v>
+        <v>6845072</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7297,19 +7302,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125733520</v>
+        <v>125733632</v>
       </c>
       <c r="B70" t="n">
         <v>78967</v>
@@ -7344,10 +7349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523552</v>
+        <v>523458</v>
       </c>
       <c r="R70" t="n">
-        <v>6845072</v>
+        <v>6845126</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7406,10 +7411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125733632</v>
+        <v>125734739</v>
       </c>
       <c r="B71" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7417,37 +7422,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523458</v>
+        <v>523608</v>
       </c>
       <c r="R71" t="n">
-        <v>6845126</v>
+        <v>6845309</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7491,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755761</v>
+        <v>125755709</v>
       </c>
       <c r="B72" t="n">
-        <v>57651</v>
+        <v>78967</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7514,39 +7519,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523387</v>
+        <v>523598</v>
       </c>
       <c r="R72" t="n">
-        <v>6845410</v>
+        <v>6845380</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125738012</v>
+        <v>125755788</v>
       </c>
       <c r="B73" t="n">
-        <v>57651</v>
+        <v>78634</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,39 +7616,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523967</v>
+        <v>523460</v>
       </c>
       <c r="R73" t="n">
-        <v>6845175</v>
+        <v>6845221</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7695,22 +7690,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125734739</v>
+        <v>125755761</v>
       </c>
       <c r="B74" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7718,37 +7713,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523608</v>
+        <v>523387</v>
       </c>
       <c r="R74" t="n">
-        <v>6845309</v>
+        <v>6845410</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7792,22 +7792,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755709</v>
+        <v>125755630</v>
       </c>
       <c r="B75" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523598</v>
+        <v>523671</v>
       </c>
       <c r="R75" t="n">
-        <v>6845380</v>
+        <v>6845353</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7901,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755788</v>
+        <v>125755629</v>
       </c>
       <c r="B76" t="n">
-        <v>78634</v>
+        <v>78726</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,21 +7912,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523460</v>
+        <v>523679</v>
       </c>
       <c r="R76" t="n">
-        <v>6845221</v>
+        <v>6845347</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7998,10 +7998,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755707</v>
+        <v>125755541</v>
       </c>
       <c r="B77" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523644</v>
+        <v>523757</v>
       </c>
       <c r="R77" t="n">
-        <v>6845389</v>
+        <v>6845248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8095,32 +8095,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755794</v>
+        <v>125755701</v>
       </c>
       <c r="B78" t="n">
-        <v>91634</v>
+        <v>78967</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523385</v>
+        <v>523839</v>
       </c>
       <c r="R78" t="n">
-        <v>6845416</v>
+        <v>6845286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8166,11 +8166,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8197,49 +8192,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125735686</v>
+        <v>125755714</v>
       </c>
       <c r="B79" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523418</v>
+        <v>523383</v>
       </c>
       <c r="R79" t="n">
-        <v>6845349</v>
+        <v>6845391</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,57 +8277,61 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755541</v>
+        <v>125735686</v>
       </c>
       <c r="B80" t="n">
-        <v>79585</v>
+        <v>98331</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523757</v>
+        <v>523418</v>
       </c>
       <c r="R80" t="n">
-        <v>6845248</v>
+        <v>6845349</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8383,19 +8378,19 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B81" t="n">
         <v>78967</v>
@@ -8430,10 +8425,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R81" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8492,32 +8487,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755714</v>
+        <v>125755794</v>
       </c>
       <c r="B82" t="n">
-        <v>78967</v>
+        <v>91634</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8527,10 +8522,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523383</v>
+        <v>523385</v>
       </c>
       <c r="R82" t="n">
-        <v>6845391</v>
+        <v>6845416</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8563,6 +8558,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10450,7 +10450,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125736651</v>
+        <v>125755712</v>
       </c>
       <c r="B102" t="n">
         <v>78967</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523722</v>
+        <v>523428</v>
       </c>
       <c r="R102" t="n">
-        <v>6845318</v>
+        <v>6845361</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125734280</v>
+        <v>125755550</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10558,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523482</v>
+        <v>523604</v>
       </c>
       <c r="R103" t="n">
-        <v>6845199</v>
+        <v>6845013</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,22 +10632,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755712</v>
+        <v>125755547</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523428</v>
+        <v>523479</v>
       </c>
       <c r="R104" t="n">
-        <v>6845361</v>
+        <v>6845112</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755550</v>
+        <v>125736651</v>
       </c>
       <c r="B105" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523604</v>
+        <v>523722</v>
       </c>
       <c r="R105" t="n">
-        <v>6845013</v>
+        <v>6845318</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10826,22 +10826,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755547</v>
+        <v>125734280</v>
       </c>
       <c r="B106" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,37 +10849,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523479</v>
+        <v>523482</v>
       </c>
       <c r="R106" t="n">
-        <v>6845112</v>
+        <v>6845199</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,12 +10923,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11129,10 +11129,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125737839</v>
+        <v>125755617</v>
       </c>
       <c r="B109" t="n">
-        <v>79556</v>
+        <v>78726</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523967</v>
+        <v>523972</v>
       </c>
       <c r="R109" t="n">
-        <v>6845175</v>
+        <v>6845173</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11214,22 +11214,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755713</v>
+        <v>125737839</v>
       </c>
       <c r="B110" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523332</v>
+        <v>523967</v>
       </c>
       <c r="R110" t="n">
-        <v>6845377</v>
+        <v>6845175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,19 +11311,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755706</v>
+        <v>125755713</v>
       </c>
       <c r="B111" t="n">
         <v>78967</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523655</v>
+        <v>523332</v>
       </c>
       <c r="R111" t="n">
-        <v>6845374</v>
+        <v>6845377</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755617</v>
+        <v>125755706</v>
       </c>
       <c r="B112" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523972</v>
+        <v>523655</v>
       </c>
       <c r="R112" t="n">
-        <v>6845173</v>
+        <v>6845374</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125732670</v>
+        <v>125755704</v>
       </c>
       <c r="B124" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,34 +12618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523617</v>
+        <v>523760</v>
       </c>
       <c r="R124" t="n">
-        <v>6845031</v>
+        <v>6845283</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755704</v>
+        <v>125755557</v>
       </c>
       <c r="B125" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523760</v>
+        <v>523340</v>
       </c>
       <c r="R125" t="n">
-        <v>6845283</v>
+        <v>6845392</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755557</v>
+        <v>125755715</v>
       </c>
       <c r="B126" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523340</v>
+        <v>523450</v>
       </c>
       <c r="R126" t="n">
-        <v>6845392</v>
+        <v>6845349</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755715</v>
+        <v>125755780</v>
       </c>
       <c r="B127" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523450</v>
+        <v>523584</v>
       </c>
       <c r="R127" t="n">
-        <v>6845349</v>
+        <v>6845361</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755780</v>
+        <v>125734818</v>
       </c>
       <c r="B128" t="n">
-        <v>78634</v>
+        <v>91247</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523584</v>
+        <v>523643</v>
       </c>
       <c r="R128" t="n">
-        <v>6845361</v>
+        <v>6845282</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125734818</v>
+        <v>125732670</v>
       </c>
       <c r="B129" t="n">
-        <v>91247</v>
+        <v>79585</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R129" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125737411</v>
+        <v>125734476</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523825</v>
+        <v>523492</v>
       </c>
       <c r="R3" t="n">
-        <v>6845311</v>
+        <v>6845165</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,7 +869,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125734228</v>
+        <v>125755703</v>
       </c>
       <c r="B4" t="n">
         <v>78967</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523467</v>
+        <v>523783</v>
       </c>
       <c r="R4" t="n">
-        <v>6845121</v>
+        <v>6845289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755703</v>
+        <v>125755705</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523783</v>
+        <v>523728</v>
       </c>
       <c r="R5" t="n">
-        <v>6845289</v>
+        <v>6845268</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755705</v>
+        <v>125755643</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>80070</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523728</v>
+        <v>523816</v>
       </c>
       <c r="R6" t="n">
-        <v>6845268</v>
+        <v>6845298</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755643</v>
+        <v>125737411</v>
       </c>
       <c r="B7" t="n">
-        <v>80070</v>
+        <v>78967</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523816</v>
+        <v>523825</v>
       </c>
       <c r="R7" t="n">
-        <v>6845298</v>
+        <v>6845311</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125734476</v>
+        <v>125734228</v>
       </c>
       <c r="B8" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523492</v>
+        <v>523467</v>
       </c>
       <c r="R8" t="n">
-        <v>6845165</v>
+        <v>6845121</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755634</v>
+        <v>125755549</v>
       </c>
       <c r="B32" t="n">
-        <v>78726</v>
+        <v>79585</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523498</v>
+        <v>523541</v>
       </c>
       <c r="R32" t="n">
-        <v>6845404</v>
+        <v>6845054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755549</v>
+        <v>125755545</v>
       </c>
       <c r="B33" t="n">
         <v>79585</v>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523541</v>
+        <v>523465</v>
       </c>
       <c r="R33" t="n">
-        <v>6845054</v>
+        <v>6845109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755545</v>
+        <v>125755657</v>
       </c>
       <c r="B34" t="n">
-        <v>79585</v>
+        <v>91387</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523465</v>
+        <v>523463</v>
       </c>
       <c r="R34" t="n">
-        <v>6845109</v>
+        <v>6845211</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,32 +3890,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755657</v>
+        <v>125755634</v>
       </c>
       <c r="B35" t="n">
-        <v>91387</v>
+        <v>78726</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523463</v>
+        <v>523498</v>
       </c>
       <c r="R35" t="n">
-        <v>6845211</v>
+        <v>6845404</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125732709</v>
+        <v>125755636</v>
       </c>
       <c r="B57" t="n">
         <v>78726</v>
@@ -6070,17 +6070,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523548</v>
+        <v>523511</v>
       </c>
       <c r="R57" t="n">
-        <v>6845076</v>
+        <v>6845102</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6124,19 +6124,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755636</v>
+        <v>125755627</v>
       </c>
       <c r="B58" t="n">
         <v>78726</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523511</v>
+        <v>523755</v>
       </c>
       <c r="R58" t="n">
-        <v>6845102</v>
+        <v>6845251</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755627</v>
+        <v>125755628</v>
       </c>
       <c r="B59" t="n">
         <v>78726</v>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523755</v>
+        <v>523728</v>
       </c>
       <c r="R59" t="n">
-        <v>6845251</v>
+        <v>6845279</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755628</v>
+        <v>125732709</v>
       </c>
       <c r="B60" t="n">
         <v>78726</v>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523728</v>
+        <v>523548</v>
       </c>
       <c r="R60" t="n">
-        <v>6845279</v>
+        <v>6845076</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,44 +6415,44 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125735892</v>
+        <v>125735337</v>
       </c>
       <c r="B61" t="n">
-        <v>92509</v>
+        <v>78726</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6462,10 +6462,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523608</v>
+        <v>523593</v>
       </c>
       <c r="R61" t="n">
-        <v>6845376</v>
+        <v>6845417</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6524,10 +6524,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125736672</v>
+        <v>125734655</v>
       </c>
       <c r="B62" t="n">
-        <v>78967</v>
+        <v>78726</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523827</v>
+        <v>523492</v>
       </c>
       <c r="R62" t="n">
-        <v>6845310</v>
+        <v>6845165</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,19 +6609,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125735337</v>
+        <v>125734972</v>
       </c>
       <c r="B63" t="n">
         <v>78726</v>
@@ -6656,10 +6656,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523593</v>
+        <v>523675</v>
       </c>
       <c r="R63" t="n">
-        <v>6845417</v>
+        <v>6845339</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6718,45 +6718,54 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125734655</v>
+        <v>125755647</v>
       </c>
       <c r="B64" t="n">
-        <v>78726</v>
+        <v>98331</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523492</v>
+        <v>523408</v>
       </c>
       <c r="R64" t="n">
-        <v>6845165</v>
+        <v>6845401</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6803,44 +6812,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734972</v>
+        <v>125735892</v>
       </c>
       <c r="B65" t="n">
-        <v>78726</v>
+        <v>92509</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6850,10 +6859,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523675</v>
+        <v>523608</v>
       </c>
       <c r="R65" t="n">
-        <v>6845339</v>
+        <v>6845376</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6912,57 +6921,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755647</v>
+        <v>125736672</v>
       </c>
       <c r="B66" t="n">
-        <v>98331</v>
+        <v>78967</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523408</v>
+        <v>523827</v>
       </c>
       <c r="R66" t="n">
-        <v>6845401</v>
+        <v>6845310</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,12 +7006,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125732736</v>
+        <v>125737510</v>
       </c>
       <c r="B83" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523551</v>
+        <v>523957</v>
       </c>
       <c r="R83" t="n">
-        <v>6845080</v>
+        <v>6845190</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755789</v>
+        <v>125732736</v>
       </c>
       <c r="B84" t="n">
-        <v>78634</v>
+        <v>78725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8697,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523480</v>
+        <v>523551</v>
       </c>
       <c r="R84" t="n">
-        <v>6845112</v>
+        <v>6845080</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,12 +8771,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125737510</v>
+        <v>125755702</v>
       </c>
       <c r="B86" t="n">
-        <v>78726</v>
+        <v>78967</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523957</v>
+        <v>523829</v>
       </c>
       <c r="R86" t="n">
-        <v>6845190</v>
+        <v>6845308</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755702</v>
+        <v>125755789</v>
       </c>
       <c r="B87" t="n">
-        <v>78967</v>
+        <v>78634</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523829</v>
+        <v>523480</v>
       </c>
       <c r="R87" t="n">
-        <v>6845308</v>
+        <v>6845112</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9074,45 +9074,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755700</v>
+        <v>125732728</v>
       </c>
       <c r="B88" t="n">
-        <v>78967</v>
+        <v>92509</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523859</v>
+        <v>523590</v>
       </c>
       <c r="R88" t="n">
-        <v>6845221</v>
+        <v>6845030</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,57 +9163,66 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755783</v>
+        <v>125755654</v>
       </c>
       <c r="B89" t="n">
-        <v>78634</v>
+        <v>98331</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523644</v>
+        <v>523428</v>
       </c>
       <c r="R89" t="n">
-        <v>6845379</v>
+        <v>6845361</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,7 +9281,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755697</v>
+        <v>125755700</v>
       </c>
       <c r="B90" t="n">
         <v>78967</v>
@@ -9303,10 +9316,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523948</v>
+        <v>523859</v>
       </c>
       <c r="R90" t="n">
-        <v>6845177</v>
+        <v>6845221</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,32 +9378,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755775</v>
+        <v>125755783</v>
       </c>
       <c r="B91" t="n">
-        <v>92509</v>
+        <v>78634</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9400,10 +9413,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523541</v>
+        <v>523644</v>
       </c>
       <c r="R91" t="n">
-        <v>6845044</v>
+        <v>6845379</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9462,10 +9475,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755553</v>
+        <v>125755697</v>
       </c>
       <c r="B92" t="n">
-        <v>79556</v>
+        <v>78967</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9473,21 +9486,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9497,10 +9510,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523626</v>
+        <v>523948</v>
       </c>
       <c r="R92" t="n">
-        <v>6845383</v>
+        <v>6845177</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9559,7 +9572,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125732728</v>
+        <v>125755775</v>
       </c>
       <c r="B93" t="n">
         <v>92509</v>
@@ -9587,21 +9600,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523590</v>
+        <v>523541</v>
       </c>
       <c r="R93" t="n">
-        <v>6845030</v>
+        <v>6845044</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9648,66 +9657,57 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755654</v>
+        <v>125755553</v>
       </c>
       <c r="B94" t="n">
-        <v>98331</v>
+        <v>79556</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523428</v>
+        <v>523626</v>
       </c>
       <c r="R94" t="n">
-        <v>6845361</v>
+        <v>6845383</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10450,7 +10450,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755712</v>
+        <v>125736651</v>
       </c>
       <c r="B102" t="n">
         <v>78967</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523428</v>
+        <v>523722</v>
       </c>
       <c r="R102" t="n">
-        <v>6845361</v>
+        <v>6845318</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755550</v>
+        <v>125734280</v>
       </c>
       <c r="B103" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10558,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523604</v>
+        <v>523482</v>
       </c>
       <c r="R103" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,22 +10632,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755547</v>
+        <v>125755712</v>
       </c>
       <c r="B104" t="n">
-        <v>79585</v>
+        <v>78967</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523479</v>
+        <v>523428</v>
       </c>
       <c r="R104" t="n">
-        <v>6845112</v>
+        <v>6845361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125736651</v>
+        <v>125755550</v>
       </c>
       <c r="B105" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523722</v>
+        <v>523604</v>
       </c>
       <c r="R105" t="n">
-        <v>6845318</v>
+        <v>6845013</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10826,22 +10826,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125734280</v>
+        <v>125755547</v>
       </c>
       <c r="B106" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,37 +10849,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523482</v>
+        <v>523479</v>
       </c>
       <c r="R106" t="n">
-        <v>6845199</v>
+        <v>6845112</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,12 +10923,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755555</v>
+        <v>125755631</v>
       </c>
       <c r="B115" t="n">
-        <v>90265</v>
+        <v>78726</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,21 +11731,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523480</v>
+        <v>523636</v>
       </c>
       <c r="R115" t="n">
-        <v>6845111</v>
+        <v>6845388</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11817,10 +11817,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755601</v>
+        <v>125755619</v>
       </c>
       <c r="B116" t="n">
-        <v>92707</v>
+        <v>78726</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11828,21 +11828,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11852,10 +11852,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523463</v>
+        <v>523952</v>
       </c>
       <c r="R116" t="n">
-        <v>6845230</v>
+        <v>6845185</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11914,45 +11914,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755784</v>
+        <v>125755608</v>
       </c>
       <c r="B117" t="n">
-        <v>78634</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523606</v>
+        <v>523745</v>
       </c>
       <c r="R117" t="n">
-        <v>6845378</v>
+        <v>6845284</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12011,54 +12016,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755563</v>
+        <v>125736623</v>
       </c>
       <c r="B118" t="n">
-        <v>56843</v>
+        <v>78967</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523483</v>
+        <v>523689</v>
       </c>
       <c r="R118" t="n">
-        <v>6845365</v>
+        <v>6845339</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12105,22 +12101,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755608</v>
+        <v>125755563</v>
       </c>
       <c r="B119" t="n">
-        <v>8447</v>
+        <v>56843</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12128,27 +12124,31 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P119" t="inlineStr">
@@ -12157,10 +12157,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523745</v>
+        <v>523483</v>
       </c>
       <c r="R119" t="n">
-        <v>6845284</v>
+        <v>6845365</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12219,10 +12219,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125736623</v>
+        <v>125732643</v>
       </c>
       <c r="B120" t="n">
-        <v>78967</v>
+        <v>79556</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12230,21 +12230,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12254,10 +12254,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523689</v>
+        <v>523617</v>
       </c>
       <c r="R120" t="n">
-        <v>6845339</v>
+        <v>6845031</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12316,10 +12316,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125732643</v>
+        <v>125755555</v>
       </c>
       <c r="B121" t="n">
-        <v>79556</v>
+        <v>90265</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12327,34 +12327,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523617</v>
+        <v>523480</v>
       </c>
       <c r="R121" t="n">
-        <v>6845031</v>
+        <v>6845111</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12401,22 +12401,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755631</v>
+        <v>125755601</v>
       </c>
       <c r="B122" t="n">
-        <v>78726</v>
+        <v>92707</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523636</v>
+        <v>523463</v>
       </c>
       <c r="R122" t="n">
-        <v>6845388</v>
+        <v>6845230</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12510,10 +12510,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755619</v>
+        <v>125755784</v>
       </c>
       <c r="B123" t="n">
-        <v>78726</v>
+        <v>78634</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,21 +12521,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523952</v>
+        <v>523606</v>
       </c>
       <c r="R123" t="n">
-        <v>6845185</v>
+        <v>6845378</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755704</v>
+        <v>125732670</v>
       </c>
       <c r="B124" t="n">
-        <v>78967</v>
+        <v>79585</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,34 +12618,34 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523760</v>
+        <v>523617</v>
       </c>
       <c r="R124" t="n">
-        <v>6845283</v>
+        <v>6845031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755557</v>
+        <v>125755704</v>
       </c>
       <c r="B125" t="n">
-        <v>91227</v>
+        <v>78967</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523340</v>
+        <v>523760</v>
       </c>
       <c r="R125" t="n">
-        <v>6845392</v>
+        <v>6845283</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755715</v>
+        <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>78967</v>
+        <v>91227</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523450</v>
+        <v>523340</v>
       </c>
       <c r="R126" t="n">
-        <v>6845349</v>
+        <v>6845392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755780</v>
+        <v>125755715</v>
       </c>
       <c r="B127" t="n">
-        <v>78634</v>
+        <v>78967</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523584</v>
+        <v>523450</v>
       </c>
       <c r="R127" t="n">
-        <v>6845361</v>
+        <v>6845349</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125734818</v>
+        <v>125755780</v>
       </c>
       <c r="B128" t="n">
-        <v>91247</v>
+        <v>78634</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523643</v>
+        <v>523584</v>
       </c>
       <c r="R128" t="n">
-        <v>6845282</v>
+        <v>6845361</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125732670</v>
+        <v>125734818</v>
       </c>
       <c r="B129" t="n">
-        <v>79585</v>
+        <v>91247</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523617</v>
+        <v>523643</v>
       </c>
       <c r="R129" t="n">
-        <v>6845031</v>
+        <v>6845282</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125736529</v>
+        <v>125755703</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523524</v>
+        <v>523783</v>
       </c>
       <c r="R2" t="n">
-        <v>6845323</v>
+        <v>6845289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125734476</v>
+        <v>125755705</v>
       </c>
       <c r="B3" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,34 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523492</v>
+        <v>523728</v>
       </c>
       <c r="R3" t="n">
-        <v>6845165</v>
+        <v>6845268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755703</v>
+        <v>125755643</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523783</v>
+        <v>523816</v>
       </c>
       <c r="R4" t="n">
-        <v>6845289</v>
+        <v>6845298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755705</v>
+        <v>125737411</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523728</v>
+        <v>523825</v>
       </c>
       <c r="R5" t="n">
-        <v>6845268</v>
+        <v>6845311</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755643</v>
+        <v>125734228</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523816</v>
+        <v>523467</v>
       </c>
       <c r="R6" t="n">
-        <v>6845298</v>
+        <v>6845121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125737411</v>
+        <v>125734476</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523825</v>
+        <v>523492</v>
       </c>
       <c r="R7" t="n">
-        <v>6845311</v>
+        <v>6845165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125734228</v>
+        <v>125736529</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523467</v>
+        <v>523524</v>
       </c>
       <c r="R8" t="n">
-        <v>6845121</v>
+        <v>6845323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125736051</v>
+        <v>125734647</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523418</v>
+        <v>523611</v>
       </c>
       <c r="R9" t="n">
-        <v>6845349</v>
+        <v>6845275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,61 +1439,57 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B10" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R10" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755698</v>
+        <v>125755632</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1563,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523867</v>
+        <v>523621</v>
       </c>
       <c r="R11" t="n">
-        <v>6845227</v>
+        <v>6845375</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755711</v>
+        <v>125755708</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523443</v>
+        <v>523626</v>
       </c>
       <c r="R12" t="n">
-        <v>6845363</v>
+        <v>6845380</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755632</v>
+        <v>125755716</v>
       </c>
       <c r="B13" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1757,21 +1753,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1781,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523621</v>
+        <v>523477</v>
       </c>
       <c r="R13" t="n">
-        <v>6845375</v>
+        <v>6845219</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125734647</v>
+        <v>125755698</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523611</v>
+        <v>523867</v>
       </c>
       <c r="R14" t="n">
-        <v>6845275</v>
+        <v>6845227</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755708</v>
+        <v>125755711</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1975,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523626</v>
+        <v>523443</v>
       </c>
       <c r="R15" t="n">
-        <v>6845380</v>
+        <v>6845363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,45 +2033,49 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755716</v>
+        <v>125735595</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>98334</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523477</v>
+        <v>523492</v>
       </c>
       <c r="R16" t="n">
-        <v>6845219</v>
+        <v>6845165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,22 +2122,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755786</v>
+        <v>125755693</v>
       </c>
       <c r="B17" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523474</v>
+        <v>523993</v>
       </c>
       <c r="R17" t="n">
-        <v>6845244</v>
+        <v>6845158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755785</v>
+        <v>125755710</v>
       </c>
       <c r="B18" t="n">
-        <v>78634</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523467</v>
+        <v>523572</v>
       </c>
       <c r="R18" t="n">
-        <v>6845333</v>
+        <v>6845367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755710</v>
+        <v>125755786</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523572</v>
+        <v>523474</v>
       </c>
       <c r="R19" t="n">
-        <v>6845367</v>
+        <v>6845244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125733598</v>
+        <v>125755785</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,37 +2436,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523483</v>
+        <v>523467</v>
       </c>
       <c r="R20" t="n">
-        <v>6845118</v>
+        <v>6845333</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2510,22 +2510,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125737958</v>
+        <v>125733598</v>
       </c>
       <c r="B21" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,37 +2533,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523967</v>
+        <v>523483</v>
       </c>
       <c r="R21" t="n">
-        <v>6845175</v>
+        <v>6845118</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755693</v>
+        <v>125737958</v>
       </c>
       <c r="B22" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,21 +2630,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523993</v>
+        <v>523967</v>
       </c>
       <c r="R22" t="n">
-        <v>6845158</v>
+        <v>6845175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2704,22 +2704,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125736021</v>
+        <v>125755790</v>
       </c>
       <c r="B23" t="n">
-        <v>79585</v>
+        <v>78635</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,34 +2727,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523418</v>
+        <v>523486</v>
       </c>
       <c r="R23" t="n">
-        <v>6845349</v>
+        <v>6845100</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2801,22 +2801,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125735304</v>
+        <v>125755593</v>
       </c>
       <c r="B24" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,37 +2824,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523580</v>
+        <v>523520</v>
       </c>
       <c r="R24" t="n">
-        <v>6845417</v>
+        <v>6845094</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2884,6 +2889,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2898,22 +2908,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125733851</v>
+        <v>125735304</v>
       </c>
       <c r="B25" t="n">
-        <v>91247</v>
+        <v>78968</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523470</v>
+        <v>523580</v>
       </c>
       <c r="R25" t="n">
-        <v>6845106</v>
+        <v>6845417</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3007,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755790</v>
+        <v>125733851</v>
       </c>
       <c r="B26" t="n">
-        <v>78634</v>
+        <v>91248</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,37 +3028,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523486</v>
+        <v>523470</v>
       </c>
       <c r="R26" t="n">
-        <v>6845100</v>
+        <v>6845106</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3092,22 +3102,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755593</v>
+        <v>125736021</v>
       </c>
       <c r="B27" t="n">
-        <v>57651</v>
+        <v>79586</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,39 +3125,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523520</v>
+        <v>523418</v>
       </c>
       <c r="R27" t="n">
-        <v>6845094</v>
+        <v>6845349</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3182,11 +3187,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3199,12 +3199,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3214,7 +3214,7 @@
         <v>125755719</v>
       </c>
       <c r="B28" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>125733581</v>
       </c>
       <c r="B29" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>125737629</v>
       </c>
       <c r="B30" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125735113</v>
+        <v>125755545</v>
       </c>
       <c r="B31" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,37 +3513,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523630</v>
+        <v>523465</v>
       </c>
       <c r="R31" t="n">
-        <v>6845423</v>
+        <v>6845109</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,12 +3587,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
         <v>125755549</v>
       </c>
       <c r="B32" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755545</v>
+        <v>125755657</v>
       </c>
       <c r="B33" t="n">
-        <v>79585</v>
+        <v>91389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523465</v>
+        <v>523463</v>
       </c>
       <c r="R33" t="n">
-        <v>6845109</v>
+        <v>6845211</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3793,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755657</v>
+        <v>125755634</v>
       </c>
       <c r="B34" t="n">
-        <v>91387</v>
+        <v>78727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523463</v>
+        <v>523498</v>
       </c>
       <c r="R34" t="n">
-        <v>6845211</v>
+        <v>6845404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755634</v>
+        <v>125735113</v>
       </c>
       <c r="B35" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3921,17 +3921,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523498</v>
+        <v>523630</v>
       </c>
       <c r="R35" t="n">
-        <v>6845404</v>
+        <v>6845423</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,22 +3975,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755695</v>
+        <v>125755625</v>
       </c>
       <c r="B36" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523990</v>
+        <v>523850</v>
       </c>
       <c r="R36" t="n">
-        <v>6845162</v>
+        <v>6845286</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755565</v>
+        <v>125755695</v>
       </c>
       <c r="B37" t="n">
-        <v>91247</v>
+        <v>78968</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523551</v>
+        <v>523990</v>
       </c>
       <c r="R37" t="n">
-        <v>6845103</v>
+        <v>6845162</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755625</v>
+        <v>125755565</v>
       </c>
       <c r="B38" t="n">
-        <v>78726</v>
+        <v>91248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523850</v>
+        <v>523551</v>
       </c>
       <c r="R38" t="n">
-        <v>6845286</v>
+        <v>6845103</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125734662</v>
+        <v>125755787</v>
       </c>
       <c r="B39" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,34 +4289,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523492</v>
+        <v>523457</v>
       </c>
       <c r="R39" t="n">
-        <v>6845165</v>
+        <v>6845237</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125734860</v>
+        <v>125735540</v>
       </c>
       <c r="B40" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4410,10 +4410,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523673</v>
+        <v>523479</v>
       </c>
       <c r="R40" t="n">
-        <v>6845294</v>
+        <v>6845406</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125735540</v>
+        <v>125734860</v>
       </c>
       <c r="B41" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523479</v>
+        <v>523673</v>
       </c>
       <c r="R41" t="n">
-        <v>6845406</v>
+        <v>6845294</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755544</v>
+        <v>125734662</v>
       </c>
       <c r="B42" t="n">
-        <v>79585</v>
+        <v>78726</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,34 +4580,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523483</v>
+        <v>523492</v>
       </c>
       <c r="R42" t="n">
-        <v>6845181</v>
+        <v>6845165</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4654,12 +4654,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -4669,7 +4669,7 @@
         <v>125755539</v>
       </c>
       <c r="B43" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4763,10 +4763,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755787</v>
+        <v>125755544</v>
       </c>
       <c r="B44" t="n">
-        <v>78634</v>
+        <v>79586</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523457</v>
+        <v>523483</v>
       </c>
       <c r="R44" t="n">
-        <v>6845237</v>
+        <v>6845181</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125737014</v>
+        <v>125755626</v>
       </c>
       <c r="B45" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4891,17 +4891,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523854</v>
+        <v>523759</v>
       </c>
       <c r="R45" t="n">
-        <v>6845289</v>
+        <v>6845238</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125735128</v>
+        <v>125737014</v>
       </c>
       <c r="B46" t="n">
-        <v>79585</v>
+        <v>78727</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,34 +4968,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523627</v>
+        <v>523854</v>
       </c>
       <c r="R46" t="n">
-        <v>6845420</v>
+        <v>6845289</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5054,10 +5054,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125734241</v>
+        <v>125755792</v>
       </c>
       <c r="B47" t="n">
-        <v>78967</v>
+        <v>92512</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5065,34 +5065,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523492</v>
+        <v>523992</v>
       </c>
       <c r="R47" t="n">
-        <v>6845165</v>
+        <v>6845170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5127,6 +5127,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5139,22 +5144,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125736099</v>
+        <v>125755717</v>
       </c>
       <c r="B48" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5182,14 +5187,14 @@
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523514</v>
+        <v>523466</v>
       </c>
       <c r="R48" t="n">
-        <v>6845340</v>
+        <v>6845180</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5236,44 +5241,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755658</v>
+        <v>125755552</v>
       </c>
       <c r="B49" t="n">
-        <v>91387</v>
+        <v>91193</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5283,10 +5288,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523487</v>
+        <v>523424</v>
       </c>
       <c r="R49" t="n">
-        <v>6845098</v>
+        <v>6845383</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5345,32 +5350,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755792</v>
+        <v>125755658</v>
       </c>
       <c r="B50" t="n">
-        <v>92503</v>
+        <v>91389</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>1503</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5380,10 +5385,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523992</v>
+        <v>523487</v>
       </c>
       <c r="R50" t="n">
-        <v>6845170</v>
+        <v>6845098</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5416,11 +5421,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5447,10 +5447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755717</v>
+        <v>125735128</v>
       </c>
       <c r="B51" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5458,37 +5458,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523466</v>
+        <v>523627</v>
       </c>
       <c r="R51" t="n">
-        <v>6845180</v>
+        <v>6845420</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,57 +5532,57 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755552</v>
+        <v>125736099</v>
       </c>
       <c r="B52" t="n">
-        <v>91192</v>
+        <v>78968</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523424</v>
+        <v>523514</v>
       </c>
       <c r="R52" t="n">
-        <v>6845383</v>
+        <v>6845340</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5629,22 +5629,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755626</v>
+        <v>125734241</v>
       </c>
       <c r="B53" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5652,34 +5652,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523759</v>
+        <v>523492</v>
       </c>
       <c r="R53" t="n">
-        <v>6845238</v>
+        <v>6845165</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5726,67 +5726,57 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125736061</v>
+        <v>125732709</v>
       </c>
       <c r="B54" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523643</v>
+        <v>523548</v>
       </c>
       <c r="R54" t="n">
-        <v>6845391</v>
+        <v>6845076</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5845,48 +5835,58 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755542</v>
+        <v>125736061</v>
       </c>
       <c r="B55" t="n">
-        <v>79585</v>
+        <v>56843</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523670</v>
+        <v>523643</v>
       </c>
       <c r="R55" t="n">
-        <v>6845353</v>
+        <v>6845391</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5930,22 +5930,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755543</v>
+        <v>125755542</v>
       </c>
       <c r="B56" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523460</v>
+        <v>523670</v>
       </c>
       <c r="R56" t="n">
-        <v>6845221</v>
+        <v>6845353</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755636</v>
+        <v>125755543</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>79586</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523511</v>
+        <v>523460</v>
       </c>
       <c r="R57" t="n">
-        <v>6845102</v>
+        <v>6845221</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755627</v>
+        <v>125755636</v>
       </c>
       <c r="B58" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523755</v>
+        <v>523511</v>
       </c>
       <c r="R58" t="n">
-        <v>6845251</v>
+        <v>6845102</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6236,7 +6236,7 @@
         <v>125755628</v>
       </c>
       <c r="B59" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125732709</v>
+        <v>125755627</v>
       </c>
       <c r="B60" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523548</v>
+        <v>523755</v>
       </c>
       <c r="R60" t="n">
-        <v>6845076</v>
+        <v>6845251</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,22 +6415,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125735337</v>
+        <v>125736672</v>
       </c>
       <c r="B61" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6438,34 +6438,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523593</v>
+        <v>523827</v>
       </c>
       <c r="R61" t="n">
-        <v>6845417</v>
+        <v>6845310</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -6524,48 +6524,48 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125734655</v>
+        <v>125735892</v>
       </c>
       <c r="B62" t="n">
-        <v>78726</v>
+        <v>92518</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523492</v>
+        <v>523608</v>
       </c>
       <c r="R62" t="n">
-        <v>6845165</v>
+        <v>6845376</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,60 +6609,69 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125734972</v>
+        <v>125755647</v>
       </c>
       <c r="B63" t="n">
-        <v>78726</v>
+        <v>98334</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523675</v>
+        <v>523408</v>
       </c>
       <c r="R63" t="n">
-        <v>6845339</v>
+        <v>6845401</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6706,69 +6715,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755647</v>
+        <v>125735337</v>
       </c>
       <c r="B64" t="n">
-        <v>98331</v>
+        <v>78727</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523408</v>
+        <v>523593</v>
       </c>
       <c r="R64" t="n">
-        <v>6845401</v>
+        <v>6845417</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6812,60 +6812,60 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125735892</v>
+        <v>125734655</v>
       </c>
       <c r="B65" t="n">
-        <v>92509</v>
+        <v>78727</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523608</v>
+        <v>523492</v>
       </c>
       <c r="R65" t="n">
-        <v>6845376</v>
+        <v>6845165</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6909,22 +6909,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125736672</v>
+        <v>125734972</v>
       </c>
       <c r="B66" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6932,34 +6932,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523827</v>
+        <v>523675</v>
       </c>
       <c r="R66" t="n">
-        <v>6845310</v>
+        <v>6845339</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125738012</v>
+        <v>125734739</v>
       </c>
       <c r="B67" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,42 +7029,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523967</v>
+        <v>523608</v>
       </c>
       <c r="R67" t="n">
-        <v>6845175</v>
+        <v>6845309</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7108,44 +7103,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755598</v>
+        <v>125755709</v>
       </c>
       <c r="B68" t="n">
-        <v>97209</v>
+        <v>78968</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7155,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523351</v>
+        <v>523598</v>
       </c>
       <c r="R68" t="n">
-        <v>6845393</v>
+        <v>6845380</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7217,10 +7212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125733520</v>
+        <v>125755788</v>
       </c>
       <c r="B69" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7228,34 +7223,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523552</v>
+        <v>523460</v>
       </c>
       <c r="R69" t="n">
-        <v>6845072</v>
+        <v>6845221</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7302,22 +7297,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125733632</v>
+        <v>125755761</v>
       </c>
       <c r="B70" t="n">
-        <v>78967</v>
+        <v>57651</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7325,34 +7320,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523458</v>
+        <v>523387</v>
       </c>
       <c r="R70" t="n">
-        <v>6845126</v>
+        <v>6845410</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7399,22 +7399,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125734739</v>
+        <v>125733520</v>
       </c>
       <c r="B71" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7422,37 +7422,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523608</v>
+        <v>523552</v>
       </c>
       <c r="R71" t="n">
-        <v>6845309</v>
+        <v>6845072</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7496,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755709</v>
+        <v>125733632</v>
       </c>
       <c r="B72" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7539,14 +7539,14 @@
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523598</v>
+        <v>523458</v>
       </c>
       <c r="R72" t="n">
-        <v>6845380</v>
+        <v>6845126</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,44 +7593,44 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755788</v>
+        <v>125755598</v>
       </c>
       <c r="B73" t="n">
-        <v>78634</v>
+        <v>97212</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523460</v>
+        <v>523351</v>
       </c>
       <c r="R73" t="n">
-        <v>6845221</v>
+        <v>6845393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7702,10 +7702,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755761</v>
+        <v>125755629</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,39 +7713,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523387</v>
+        <v>523679</v>
       </c>
       <c r="R74" t="n">
-        <v>6845410</v>
+        <v>6845347</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7807,7 +7802,7 @@
         <v>125755630</v>
       </c>
       <c r="B75" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7901,10 +7896,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755629</v>
+        <v>125738012</v>
       </c>
       <c r="B76" t="n">
-        <v>78726</v>
+        <v>57651</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,34 +7907,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523679</v>
+        <v>523967</v>
       </c>
       <c r="R76" t="n">
-        <v>6845347</v>
+        <v>6845175</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7986,22 +7986,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755541</v>
+        <v>125755701</v>
       </c>
       <c r="B77" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523757</v>
+        <v>523839</v>
       </c>
       <c r="R77" t="n">
-        <v>6845248</v>
+        <v>6845286</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B78" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R78" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8192,10 +8192,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755714</v>
+        <v>125755541</v>
       </c>
       <c r="B79" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8203,21 +8203,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523383</v>
+        <v>523757</v>
       </c>
       <c r="R79" t="n">
-        <v>6845391</v>
+        <v>6845248</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8289,49 +8289,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125735686</v>
+        <v>125755794</v>
       </c>
       <c r="B80" t="n">
-        <v>98331</v>
+        <v>91638</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523418</v>
+        <v>523385</v>
       </c>
       <c r="R80" t="n">
-        <v>6845349</v>
+        <v>6845416</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8366,6 +8362,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -8378,22 +8379,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755707</v>
+        <v>125755714</v>
       </c>
       <c r="B81" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8425,10 +8426,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523644</v>
+        <v>523383</v>
       </c>
       <c r="R81" t="n">
-        <v>6845389</v>
+        <v>6845391</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8487,45 +8488,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755794</v>
+        <v>125735686</v>
       </c>
       <c r="B82" t="n">
-        <v>91634</v>
+        <v>98334</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>4217</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523385</v>
+        <v>523418</v>
       </c>
       <c r="R82" t="n">
-        <v>6845416</v>
+        <v>6845349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8560,11 +8565,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -8577,22 +8577,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125737510</v>
+        <v>125755702</v>
       </c>
       <c r="B83" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,37 +8600,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523957</v>
+        <v>523829</v>
       </c>
       <c r="R83" t="n">
-        <v>6845190</v>
+        <v>6845308</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,22 +8674,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125732736</v>
+        <v>125755789</v>
       </c>
       <c r="B84" t="n">
-        <v>78725</v>
+        <v>78635</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8697,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523551</v>
+        <v>523480</v>
       </c>
       <c r="R84" t="n">
-        <v>6845080</v>
+        <v>6845112</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,19 +8771,19 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755621</v>
+        <v>125732736</v>
       </c>
       <c r="B85" t="n">
         <v>78726</v>
@@ -8794,37 +8794,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523920</v>
+        <v>523551</v>
       </c>
       <c r="R85" t="n">
-        <v>6845217</v>
+        <v>6845080</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8868,22 +8868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755702</v>
+        <v>125755621</v>
       </c>
       <c r="B86" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523829</v>
+        <v>523920</v>
       </c>
       <c r="R86" t="n">
-        <v>6845308</v>
+        <v>6845217</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,10 +8977,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755789</v>
+        <v>125737510</v>
       </c>
       <c r="B87" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8988,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523480</v>
+        <v>523957</v>
       </c>
       <c r="R87" t="n">
-        <v>6845112</v>
+        <v>6845190</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,61 +9062,57 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125732728</v>
+        <v>125755700</v>
       </c>
       <c r="B88" t="n">
-        <v>92509</v>
+        <v>78968</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523590</v>
+        <v>523859</v>
       </c>
       <c r="R88" t="n">
-        <v>6845030</v>
+        <v>6845221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9163,66 +9159,57 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755654</v>
+        <v>125755697</v>
       </c>
       <c r="B89" t="n">
-        <v>98331</v>
+        <v>78968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523428</v>
+        <v>523948</v>
       </c>
       <c r="R89" t="n">
-        <v>6845361</v>
+        <v>6845177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9281,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755700</v>
+        <v>125755775</v>
       </c>
       <c r="B90" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9316,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523859</v>
+        <v>523541</v>
       </c>
       <c r="R90" t="n">
-        <v>6845221</v>
+        <v>6845044</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9381,7 +9368,7 @@
         <v>125755783</v>
       </c>
       <c r="B91" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9475,45 +9462,49 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755697</v>
+        <v>125732728</v>
       </c>
       <c r="B92" t="n">
-        <v>78967</v>
+        <v>92518</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523948</v>
+        <v>523590</v>
       </c>
       <c r="R92" t="n">
-        <v>6845177</v>
+        <v>6845030</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,57 +9551,66 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755775</v>
+        <v>125755654</v>
       </c>
       <c r="B93" t="n">
-        <v>92509</v>
+        <v>98334</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523541</v>
+        <v>523428</v>
       </c>
       <c r="R93" t="n">
-        <v>6845044</v>
+        <v>6845361</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9672,7 +9672,7 @@
         <v>125755553</v>
       </c>
       <c r="B94" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9766,32 +9766,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125737769</v>
+        <v>125755774</v>
       </c>
       <c r="B95" t="n">
-        <v>79585</v>
+        <v>92518</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523967</v>
+        <v>523526</v>
       </c>
       <c r="R95" t="n">
-        <v>6845175</v>
+        <v>6845095</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,12 +9851,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -9866,7 +9866,7 @@
         <v>125755694</v>
       </c>
       <c r="B96" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9960,50 +9960,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755610</v>
+        <v>125737769</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523527</v>
+        <v>523967</v>
       </c>
       <c r="R97" t="n">
-        <v>6845375</v>
+        <v>6845175</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,57 +10045,62 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755624</v>
+        <v>125755610</v>
       </c>
       <c r="B98" t="n">
-        <v>78726</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523853</v>
+        <v>523527</v>
       </c>
       <c r="R98" t="n">
-        <v>6845279</v>
+        <v>6845375</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10159,32 +10159,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755774</v>
+        <v>125755781</v>
       </c>
       <c r="B99" t="n">
-        <v>92509</v>
+        <v>78635</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523526</v>
+        <v>523958</v>
       </c>
       <c r="R99" t="n">
-        <v>6845095</v>
+        <v>6845195</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755781</v>
+        <v>125755624</v>
       </c>
       <c r="B100" t="n">
-        <v>78634</v>
+        <v>78727</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523958</v>
+        <v>523853</v>
       </c>
       <c r="R100" t="n">
-        <v>6845195</v>
+        <v>6845279</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125737335</v>
+        <v>125755550</v>
       </c>
       <c r="B101" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10384,17 +10384,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523835</v>
+        <v>523604</v>
       </c>
       <c r="R101" t="n">
-        <v>6845199</v>
+        <v>6845013</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,22 +10438,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125736651</v>
+        <v>125755712</v>
       </c>
       <c r="B102" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523722</v>
+        <v>523428</v>
       </c>
       <c r="R102" t="n">
-        <v>6845318</v>
+        <v>6845361</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125734280</v>
+        <v>125755547</v>
       </c>
       <c r="B103" t="n">
-        <v>78967</v>
+        <v>79586</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10558,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523482</v>
+        <v>523479</v>
       </c>
       <c r="R103" t="n">
-        <v>6845199</v>
+        <v>6845112</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,22 +10632,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755712</v>
+        <v>125755620</v>
       </c>
       <c r="B104" t="n">
-        <v>78967</v>
+        <v>78727</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523428</v>
+        <v>523925</v>
       </c>
       <c r="R104" t="n">
-        <v>6845361</v>
+        <v>6845214</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B105" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10772,17 +10772,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R105" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10826,22 +10826,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755547</v>
+        <v>125736651</v>
       </c>
       <c r="B106" t="n">
-        <v>79585</v>
+        <v>78968</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523479</v>
+        <v>523722</v>
       </c>
       <c r="R106" t="n">
-        <v>6845112</v>
+        <v>6845318</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10923,22 +10923,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755620</v>
+        <v>125734280</v>
       </c>
       <c r="B107" t="n">
-        <v>78726</v>
+        <v>78968</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,37 +10946,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523925</v>
+        <v>523482</v>
       </c>
       <c r="R107" t="n">
-        <v>6845214</v>
+        <v>6845199</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11020,12 +11020,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
@@ -11035,7 +11035,7 @@
         <v>125736699</v>
       </c>
       <c r="B108" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11132,7 +11132,7 @@
         <v>125755617</v>
       </c>
       <c r="B109" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11229,7 +11229,7 @@
         <v>125737839</v>
       </c>
       <c r="B110" t="n">
-        <v>79556</v>
+        <v>79557</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11326,7 +11326,7 @@
         <v>125755713</v>
       </c>
       <c r="B111" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>125755706</v>
       </c>
       <c r="B112" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11520,7 +11520,7 @@
         <v>125755651</v>
       </c>
       <c r="B113" t="n">
-        <v>98331</v>
+        <v>98334</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11626,7 +11626,7 @@
         <v>125755635</v>
       </c>
       <c r="B114" t="n">
-        <v>78726</v>
+        <v>78727</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11720,45 +11720,54 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755631</v>
+        <v>125755563</v>
       </c>
       <c r="B115" t="n">
-        <v>78726</v>
+        <v>56843</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523636</v>
+        <v>523483</v>
       </c>
       <c r="R115" t="n">
-        <v>6845388</v>
+        <v>6845365</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11817,10 +11826,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755619</v>
+        <v>125755555</v>
       </c>
       <c r="B116" t="n">
-        <v>78726</v>
+        <v>90266</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11828,21 +11837,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -11852,10 +11861,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523952</v>
+        <v>523480</v>
       </c>
       <c r="R116" t="n">
-        <v>6845185</v>
+        <v>6845111</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11914,50 +11923,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755608</v>
+        <v>125755601</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>92710</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523745</v>
+        <v>523463</v>
       </c>
       <c r="R117" t="n">
-        <v>6845284</v>
+        <v>6845230</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12016,10 +12020,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125736623</v>
+        <v>125755784</v>
       </c>
       <c r="B118" t="n">
-        <v>78967</v>
+        <v>78635</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12027,34 +12031,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523689</v>
+        <v>523606</v>
       </c>
       <c r="R118" t="n">
-        <v>6845339</v>
+        <v>6845378</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12101,66 +12105,57 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755563</v>
+        <v>125755631</v>
       </c>
       <c r="B119" t="n">
-        <v>56843</v>
+        <v>78727</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523483</v>
+        <v>523636</v>
       </c>
       <c r="R119" t="n">
-        <v>6845365</v>
+        <v>6845388</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12219,10 +12214,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125732643</v>
+        <v>125755619</v>
       </c>
       <c r="B120" t="n">
-        <v>79556</v>
+        <v>78727</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12230,34 +12225,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523617</v>
+        <v>523952</v>
       </c>
       <c r="R120" t="n">
-        <v>6845031</v>
+        <v>6845185</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12304,22 +12299,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755555</v>
+        <v>125732643</v>
       </c>
       <c r="B121" t="n">
-        <v>90265</v>
+        <v>79557</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12327,34 +12322,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523480</v>
+        <v>523617</v>
       </c>
       <c r="R121" t="n">
-        <v>6845111</v>
+        <v>6845031</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12401,22 +12396,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755601</v>
+        <v>125736623</v>
       </c>
       <c r="B122" t="n">
-        <v>92707</v>
+        <v>78968</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12424,34 +12419,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523463</v>
+        <v>523689</v>
       </c>
       <c r="R122" t="n">
-        <v>6845230</v>
+        <v>6845339</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12498,57 +12493,62 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755784</v>
+        <v>125755608</v>
       </c>
       <c r="B123" t="n">
-        <v>78634</v>
+        <v>8447</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523606</v>
+        <v>523745</v>
       </c>
       <c r="R123" t="n">
-        <v>6845378</v>
+        <v>6845284</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12610,7 +12610,7 @@
         <v>125732670</v>
       </c>
       <c r="B124" t="n">
-        <v>79585</v>
+        <v>79586</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755704</v>
+        <v>125734818</v>
       </c>
       <c r="B125" t="n">
-        <v>78967</v>
+        <v>91248</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,37 +12715,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523760</v>
+        <v>523643</v>
       </c>
       <c r="R125" t="n">
-        <v>6845283</v>
+        <v>6845282</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12789,22 +12789,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755557</v>
+        <v>125755715</v>
       </c>
       <c r="B126" t="n">
-        <v>91227</v>
+        <v>78968</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523340</v>
+        <v>523450</v>
       </c>
       <c r="R126" t="n">
-        <v>6845392</v>
+        <v>6845349</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755715</v>
+        <v>125755557</v>
       </c>
       <c r="B127" t="n">
-        <v>78967</v>
+        <v>91228</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523450</v>
+        <v>523340</v>
       </c>
       <c r="R127" t="n">
-        <v>6845349</v>
+        <v>6845392</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12998,7 +12998,7 @@
         <v>125755780</v>
       </c>
       <c r="B128" t="n">
-        <v>78634</v>
+        <v>78635</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125734818</v>
+        <v>125755704</v>
       </c>
       <c r="B129" t="n">
-        <v>91247</v>
+        <v>78968</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523643</v>
+        <v>523760</v>
       </c>
       <c r="R129" t="n">
-        <v>6845282</v>
+        <v>6845283</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -1354,48 +1354,52 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125734647</v>
+        <v>125735595</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>98334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523611</v>
+        <v>523492</v>
       </c>
       <c r="R9" t="n">
-        <v>6845275</v>
+        <v>6845165</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,19 +1443,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125736051</v>
+        <v>125755708</v>
       </c>
       <c r="B10" t="n">
         <v>78968</v>
@@ -1482,14 +1486,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523418</v>
+        <v>523626</v>
       </c>
       <c r="R10" t="n">
-        <v>6845349</v>
+        <v>6845380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1540,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755632</v>
+        <v>125755716</v>
       </c>
       <c r="B11" t="n">
-        <v>78727</v>
+        <v>78968</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,21 +1563,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523621</v>
+        <v>523477</v>
       </c>
       <c r="R11" t="n">
-        <v>6845375</v>
+        <v>6845219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1649,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755708</v>
+        <v>125755698</v>
       </c>
       <c r="B12" t="n">
         <v>78968</v>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523626</v>
+        <v>523867</v>
       </c>
       <c r="R12" t="n">
-        <v>6845380</v>
+        <v>6845227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1746,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755716</v>
+        <v>125755711</v>
       </c>
       <c r="B13" t="n">
         <v>78968</v>
@@ -1777,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523477</v>
+        <v>523443</v>
       </c>
       <c r="R13" t="n">
-        <v>6845219</v>
+        <v>6845363</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1843,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755698</v>
+        <v>125734647</v>
       </c>
       <c r="B14" t="n">
         <v>78968</v>
@@ -1870,17 +1874,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523867</v>
+        <v>523611</v>
       </c>
       <c r="R14" t="n">
-        <v>6845227</v>
+        <v>6845275</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,19 +1928,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755711</v>
+        <v>125736051</v>
       </c>
       <c r="B15" t="n">
         <v>78968</v>
@@ -1967,14 +1971,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523443</v>
+        <v>523418</v>
       </c>
       <c r="R15" t="n">
-        <v>6845363</v>
+        <v>6845349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,61 +2025,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125735595</v>
+        <v>125755632</v>
       </c>
       <c r="B16" t="n">
-        <v>98334</v>
+        <v>78727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523492</v>
+        <v>523621</v>
       </c>
       <c r="R16" t="n">
-        <v>6845165</v>
+        <v>6845375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,22 +2122,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755693</v>
+        <v>125755786</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523993</v>
+        <v>523474</v>
       </c>
       <c r="R17" t="n">
-        <v>6845158</v>
+        <v>6845244</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755710</v>
+        <v>125755785</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523572</v>
+        <v>523467</v>
       </c>
       <c r="R18" t="n">
-        <v>6845367</v>
+        <v>6845333</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755786</v>
+        <v>125755693</v>
       </c>
       <c r="B19" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523474</v>
+        <v>523993</v>
       </c>
       <c r="R19" t="n">
-        <v>6845244</v>
+        <v>6845158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755785</v>
+        <v>125755710</v>
       </c>
       <c r="B20" t="n">
-        <v>78635</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,21 +2436,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523467</v>
+        <v>523572</v>
       </c>
       <c r="R20" t="n">
-        <v>6845333</v>
+        <v>6845367</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125735304</v>
+        <v>125755719</v>
       </c>
       <c r="B25" t="n">
         <v>78968</v>
@@ -2951,17 +2951,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523580</v>
+        <v>523554</v>
       </c>
       <c r="R25" t="n">
-        <v>6845417</v>
+        <v>6845068</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3005,22 +3005,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125733851</v>
+        <v>125735304</v>
       </c>
       <c r="B26" t="n">
-        <v>91248</v>
+        <v>78968</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,21 +3028,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523470</v>
+        <v>523580</v>
       </c>
       <c r="R26" t="n">
-        <v>6845106</v>
+        <v>6845417</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125736021</v>
+        <v>125733851</v>
       </c>
       <c r="B27" t="n">
-        <v>79586</v>
+        <v>91248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,37 +3125,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523418</v>
+        <v>523470</v>
       </c>
       <c r="R27" t="n">
-        <v>6845349</v>
+        <v>6845106</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3199,22 +3199,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755719</v>
+        <v>125736021</v>
       </c>
       <c r="B28" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,34 +3222,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523554</v>
+        <v>523418</v>
       </c>
       <c r="R28" t="n">
-        <v>6845068</v>
+        <v>6845349</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3296,12 +3296,12 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755709</v>
+        <v>125755788</v>
       </c>
       <c r="B68" t="n">
-        <v>78968</v>
+        <v>78635</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523598</v>
+        <v>523460</v>
       </c>
       <c r="R68" t="n">
-        <v>6845380</v>
+        <v>6845221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,32 +7212,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755788</v>
+        <v>125755598</v>
       </c>
       <c r="B69" t="n">
-        <v>78635</v>
+        <v>97212</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523460</v>
+        <v>523351</v>
       </c>
       <c r="R69" t="n">
-        <v>6845221</v>
+        <v>6845393</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755761</v>
+        <v>125755709</v>
       </c>
       <c r="B70" t="n">
-        <v>57651</v>
+        <v>78968</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7320,39 +7320,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523387</v>
+        <v>523598</v>
       </c>
       <c r="R70" t="n">
-        <v>6845410</v>
+        <v>6845380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7411,10 +7406,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125733520</v>
+        <v>125755761</v>
       </c>
       <c r="B71" t="n">
-        <v>78968</v>
+        <v>57651</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7422,34 +7417,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523552</v>
+        <v>523387</v>
       </c>
       <c r="R71" t="n">
-        <v>6845072</v>
+        <v>6845410</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,19 +7496,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125733632</v>
+        <v>125733520</v>
       </c>
       <c r="B72" t="n">
         <v>78968</v>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523458</v>
+        <v>523552</v>
       </c>
       <c r="R72" t="n">
-        <v>6845126</v>
+        <v>6845072</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,45 +7605,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755598</v>
+        <v>125733632</v>
       </c>
       <c r="B73" t="n">
-        <v>97212</v>
+        <v>78968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523351</v>
+        <v>523458</v>
       </c>
       <c r="R73" t="n">
-        <v>6845393</v>
+        <v>6845126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,22 +7690,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755629</v>
+        <v>125738012</v>
       </c>
       <c r="B74" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,34 +7713,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523679</v>
+        <v>523967</v>
       </c>
       <c r="R74" t="n">
-        <v>6845347</v>
+        <v>6845175</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,19 +7792,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755630</v>
+        <v>125755629</v>
       </c>
       <c r="B75" t="n">
         <v>78727</v>
@@ -7834,10 +7839,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523671</v>
+        <v>523679</v>
       </c>
       <c r="R75" t="n">
-        <v>6845353</v>
+        <v>6845347</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7896,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125738012</v>
+        <v>125755630</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>78727</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7907,39 +7912,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523967</v>
+        <v>523671</v>
       </c>
       <c r="R76" t="n">
-        <v>6845175</v>
+        <v>6845353</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7986,12 +7986,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125737769</v>
+        <v>125755781</v>
       </c>
       <c r="B97" t="n">
-        <v>79586</v>
+        <v>78635</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523967</v>
+        <v>523958</v>
       </c>
       <c r="R97" t="n">
-        <v>6845175</v>
+        <v>6845195</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10045,62 +10045,57 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755610</v>
+        <v>125737769</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>79586</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523527</v>
+        <v>523967</v>
       </c>
       <c r="R98" t="n">
-        <v>6845375</v>
+        <v>6845175</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,57 +10142,62 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755781</v>
+        <v>125755610</v>
       </c>
       <c r="B99" t="n">
-        <v>78635</v>
+        <v>8447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523958</v>
+        <v>523527</v>
       </c>
       <c r="R99" t="n">
-        <v>6845195</v>
+        <v>6845375</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10353,7 +10353,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B101" t="n">
         <v>79586</v>
@@ -10384,17 +10384,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R101" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,19 +10438,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755712</v>
+        <v>125736651</v>
       </c>
       <c r="B102" t="n">
         <v>78968</v>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523428</v>
+        <v>523722</v>
       </c>
       <c r="R102" t="n">
-        <v>6845361</v>
+        <v>6845318</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755547</v>
+        <v>125734280</v>
       </c>
       <c r="B103" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10558,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523479</v>
+        <v>523482</v>
       </c>
       <c r="R103" t="n">
-        <v>6845112</v>
+        <v>6845199</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,22 +10632,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755620</v>
+        <v>125755550</v>
       </c>
       <c r="B104" t="n">
-        <v>78727</v>
+        <v>79586</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523925</v>
+        <v>523604</v>
       </c>
       <c r="R104" t="n">
-        <v>6845214</v>
+        <v>6845013</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125737335</v>
+        <v>125755712</v>
       </c>
       <c r="B105" t="n">
-        <v>79586</v>
+        <v>78968</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,37 +10752,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523835</v>
+        <v>523428</v>
       </c>
       <c r="R105" t="n">
-        <v>6845199</v>
+        <v>6845361</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10826,22 +10826,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125736651</v>
+        <v>125755547</v>
       </c>
       <c r="B106" t="n">
-        <v>78968</v>
+        <v>79586</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523722</v>
+        <v>523479</v>
       </c>
       <c r="R106" t="n">
-        <v>6845318</v>
+        <v>6845112</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10923,22 +10923,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125734280</v>
+        <v>125755620</v>
       </c>
       <c r="B107" t="n">
-        <v>78968</v>
+        <v>78727</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,37 +10946,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523482</v>
+        <v>523925</v>
       </c>
       <c r="R107" t="n">
-        <v>6845199</v>
+        <v>6845214</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11020,12 +11020,12 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755703</v>
+        <v>125736529</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -706,14 +706,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523783</v>
+        <v>523524</v>
       </c>
       <c r="R2" t="n">
-        <v>6845289</v>
+        <v>6845323</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755705</v>
+        <v>125734228</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523728</v>
+        <v>523467</v>
       </c>
       <c r="R3" t="n">
-        <v>6845268</v>
+        <v>6845121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755643</v>
+        <v>125734476</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>79590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523816</v>
+        <v>523492</v>
       </c>
       <c r="R4" t="n">
-        <v>6845298</v>
+        <v>6845165</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -969,7 +969,7 @@
         <v>125737411</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125734228</v>
+        <v>125755703</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523467</v>
+        <v>523783</v>
       </c>
       <c r="R6" t="n">
-        <v>6845121</v>
+        <v>6845289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734476</v>
+        <v>125755705</v>
       </c>
       <c r="B7" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523492</v>
+        <v>523728</v>
       </c>
       <c r="R7" t="n">
-        <v>6845165</v>
+        <v>6845268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125736529</v>
+        <v>125755643</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523524</v>
+        <v>523816</v>
       </c>
       <c r="R8" t="n">
-        <v>6845323</v>
+        <v>6845298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,61 +1342,57 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125735595</v>
+        <v>125755632</v>
       </c>
       <c r="B9" t="n">
-        <v>98334</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523492</v>
+        <v>523621</v>
       </c>
       <c r="R9" t="n">
-        <v>6845165</v>
+        <v>6845375</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1458,7 +1454,7 @@
         <v>125755708</v>
       </c>
       <c r="B10" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1545,7 +1541,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1555,7 +1551,7 @@
         <v>125755716</v>
       </c>
       <c r="B11" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1642,7 +1638,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1652,7 +1648,7 @@
         <v>125755698</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,7 +1745,7 @@
         <v>125755711</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1836,55 +1832,59 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125734647</v>
+        <v>125735595</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523611</v>
+        <v>523492</v>
       </c>
       <c r="R14" t="n">
-        <v>6845275</v>
+        <v>6845165</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,22 +1928,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125736051</v>
+        <v>125734647</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,17 +1971,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523418</v>
+        <v>523611</v>
       </c>
       <c r="R15" t="n">
-        <v>6845349</v>
+        <v>6845275</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2025,22 +2025,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755632</v>
+        <v>125736051</v>
       </c>
       <c r="B16" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,34 +2048,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523621</v>
+        <v>523418</v>
       </c>
       <c r="R16" t="n">
-        <v>6845375</v>
+        <v>6845349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,22 +2122,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755786</v>
+        <v>125737958</v>
       </c>
       <c r="B17" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523474</v>
+        <v>523967</v>
       </c>
       <c r="R17" t="n">
-        <v>6845244</v>
+        <v>6845175</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755785</v>
+        <v>125755693</v>
       </c>
       <c r="B18" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523467</v>
+        <v>523993</v>
       </c>
       <c r="R18" t="n">
-        <v>6845333</v>
+        <v>6845158</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755693</v>
+        <v>125755710</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523993</v>
+        <v>523572</v>
       </c>
       <c r="R19" t="n">
-        <v>6845158</v>
+        <v>6845367</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,17 +2418,17 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755710</v>
+        <v>125733598</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,17 +2456,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523572</v>
+        <v>523483</v>
       </c>
       <c r="R20" t="n">
-        <v>6845367</v>
+        <v>6845118</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2510,22 +2510,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125733598</v>
+        <v>125755786</v>
       </c>
       <c r="B21" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,37 +2533,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523483</v>
+        <v>523474</v>
       </c>
       <c r="R21" t="n">
-        <v>6845118</v>
+        <v>6845244</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125737958</v>
+        <v>125755785</v>
       </c>
       <c r="B22" t="n">
-        <v>78727</v>
+        <v>78639</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,21 +2630,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523967</v>
+        <v>523467</v>
       </c>
       <c r="R22" t="n">
-        <v>6845175</v>
+        <v>6845333</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2704,22 +2704,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755790</v>
+        <v>125755593</v>
       </c>
       <c r="B23" t="n">
-        <v>78635</v>
+        <v>57651</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,34 +2727,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523486</v>
+        <v>523520</v>
       </c>
       <c r="R23" t="n">
-        <v>6845100</v>
+        <v>6845094</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2787,6 +2792,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2813,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755593</v>
+        <v>125755790</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,39 +2834,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523520</v>
+        <v>523486</v>
       </c>
       <c r="R24" t="n">
-        <v>6845094</v>
+        <v>6845100</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2889,11 +2894,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2923,7 +2923,7 @@
         <v>125755719</v>
       </c>
       <c r="B25" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3010,17 +3010,17 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125735304</v>
+        <v>125736021</v>
       </c>
       <c r="B26" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,37 +3028,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523580</v>
+        <v>523418</v>
       </c>
       <c r="R26" t="n">
-        <v>6845417</v>
+        <v>6845349</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3102,22 +3102,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125733851</v>
+        <v>125735304</v>
       </c>
       <c r="B27" t="n">
-        <v>91248</v>
+        <v>78972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523470</v>
+        <v>523580</v>
       </c>
       <c r="R27" t="n">
-        <v>6845106</v>
+        <v>6845417</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125736021</v>
+        <v>125733851</v>
       </c>
       <c r="B28" t="n">
-        <v>79586</v>
+        <v>91252</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,37 +3222,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523418</v>
+        <v>523470</v>
       </c>
       <c r="R28" t="n">
-        <v>6845349</v>
+        <v>6845106</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3296,57 +3296,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125733581</v>
+        <v>125755657</v>
       </c>
       <c r="B29" t="n">
-        <v>78968</v>
+        <v>91393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523528</v>
+        <v>523463</v>
       </c>
       <c r="R29" t="n">
-        <v>6845135</v>
+        <v>6845211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125737629</v>
+        <v>125755545</v>
       </c>
       <c r="B30" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523960</v>
+        <v>523465</v>
       </c>
       <c r="R30" t="n">
-        <v>6845161</v>
+        <v>6845109</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,22 +3490,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755545</v>
+        <v>125755549</v>
       </c>
       <c r="B31" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523465</v>
+        <v>523541</v>
       </c>
       <c r="R31" t="n">
-        <v>6845109</v>
+        <v>6845054</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755549</v>
+        <v>125755634</v>
       </c>
       <c r="B32" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523541</v>
+        <v>523498</v>
       </c>
       <c r="R32" t="n">
-        <v>6845054</v>
+        <v>6845404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,45 +3696,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755657</v>
+        <v>125733581</v>
       </c>
       <c r="B33" t="n">
-        <v>91389</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523463</v>
+        <v>523528</v>
       </c>
       <c r="R33" t="n">
-        <v>6845211</v>
+        <v>6845135</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,22 +3781,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755634</v>
+        <v>125737629</v>
       </c>
       <c r="B34" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523498</v>
+        <v>523960</v>
       </c>
       <c r="R34" t="n">
-        <v>6845404</v>
+        <v>6845161</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3878,12 +3878,12 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -3893,7 +3893,7 @@
         <v>125735113</v>
       </c>
       <c r="B35" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>125755625</v>
       </c>
       <c r="B36" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>125755695</v>
       </c>
       <c r="B37" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125755565</v>
       </c>
       <c r="B38" t="n">
-        <v>91248</v>
+        <v>91252</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>125755787</v>
       </c>
       <c r="B39" t="n">
-        <v>78635</v>
+        <v>78639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4375,10 +4375,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B40" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R40" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125734860</v>
+        <v>125755544</v>
       </c>
       <c r="B41" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523673</v>
+        <v>523483</v>
       </c>
       <c r="R41" t="n">
-        <v>6845294</v>
+        <v>6845181</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4557,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734662</v>
+        <v>125734860</v>
       </c>
       <c r="B42" t="n">
-        <v>78726</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523492</v>
+        <v>523673</v>
       </c>
       <c r="R42" t="n">
-        <v>6845165</v>
+        <v>6845294</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755539</v>
+        <v>125734662</v>
       </c>
       <c r="B43" t="n">
-        <v>79586</v>
+        <v>78730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,34 +4677,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523924</v>
+        <v>523492</v>
       </c>
       <c r="R43" t="n">
-        <v>6845215</v>
+        <v>6845165</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B44" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,37 +4774,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R44" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4848,44 +4848,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755626</v>
+        <v>125755658</v>
       </c>
       <c r="B45" t="n">
-        <v>78727</v>
+        <v>91393</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4895,10 +4895,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523759</v>
+        <v>523487</v>
       </c>
       <c r="R45" t="n">
-        <v>6845238</v>
+        <v>6845098</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4957,10 +4957,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125737014</v>
+        <v>125755792</v>
       </c>
       <c r="B46" t="n">
-        <v>78727</v>
+        <v>92516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523854</v>
+        <v>523992</v>
       </c>
       <c r="R46" t="n">
-        <v>6845289</v>
+        <v>6845170</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5028,6 +5028,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5042,44 +5047,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755792</v>
+        <v>125755552</v>
       </c>
       <c r="B47" t="n">
-        <v>92512</v>
+        <v>91197</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5089,10 +5094,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523992</v>
+        <v>523424</v>
       </c>
       <c r="R47" t="n">
-        <v>6845170</v>
+        <v>6845383</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5125,11 +5130,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5159,7 +5159,7 @@
         <v>125755717</v>
       </c>
       <c r="B48" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5246,55 +5246,55 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755552</v>
+        <v>125737014</v>
       </c>
       <c r="B49" t="n">
-        <v>91193</v>
+        <v>78731</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523424</v>
+        <v>523854</v>
       </c>
       <c r="R49" t="n">
-        <v>6845383</v>
+        <v>6845289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5338,60 +5338,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755658</v>
+        <v>125735128</v>
       </c>
       <c r="B50" t="n">
-        <v>91389</v>
+        <v>79590</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523487</v>
+        <v>523627</v>
       </c>
       <c r="R50" t="n">
-        <v>6845098</v>
+        <v>6845420</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5435,22 +5435,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125735128</v>
+        <v>125736099</v>
       </c>
       <c r="B51" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5458,37 +5458,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523627</v>
+        <v>523514</v>
       </c>
       <c r="R51" t="n">
-        <v>6845420</v>
+        <v>6845340</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,22 +5532,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125736099</v>
+        <v>125734241</v>
       </c>
       <c r="B52" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523514</v>
+        <v>523492</v>
       </c>
       <c r="R52" t="n">
-        <v>6845340</v>
+        <v>6845165</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,10 +5641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125734241</v>
+        <v>125755626</v>
       </c>
       <c r="B53" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5652,34 +5652,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523492</v>
+        <v>523759</v>
       </c>
       <c r="R53" t="n">
-        <v>6845165</v>
+        <v>6845238</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5726,57 +5726,67 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125732709</v>
+        <v>125736061</v>
       </c>
       <c r="B54" t="n">
-        <v>78727</v>
+        <v>56843</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523548</v>
+        <v>523643</v>
       </c>
       <c r="R54" t="n">
-        <v>6845076</v>
+        <v>6845391</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -5835,58 +5845,48 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125736061</v>
+        <v>125755636</v>
       </c>
       <c r="B55" t="n">
-        <v>56843</v>
+        <v>78731</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523643</v>
+        <v>523511</v>
       </c>
       <c r="R55" t="n">
-        <v>6845391</v>
+        <v>6845102</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5930,22 +5930,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755542</v>
+        <v>125755627</v>
       </c>
       <c r="B56" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523670</v>
+        <v>523755</v>
       </c>
       <c r="R56" t="n">
-        <v>6845353</v>
+        <v>6845251</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6039,10 +6039,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755543</v>
+        <v>125755628</v>
       </c>
       <c r="B57" t="n">
-        <v>79586</v>
+        <v>78731</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523460</v>
+        <v>523728</v>
       </c>
       <c r="R57" t="n">
-        <v>6845221</v>
+        <v>6845279</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755636</v>
+        <v>125755542</v>
       </c>
       <c r="B58" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523511</v>
+        <v>523670</v>
       </c>
       <c r="R58" t="n">
-        <v>6845102</v>
+        <v>6845353</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755628</v>
+        <v>125755543</v>
       </c>
       <c r="B59" t="n">
-        <v>78727</v>
+        <v>79590</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523728</v>
+        <v>523460</v>
       </c>
       <c r="R59" t="n">
-        <v>6845279</v>
+        <v>6845221</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755627</v>
+        <v>125732709</v>
       </c>
       <c r="B60" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523755</v>
+        <v>523548</v>
       </c>
       <c r="R60" t="n">
-        <v>6845251</v>
+        <v>6845076</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,12 +6415,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6430,7 +6430,7 @@
         <v>125736672</v>
       </c>
       <c r="B61" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6524,32 +6524,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125735892</v>
+        <v>125735337</v>
       </c>
       <c r="B62" t="n">
-        <v>92518</v>
+        <v>78731</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6559,10 +6559,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523608</v>
+        <v>523593</v>
       </c>
       <c r="R62" t="n">
-        <v>6845376</v>
+        <v>6845417</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6621,54 +6621,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755647</v>
+        <v>125734655</v>
       </c>
       <c r="B63" t="n">
-        <v>98334</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523408</v>
+        <v>523492</v>
       </c>
       <c r="R63" t="n">
-        <v>6845401</v>
+        <v>6845165</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6715,22 +6706,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125735337</v>
+        <v>125734972</v>
       </c>
       <c r="B64" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6762,10 +6753,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523593</v>
+        <v>523675</v>
       </c>
       <c r="R64" t="n">
-        <v>6845417</v>
+        <v>6845339</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6824,48 +6815,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734655</v>
+        <v>125735892</v>
       </c>
       <c r="B65" t="n">
-        <v>78727</v>
+        <v>92522</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523492</v>
+        <v>523608</v>
       </c>
       <c r="R65" t="n">
-        <v>6845165</v>
+        <v>6845376</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6909,60 +6900,69 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125734972</v>
+        <v>125755647</v>
       </c>
       <c r="B66" t="n">
-        <v>78727</v>
+        <v>98338</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523675</v>
+        <v>523408</v>
       </c>
       <c r="R66" t="n">
-        <v>6845339</v>
+        <v>6845401</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,12 +7006,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7021,7 +7021,7 @@
         <v>125734739</v>
       </c>
       <c r="B67" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7115,32 +7115,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755788</v>
+        <v>125755598</v>
       </c>
       <c r="B68" t="n">
-        <v>78635</v>
+        <v>97216</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>221945</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523460</v>
+        <v>523351</v>
       </c>
       <c r="R68" t="n">
-        <v>6845221</v>
+        <v>6845393</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,45 +7212,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755598</v>
+        <v>125733520</v>
       </c>
       <c r="B69" t="n">
-        <v>97212</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523351</v>
+        <v>523552</v>
       </c>
       <c r="R69" t="n">
-        <v>6845393</v>
+        <v>6845072</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7297,22 +7297,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755709</v>
+        <v>125733632</v>
       </c>
       <c r="B70" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7340,14 +7340,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523598</v>
+        <v>523458</v>
       </c>
       <c r="R70" t="n">
-        <v>6845380</v>
+        <v>6845126</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7394,19 +7394,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755761</v>
+        <v>125738012</v>
       </c>
       <c r="B71" t="n">
         <v>57651</v>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523387</v>
+        <v>523967</v>
       </c>
       <c r="R71" t="n">
-        <v>6845410</v>
+        <v>6845175</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125733520</v>
+        <v>125755788</v>
       </c>
       <c r="B72" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,34 +7519,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523552</v>
+        <v>523460</v>
       </c>
       <c r="R72" t="n">
-        <v>6845072</v>
+        <v>6845221</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,22 +7593,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125733632</v>
+        <v>125755709</v>
       </c>
       <c r="B73" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7636,14 +7636,14 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523458</v>
+        <v>523598</v>
       </c>
       <c r="R73" t="n">
-        <v>6845126</v>
+        <v>6845380</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,22 +7690,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125738012</v>
+        <v>125755630</v>
       </c>
       <c r="B74" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,39 +7713,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523967</v>
+        <v>523671</v>
       </c>
       <c r="R74" t="n">
-        <v>6845175</v>
+        <v>6845353</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7792,12 +7787,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7807,7 +7802,7 @@
         <v>125755629</v>
       </c>
       <c r="B75" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7901,10 +7896,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755630</v>
+        <v>125755761</v>
       </c>
       <c r="B76" t="n">
-        <v>78727</v>
+        <v>57651</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,34 +7907,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523671</v>
+        <v>523387</v>
       </c>
       <c r="R76" t="n">
-        <v>6845353</v>
+        <v>6845410</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7991,52 +7991,56 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755701</v>
+        <v>125735686</v>
       </c>
       <c r="B77" t="n">
-        <v>78968</v>
+        <v>98338</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523839</v>
+        <v>523418</v>
       </c>
       <c r="R77" t="n">
-        <v>6845286</v>
+        <v>6845349</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8083,22 +8087,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755707</v>
+        <v>125755701</v>
       </c>
       <c r="B78" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8130,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523644</v>
+        <v>523839</v>
       </c>
       <c r="R78" t="n">
-        <v>6845389</v>
+        <v>6845286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8192,10 +8196,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755541</v>
+        <v>125755707</v>
       </c>
       <c r="B79" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8203,21 +8207,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8227,10 +8231,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523757</v>
+        <v>523644</v>
       </c>
       <c r="R79" t="n">
-        <v>6845248</v>
+        <v>6845389</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8282,7 +8286,7 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8292,7 +8296,7 @@
         <v>125755794</v>
       </c>
       <c r="B80" t="n">
-        <v>91638</v>
+        <v>91642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8394,7 +8398,7 @@
         <v>125755714</v>
       </c>
       <c r="B81" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8481,56 +8485,52 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125735686</v>
+        <v>125755541</v>
       </c>
       <c r="B82" t="n">
-        <v>98334</v>
+        <v>79590</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523418</v>
+        <v>523757</v>
       </c>
       <c r="R82" t="n">
-        <v>6845349</v>
+        <v>6845248</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,22 +8577,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755702</v>
+        <v>125737510</v>
       </c>
       <c r="B83" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,37 +8600,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523829</v>
+        <v>523957</v>
       </c>
       <c r="R83" t="n">
-        <v>6845308</v>
+        <v>6845190</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,22 +8674,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755789</v>
+        <v>125755702</v>
       </c>
       <c r="B84" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523480</v>
+        <v>523829</v>
       </c>
       <c r="R84" t="n">
-        <v>6845112</v>
+        <v>6845308</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8776,17 +8776,17 @@
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125732736</v>
+        <v>125755789</v>
       </c>
       <c r="B85" t="n">
-        <v>78726</v>
+        <v>78639</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,37 +8794,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523551</v>
+        <v>523480</v>
       </c>
       <c r="R85" t="n">
-        <v>6845080</v>
+        <v>6845112</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8868,22 +8868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755621</v>
+        <v>125732736</v>
       </c>
       <c r="B86" t="n">
-        <v>78727</v>
+        <v>78730</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523920</v>
+        <v>523551</v>
       </c>
       <c r="R86" t="n">
-        <v>6845217</v>
+        <v>6845080</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125737510</v>
+        <v>125755621</v>
       </c>
       <c r="B87" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9008,17 +9008,17 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523957</v>
+        <v>523920</v>
       </c>
       <c r="R87" t="n">
-        <v>6845190</v>
+        <v>6845217</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,22 +9062,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755700</v>
+        <v>125755783</v>
       </c>
       <c r="B88" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9085,21 +9085,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523859</v>
+        <v>523644</v>
       </c>
       <c r="R88" t="n">
-        <v>6845221</v>
+        <v>6845379</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,10 +9171,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755697</v>
+        <v>125755700</v>
       </c>
       <c r="B89" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523948</v>
+        <v>523859</v>
       </c>
       <c r="R89" t="n">
-        <v>6845177</v>
+        <v>6845221</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755775</v>
+        <v>125755697</v>
       </c>
       <c r="B90" t="n">
-        <v>92518</v>
+        <v>78972</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523541</v>
+        <v>523948</v>
       </c>
       <c r="R90" t="n">
-        <v>6845044</v>
+        <v>6845177</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,32 +9365,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755783</v>
+        <v>125755775</v>
       </c>
       <c r="B91" t="n">
-        <v>78635</v>
+        <v>92522</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9400,10 +9400,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523644</v>
+        <v>523541</v>
       </c>
       <c r="R91" t="n">
-        <v>6845379</v>
+        <v>6845044</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9455,56 +9455,61 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125732728</v>
+        <v>125755654</v>
       </c>
       <c r="B92" t="n">
-        <v>92518</v>
+        <v>98338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523590</v>
+        <v>523428</v>
       </c>
       <c r="R92" t="n">
-        <v>6845030</v>
+        <v>6845361</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9551,66 +9556,57 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755654</v>
+        <v>125755553</v>
       </c>
       <c r="B93" t="n">
-        <v>98334</v>
+        <v>79561</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523428</v>
+        <v>523626</v>
       </c>
       <c r="R93" t="n">
-        <v>6845361</v>
+        <v>6845383</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9669,45 +9665,49 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755553</v>
+        <v>125732728</v>
       </c>
       <c r="B94" t="n">
-        <v>79557</v>
+        <v>92522</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523626</v>
+        <v>523590</v>
       </c>
       <c r="R94" t="n">
-        <v>6845383</v>
+        <v>6845030</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,44 +9754,44 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755774</v>
+        <v>125737769</v>
       </c>
       <c r="B95" t="n">
-        <v>92518</v>
+        <v>79590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523526</v>
+        <v>523967</v>
       </c>
       <c r="R95" t="n">
-        <v>6845095</v>
+        <v>6845175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,22 +9851,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755694</v>
+        <v>125755781</v>
       </c>
       <c r="B96" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523979</v>
+        <v>523958</v>
       </c>
       <c r="R96" t="n">
-        <v>6845154</v>
+        <v>6845195</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9960,32 +9960,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755781</v>
+        <v>125755774</v>
       </c>
       <c r="B97" t="n">
-        <v>78635</v>
+        <v>92522</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523958</v>
+        <v>523526</v>
       </c>
       <c r="R97" t="n">
-        <v>6845195</v>
+        <v>6845095</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,17 +10050,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125737769</v>
+        <v>125755694</v>
       </c>
       <c r="B98" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10068,21 +10068,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523967</v>
+        <v>523979</v>
       </c>
       <c r="R98" t="n">
-        <v>6845175</v>
+        <v>6845154</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10142,12 +10142,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10259,7 +10259,7 @@
         <v>125755624</v>
       </c>
       <c r="B100" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125737335</v>
+        <v>125736651</v>
       </c>
       <c r="B101" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10364,37 +10364,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523835</v>
+        <v>523722</v>
       </c>
       <c r="R101" t="n">
-        <v>6845199</v>
+        <v>6845318</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,22 +10438,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125736651</v>
+        <v>125737335</v>
       </c>
       <c r="B102" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,37 +10461,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523722</v>
+        <v>523835</v>
       </c>
       <c r="R102" t="n">
-        <v>6845318</v>
+        <v>6845199</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10535,12 +10535,12 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
         <v>125734280</v>
       </c>
       <c r="B103" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>125755550</v>
       </c>
       <c r="B104" t="n">
-        <v>79586</v>
+        <v>79590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10741,10 +10741,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755712</v>
+        <v>125755547</v>
       </c>
       <c r="B105" t="n">
-        <v>78968</v>
+        <v>79590</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523428</v>
+        <v>523479</v>
       </c>
       <c r="R105" t="n">
-        <v>6845361</v>
+        <v>6845112</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755547</v>
+        <v>125755712</v>
       </c>
       <c r="B106" t="n">
-        <v>79586</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523479</v>
+        <v>523428</v>
       </c>
       <c r="R106" t="n">
-        <v>6845112</v>
+        <v>6845361</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -10938,7 +10938,7 @@
         <v>125755620</v>
       </c>
       <c r="B107" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11032,10 +11032,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125736699</v>
+        <v>125755713</v>
       </c>
       <c r="B108" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523766</v>
+        <v>523332</v>
       </c>
       <c r="R108" t="n">
-        <v>6845303</v>
+        <v>6845377</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,22 +11117,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755617</v>
+        <v>125755706</v>
       </c>
       <c r="B109" t="n">
-        <v>78727</v>
+        <v>78972</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523972</v>
+        <v>523655</v>
       </c>
       <c r="R109" t="n">
-        <v>6845173</v>
+        <v>6845374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -11229,7 +11229,7 @@
         <v>125737839</v>
       </c>
       <c r="B110" t="n">
-        <v>79557</v>
+        <v>79561</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11323,10 +11323,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755713</v>
+        <v>125736699</v>
       </c>
       <c r="B111" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523332</v>
+        <v>523766</v>
       </c>
       <c r="R111" t="n">
-        <v>6845377</v>
+        <v>6845303</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,22 +11408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755706</v>
+        <v>125755617</v>
       </c>
       <c r="B112" t="n">
-        <v>78968</v>
+        <v>78731</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523655</v>
+        <v>523972</v>
       </c>
       <c r="R112" t="n">
-        <v>6845374</v>
+        <v>6845173</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11517,54 +11517,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B113" t="n">
-        <v>98334</v>
+        <v>78731</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R113" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11623,45 +11614,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B114" t="n">
-        <v>78727</v>
+        <v>98338</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R114" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11720,54 +11720,45 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755563</v>
+        <v>125732643</v>
       </c>
       <c r="B115" t="n">
-        <v>56843</v>
+        <v>79561</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L115" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523483</v>
+        <v>523617</v>
       </c>
       <c r="R115" t="n">
-        <v>6845365</v>
+        <v>6845031</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11814,22 +11805,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755555</v>
+        <v>125736623</v>
       </c>
       <c r="B116" t="n">
-        <v>90266</v>
+        <v>78972</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11837,34 +11828,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523480</v>
+        <v>523689</v>
       </c>
       <c r="R116" t="n">
-        <v>6845111</v>
+        <v>6845339</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11911,57 +11902,62 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755601</v>
+        <v>125755608</v>
       </c>
       <c r="B117" t="n">
-        <v>92710</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>2079</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523463</v>
+        <v>523745</v>
       </c>
       <c r="R117" t="n">
-        <v>6845230</v>
+        <v>6845284</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12020,10 +12016,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755784</v>
+        <v>125755619</v>
       </c>
       <c r="B118" t="n">
-        <v>78635</v>
+        <v>78731</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12031,21 +12027,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12055,10 +12051,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523606</v>
+        <v>523952</v>
       </c>
       <c r="R118" t="n">
-        <v>6845378</v>
+        <v>6845185</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12120,7 +12116,7 @@
         <v>125755631</v>
       </c>
       <c r="B119" t="n">
-        <v>78727</v>
+        <v>78731</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12214,10 +12210,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755619</v>
+        <v>125755555</v>
       </c>
       <c r="B120" t="n">
-        <v>78727</v>
+        <v>90270</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12225,21 +12221,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12249,10 +12245,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523952</v>
+        <v>523480</v>
       </c>
       <c r="R120" t="n">
-        <v>6845185</v>
+        <v>6845111</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12311,10 +12307,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125732643</v>
+        <v>125755601</v>
       </c>
       <c r="B121" t="n">
-        <v>79557</v>
+        <v>92714</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12322,34 +12318,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229821</v>
+        <v>2079</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523617</v>
+        <v>523463</v>
       </c>
       <c r="R121" t="n">
-        <v>6845031</v>
+        <v>6845230</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12396,22 +12392,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125736623</v>
+        <v>125755784</v>
       </c>
       <c r="B122" t="n">
-        <v>78968</v>
+        <v>78639</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12419,34 +12415,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523689</v>
+        <v>523606</v>
       </c>
       <c r="R122" t="n">
-        <v>6845339</v>
+        <v>6845378</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12493,22 +12489,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755608</v>
+        <v>125755563</v>
       </c>
       <c r="B123" t="n">
-        <v>8447</v>
+        <v>56843</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12516,27 +12512,31 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>hane</t>
         </is>
       </c>
       <c r="P123" t="inlineStr">
@@ -12545,10 +12545,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523745</v>
+        <v>523483</v>
       </c>
       <c r="R123" t="n">
-        <v>6845284</v>
+        <v>6845365</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125732670</v>
+        <v>125734818</v>
       </c>
       <c r="B124" t="n">
-        <v>79586</v>
+        <v>91252</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,37 +12618,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523617</v>
+        <v>523643</v>
       </c>
       <c r="R124" t="n">
-        <v>6845031</v>
+        <v>6845282</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125734818</v>
+        <v>125732670</v>
       </c>
       <c r="B125" t="n">
-        <v>91248</v>
+        <v>79590</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,37 +12715,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R125" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12789,22 +12789,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755715</v>
+        <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>78968</v>
+        <v>91232</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523450</v>
+        <v>523340</v>
       </c>
       <c r="R126" t="n">
-        <v>6845349</v>
+        <v>6845392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755557</v>
+        <v>125755780</v>
       </c>
       <c r="B127" t="n">
-        <v>91228</v>
+        <v>78639</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523340</v>
+        <v>523584</v>
       </c>
       <c r="R127" t="n">
-        <v>6845392</v>
+        <v>6845361</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755780</v>
+        <v>125755704</v>
       </c>
       <c r="B128" t="n">
-        <v>78635</v>
+        <v>78972</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523584</v>
+        <v>523760</v>
       </c>
       <c r="R128" t="n">
-        <v>6845361</v>
+        <v>6845283</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13085,17 +13085,17 @@
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125755704</v>
+        <v>125755715</v>
       </c>
       <c r="B129" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13127,10 +13127,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523760</v>
+        <v>523450</v>
       </c>
       <c r="R129" t="n">
-        <v>6845283</v>
+        <v>6845349</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13182,7 +13182,7 @@
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755787</v>
+        <v>125734860</v>
       </c>
       <c r="B39" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,37 +4289,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523457</v>
+        <v>523673</v>
       </c>
       <c r="R39" t="n">
-        <v>6845237</v>
+        <v>6845294</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755539</v>
+        <v>125734662</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,34 +4386,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523924</v>
+        <v>523492</v>
       </c>
       <c r="R40" t="n">
-        <v>6845215</v>
+        <v>6845165</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R41" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4557,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734860</v>
+        <v>125755787</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523673</v>
+        <v>523457</v>
       </c>
       <c r="R42" t="n">
-        <v>6845294</v>
+        <v>6845237</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125734662</v>
+        <v>125755539</v>
       </c>
       <c r="B43" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,34 +4677,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523492</v>
+        <v>523924</v>
       </c>
       <c r="R43" t="n">
-        <v>6845165</v>
+        <v>6845215</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125735540</v>
+        <v>125755544</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,37 +4774,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523479</v>
+        <v>523483</v>
       </c>
       <c r="R44" t="n">
-        <v>6845406</v>
+        <v>6845181</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4848,60 +4848,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755658</v>
+        <v>125735128</v>
       </c>
       <c r="B45" t="n">
-        <v>91393</v>
+        <v>79590</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523487</v>
+        <v>523627</v>
       </c>
       <c r="R45" t="n">
-        <v>6845098</v>
+        <v>6845420</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755792</v>
+        <v>125736099</v>
       </c>
       <c r="B46" t="n">
-        <v>92516</v>
+        <v>78972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,34 +4968,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523992</v>
+        <v>523514</v>
       </c>
       <c r="R46" t="n">
-        <v>6845170</v>
+        <v>6845340</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5030,11 +5030,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5047,57 +5042,57 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755552</v>
+        <v>125734241</v>
       </c>
       <c r="B47" t="n">
-        <v>91197</v>
+        <v>78972</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523424</v>
+        <v>523492</v>
       </c>
       <c r="R47" t="n">
-        <v>6845383</v>
+        <v>6845165</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,44 +5139,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755717</v>
+        <v>125755658</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5191,10 +5186,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523466</v>
+        <v>523487</v>
       </c>
       <c r="R48" t="n">
-        <v>6845180</v>
+        <v>6845098</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5246,17 +5241,17 @@
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125737014</v>
+        <v>125755792</v>
       </c>
       <c r="B49" t="n">
-        <v>78731</v>
+        <v>92516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,37 +5259,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523854</v>
+        <v>523992</v>
       </c>
       <c r="R49" t="n">
-        <v>6845289</v>
+        <v>6845170</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5324,6 +5319,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5338,60 +5338,60 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125735128</v>
+        <v>125755552</v>
       </c>
       <c r="B50" t="n">
-        <v>79590</v>
+        <v>91197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523627</v>
+        <v>523424</v>
       </c>
       <c r="R50" t="n">
-        <v>6845420</v>
+        <v>6845383</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5435,19 +5435,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125736099</v>
+        <v>125755717</v>
       </c>
       <c r="B51" t="n">
         <v>78972</v>
@@ -5478,14 +5478,14 @@
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523514</v>
+        <v>523466</v>
       </c>
       <c r="R51" t="n">
-        <v>6845340</v>
+        <v>6845180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5532,22 +5532,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125734241</v>
+        <v>125737014</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5555,37 +5555,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523492</v>
+        <v>523854</v>
       </c>
       <c r="R52" t="n">
-        <v>6845165</v>
+        <v>6845289</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5629,12 +5629,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125737510</v>
+        <v>125732736</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>78730</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523957</v>
+        <v>523551</v>
       </c>
       <c r="R83" t="n">
-        <v>6845190</v>
+        <v>6845080</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755702</v>
+        <v>125737510</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8697,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523829</v>
+        <v>523957</v>
       </c>
       <c r="R84" t="n">
-        <v>6845308</v>
+        <v>6845190</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8771,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755789</v>
+        <v>125755621</v>
       </c>
       <c r="B85" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523480</v>
+        <v>523920</v>
       </c>
       <c r="R85" t="n">
-        <v>6845112</v>
+        <v>6845217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125732736</v>
+        <v>125755789</v>
       </c>
       <c r="B86" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523551</v>
+        <v>523480</v>
       </c>
       <c r="R86" t="n">
-        <v>6845080</v>
+        <v>6845112</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755621</v>
+        <v>125755702</v>
       </c>
       <c r="B87" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523920</v>
+        <v>523829</v>
       </c>
       <c r="R87" t="n">
-        <v>6845217</v>
+        <v>6845308</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9067,7 +9067,7 @@
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125737335</v>
+        <v>125755712</v>
       </c>
       <c r="B102" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,37 +10461,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523835</v>
+        <v>523428</v>
       </c>
       <c r="R102" t="n">
-        <v>6845199</v>
+        <v>6845361</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125734280</v>
+        <v>125737335</v>
       </c>
       <c r="B103" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,21 +10558,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523482</v>
+        <v>523835</v>
       </c>
       <c r="R103" t="n">
         <v>6845199</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755550</v>
+        <v>125734280</v>
       </c>
       <c r="B104" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,37 +10655,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523604</v>
+        <v>523482</v>
       </c>
       <c r="R104" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10729,22 +10729,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755547</v>
+        <v>125755620</v>
       </c>
       <c r="B105" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523479</v>
+        <v>523925</v>
       </c>
       <c r="R105" t="n">
-        <v>6845112</v>
+        <v>6845214</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755712</v>
+        <v>125755550</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523428</v>
+        <v>523604</v>
       </c>
       <c r="R106" t="n">
-        <v>6845361</v>
+        <v>6845013</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10928,17 +10928,17 @@
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755620</v>
+        <v>125755547</v>
       </c>
       <c r="B107" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,21 +10946,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10970,10 +10970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523925</v>
+        <v>523479</v>
       </c>
       <c r="R107" t="n">
-        <v>6845214</v>
+        <v>6845112</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125734818</v>
+        <v>125755557</v>
       </c>
       <c r="B124" t="n">
-        <v>91252</v>
+        <v>91232</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,37 +12618,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523643</v>
+        <v>523340</v>
       </c>
       <c r="R124" t="n">
-        <v>6845282</v>
+        <v>6845392</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125732670</v>
+        <v>125755780</v>
       </c>
       <c r="B125" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,34 +12715,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523617</v>
+        <v>523584</v>
       </c>
       <c r="R125" t="n">
-        <v>6845031</v>
+        <v>6845361</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12789,22 +12789,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755557</v>
+        <v>125755704</v>
       </c>
       <c r="B126" t="n">
-        <v>91232</v>
+        <v>78972</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523340</v>
+        <v>523760</v>
       </c>
       <c r="R126" t="n">
-        <v>6845392</v>
+        <v>6845283</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12891,17 +12891,17 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755780</v>
+        <v>125755715</v>
       </c>
       <c r="B127" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523584</v>
+        <v>523450</v>
       </c>
       <c r="R127" t="n">
-        <v>6845361</v>
+        <v>6845349</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12988,17 +12988,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755704</v>
+        <v>125734818</v>
       </c>
       <c r="B128" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523760</v>
+        <v>523643</v>
       </c>
       <c r="R128" t="n">
-        <v>6845283</v>
+        <v>6845282</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125755715</v>
+        <v>125732670</v>
       </c>
       <c r="B129" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,34 +13103,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523450</v>
+        <v>523617</v>
       </c>
       <c r="R129" t="n">
-        <v>6845349</v>
+        <v>6845031</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125736529</v>
+        <v>125755643</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523524</v>
+        <v>523816</v>
       </c>
       <c r="R2" t="n">
-        <v>6845323</v>
+        <v>6845298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125734228</v>
+        <v>125755703</v>
       </c>
       <c r="B3" t="n">
         <v>78972</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523467</v>
+        <v>523783</v>
       </c>
       <c r="R3" t="n">
-        <v>6845121</v>
+        <v>6845289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125734476</v>
+        <v>125755705</v>
       </c>
       <c r="B4" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523492</v>
+        <v>523728</v>
       </c>
       <c r="R4" t="n">
-        <v>6845165</v>
+        <v>6845268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755703</v>
+        <v>125734228</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523783</v>
+        <v>523467</v>
       </c>
       <c r="R6" t="n">
-        <v>6845289</v>
+        <v>6845121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755705</v>
+        <v>125734476</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523728</v>
+        <v>523492</v>
       </c>
       <c r="R7" t="n">
-        <v>6845268</v>
+        <v>6845165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755643</v>
+        <v>125736529</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523816</v>
+        <v>523524</v>
       </c>
       <c r="R8" t="n">
-        <v>6845298</v>
+        <v>6845323</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,22 +1342,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755632</v>
+        <v>125755708</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523621</v>
+        <v>523626</v>
       </c>
       <c r="R9" t="n">
-        <v>6845375</v>
+        <v>6845380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755708</v>
+        <v>125755716</v>
       </c>
       <c r="B10" t="n">
         <v>78972</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523626</v>
+        <v>523477</v>
       </c>
       <c r="R10" t="n">
-        <v>6845380</v>
+        <v>6845219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,14 +1541,14 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B11" t="n">
         <v>78972</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R11" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1638,14 +1638,14 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755698</v>
+        <v>125755711</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523867</v>
+        <v>523443</v>
       </c>
       <c r="R12" t="n">
-        <v>6845227</v>
+        <v>6845363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755711</v>
+        <v>125734647</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1773,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523443</v>
+        <v>523611</v>
       </c>
       <c r="R13" t="n">
-        <v>6845363</v>
+        <v>6845275</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,61 +1827,57 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B14" t="n">
-        <v>98338</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R14" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125734647</v>
+        <v>125755632</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1951,37 +1947,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523611</v>
+        <v>523621</v>
       </c>
       <c r="R15" t="n">
-        <v>6845275</v>
+        <v>6845375</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2025,57 +2021,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125736051</v>
+        <v>125735595</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523418</v>
+        <v>523492</v>
       </c>
       <c r="R16" t="n">
-        <v>6845349</v>
+        <v>6845165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125737958</v>
+        <v>125755785</v>
       </c>
       <c r="B17" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523967</v>
+        <v>523467</v>
       </c>
       <c r="R17" t="n">
-        <v>6845175</v>
+        <v>6845333</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755693</v>
+        <v>125755786</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523993</v>
+        <v>523474</v>
       </c>
       <c r="R18" t="n">
-        <v>6845158</v>
+        <v>6845244</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755710</v>
+        <v>125755693</v>
       </c>
       <c r="B19" t="n">
         <v>78972</v>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523572</v>
+        <v>523993</v>
       </c>
       <c r="R19" t="n">
-        <v>6845367</v>
+        <v>6845158</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2418,14 +2418,14 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125733598</v>
+        <v>125755710</v>
       </c>
       <c r="B20" t="n">
         <v>78972</v>
@@ -2456,17 +2456,17 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523483</v>
+        <v>523572</v>
       </c>
       <c r="R20" t="n">
-        <v>6845118</v>
+        <v>6845367</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2510,22 +2510,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755786</v>
+        <v>125737958</v>
       </c>
       <c r="B21" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523474</v>
+        <v>523967</v>
       </c>
       <c r="R21" t="n">
-        <v>6845244</v>
+        <v>6845175</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2607,22 +2607,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755785</v>
+        <v>125733598</v>
       </c>
       <c r="B22" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,37 +2630,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523467</v>
+        <v>523483</v>
       </c>
       <c r="R22" t="n">
-        <v>6845333</v>
+        <v>6845118</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,22 +2704,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755593</v>
+        <v>125755790</v>
       </c>
       <c r="B23" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,39 +2727,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523520</v>
+        <v>523486</v>
       </c>
       <c r="R23" t="n">
-        <v>6845094</v>
+        <v>6845100</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2792,11 +2787,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2823,10 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755790</v>
+        <v>125755593</v>
       </c>
       <c r="B24" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,34 +2824,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523486</v>
+        <v>523520</v>
       </c>
       <c r="R24" t="n">
-        <v>6845100</v>
+        <v>6845094</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2894,6 +2889,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3010,7 +3010,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755657</v>
+        <v>125737629</v>
       </c>
       <c r="B29" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523463</v>
+        <v>523960</v>
       </c>
       <c r="R29" t="n">
-        <v>6845211</v>
+        <v>6845161</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755545</v>
+        <v>125733581</v>
       </c>
       <c r="B30" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,34 +3416,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523465</v>
+        <v>523528</v>
       </c>
       <c r="R30" t="n">
-        <v>6845109</v>
+        <v>6845135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,22 +3490,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755549</v>
+        <v>125735113</v>
       </c>
       <c r="B31" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,37 +3513,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523541</v>
+        <v>523630</v>
       </c>
       <c r="R31" t="n">
-        <v>6845054</v>
+        <v>6845423</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,22 +3587,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755634</v>
+        <v>125755549</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523498</v>
+        <v>523541</v>
       </c>
       <c r="R32" t="n">
-        <v>6845404</v>
+        <v>6845054</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125733581</v>
+        <v>125755545</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,34 +3707,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523528</v>
+        <v>523465</v>
       </c>
       <c r="R33" t="n">
-        <v>6845135</v>
+        <v>6845109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,22 +3781,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125737629</v>
+        <v>125755634</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523960</v>
+        <v>523498</v>
       </c>
       <c r="R34" t="n">
-        <v>6845161</v>
+        <v>6845404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3878,60 +3878,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735113</v>
+        <v>125755657</v>
       </c>
       <c r="B35" t="n">
-        <v>78731</v>
+        <v>91393</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523630</v>
+        <v>523463</v>
       </c>
       <c r="R35" t="n">
-        <v>6845423</v>
+        <v>6845211</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,22 +3975,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755625</v>
+        <v>125755695</v>
       </c>
       <c r="B36" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523850</v>
+        <v>523990</v>
       </c>
       <c r="R36" t="n">
-        <v>6845286</v>
+        <v>6845162</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755695</v>
+        <v>125755565</v>
       </c>
       <c r="B37" t="n">
-        <v>78972</v>
+        <v>91252</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523990</v>
+        <v>523551</v>
       </c>
       <c r="R37" t="n">
-        <v>6845162</v>
+        <v>6845103</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755565</v>
+        <v>125755625</v>
       </c>
       <c r="B38" t="n">
-        <v>91252</v>
+        <v>78731</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523551</v>
+        <v>523850</v>
       </c>
       <c r="R38" t="n">
-        <v>6845103</v>
+        <v>6845286</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125734860</v>
+        <v>125755787</v>
       </c>
       <c r="B39" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,37 +4289,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523673</v>
+        <v>523457</v>
       </c>
       <c r="R39" t="n">
-        <v>6845294</v>
+        <v>6845237</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125734662</v>
+        <v>125755544</v>
       </c>
       <c r="B40" t="n">
-        <v>78730</v>
+        <v>79590</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,34 +4386,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523492</v>
+        <v>523483</v>
       </c>
       <c r="R40" t="n">
-        <v>6845165</v>
+        <v>6845181</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B41" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R41" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4557,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755787</v>
+        <v>125734860</v>
       </c>
       <c r="B42" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523457</v>
+        <v>523673</v>
       </c>
       <c r="R42" t="n">
-        <v>6845237</v>
+        <v>6845294</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755539</v>
+        <v>125734662</v>
       </c>
       <c r="B43" t="n">
-        <v>79590</v>
+        <v>78730</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,34 +4677,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523924</v>
+        <v>523492</v>
       </c>
       <c r="R43" t="n">
-        <v>6845215</v>
+        <v>6845165</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B44" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,37 +4774,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R44" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4848,22 +4848,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125735128</v>
+        <v>125737014</v>
       </c>
       <c r="B45" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523627</v>
+        <v>523854</v>
       </c>
       <c r="R45" t="n">
-        <v>6845420</v>
+        <v>6845289</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4957,45 +4957,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125736099</v>
+        <v>125755658</v>
       </c>
       <c r="B46" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523514</v>
+        <v>523487</v>
       </c>
       <c r="R46" t="n">
-        <v>6845340</v>
+        <v>6845098</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5042,22 +5042,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125734241</v>
+        <v>125755792</v>
       </c>
       <c r="B47" t="n">
-        <v>78972</v>
+        <v>92516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5065,34 +5065,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523492</v>
+        <v>523992</v>
       </c>
       <c r="R47" t="n">
-        <v>6845165</v>
+        <v>6845170</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5127,6 +5127,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5139,44 +5144,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755658</v>
+        <v>125755717</v>
       </c>
       <c r="B48" t="n">
-        <v>91393</v>
+        <v>78972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5186,10 +5191,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523487</v>
+        <v>523466</v>
       </c>
       <c r="R48" t="n">
-        <v>6845098</v>
+        <v>6845180</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5248,32 +5253,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755792</v>
+        <v>125755552</v>
       </c>
       <c r="B49" t="n">
-        <v>92516</v>
+        <v>91197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5283,10 +5288,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523992</v>
+        <v>523424</v>
       </c>
       <c r="R49" t="n">
-        <v>6845170</v>
+        <v>6845383</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5319,11 +5324,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5350,32 +5350,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755552</v>
+        <v>125755626</v>
       </c>
       <c r="B50" t="n">
-        <v>91197</v>
+        <v>78731</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523424</v>
+        <v>523759</v>
       </c>
       <c r="R50" t="n">
-        <v>6845383</v>
+        <v>6845238</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5447,10 +5447,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755717</v>
+        <v>125735128</v>
       </c>
       <c r="B51" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5458,37 +5458,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523466</v>
+        <v>523627</v>
       </c>
       <c r="R51" t="n">
-        <v>6845180</v>
+        <v>6845420</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,22 +5532,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125737014</v>
+        <v>125736099</v>
       </c>
       <c r="B52" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5555,37 +5555,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523854</v>
+        <v>523514</v>
       </c>
       <c r="R52" t="n">
-        <v>6845289</v>
+        <v>6845340</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5629,22 +5629,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755626</v>
+        <v>125734241</v>
       </c>
       <c r="B53" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5652,34 +5652,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523759</v>
+        <v>523492</v>
       </c>
       <c r="R53" t="n">
-        <v>6845238</v>
+        <v>6845165</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5726,12 +5726,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5845,10 +5845,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755636</v>
+        <v>125755542</v>
       </c>
       <c r="B55" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5856,21 +5856,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5880,10 +5880,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523511</v>
+        <v>523670</v>
       </c>
       <c r="R55" t="n">
-        <v>6845102</v>
+        <v>6845353</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5942,10 +5942,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755627</v>
+        <v>125755543</v>
       </c>
       <c r="B56" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5953,21 +5953,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5977,10 +5977,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523755</v>
+        <v>523460</v>
       </c>
       <c r="R56" t="n">
-        <v>6845251</v>
+        <v>6845221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755628</v>
+        <v>125732709</v>
       </c>
       <c r="B57" t="n">
         <v>78731</v>
@@ -6070,17 +6070,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523728</v>
+        <v>523548</v>
       </c>
       <c r="R57" t="n">
-        <v>6845279</v>
+        <v>6845076</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6124,22 +6124,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755542</v>
+        <v>125755636</v>
       </c>
       <c r="B58" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6147,21 +6147,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523670</v>
+        <v>523511</v>
       </c>
       <c r="R58" t="n">
-        <v>6845353</v>
+        <v>6845102</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755543</v>
+        <v>125755627</v>
       </c>
       <c r="B59" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6244,21 +6244,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523460</v>
+        <v>523755</v>
       </c>
       <c r="R59" t="n">
-        <v>6845221</v>
+        <v>6845251</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125732709</v>
+        <v>125755628</v>
       </c>
       <c r="B60" t="n">
         <v>78731</v>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523548</v>
+        <v>523728</v>
       </c>
       <c r="R60" t="n">
-        <v>6845076</v>
+        <v>6845279</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,60 +6415,69 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125736672</v>
+        <v>125755647</v>
       </c>
       <c r="B61" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523827</v>
+        <v>523408</v>
       </c>
       <c r="R61" t="n">
-        <v>6845310</v>
+        <v>6845401</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,44 +6521,44 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125735337</v>
+        <v>125735892</v>
       </c>
       <c r="B62" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6559,10 +6568,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523593</v>
+        <v>523608</v>
       </c>
       <c r="R62" t="n">
-        <v>6845417</v>
+        <v>6845376</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6621,10 +6630,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125734655</v>
+        <v>125736672</v>
       </c>
       <c r="B63" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,37 +6641,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523492</v>
+        <v>523827</v>
       </c>
       <c r="R63" t="n">
-        <v>6845165</v>
+        <v>6845310</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6706,19 +6715,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125734972</v>
+        <v>125735337</v>
       </c>
       <c r="B64" t="n">
         <v>78731</v>
@@ -6753,10 +6762,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523675</v>
+        <v>523593</v>
       </c>
       <c r="R64" t="n">
-        <v>6845339</v>
+        <v>6845417</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -6815,48 +6824,48 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125735892</v>
+        <v>125734655</v>
       </c>
       <c r="B65" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523608</v>
+        <v>523492</v>
       </c>
       <c r="R65" t="n">
-        <v>6845376</v>
+        <v>6845165</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6900,69 +6909,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755647</v>
+        <v>125734972</v>
       </c>
       <c r="B66" t="n">
-        <v>98338</v>
+        <v>78731</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523408</v>
+        <v>523675</v>
       </c>
       <c r="R66" t="n">
-        <v>6845401</v>
+        <v>6845339</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,12 +7006,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7115,32 +7115,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755598</v>
+        <v>125755788</v>
       </c>
       <c r="B68" t="n">
-        <v>97216</v>
+        <v>78639</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221945</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523351</v>
+        <v>523460</v>
       </c>
       <c r="R68" t="n">
-        <v>6845393</v>
+        <v>6845221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125733520</v>
+        <v>125755761</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,34 +7223,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523552</v>
+        <v>523387</v>
       </c>
       <c r="R69" t="n">
-        <v>6845072</v>
+        <v>6845410</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7297,19 +7302,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125733632</v>
+        <v>125755709</v>
       </c>
       <c r="B70" t="n">
         <v>78972</v>
@@ -7340,14 +7345,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523458</v>
+        <v>523598</v>
       </c>
       <c r="R70" t="n">
-        <v>6845126</v>
+        <v>6845380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7394,62 +7399,57 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125738012</v>
+        <v>125755598</v>
       </c>
       <c r="B71" t="n">
-        <v>57651</v>
+        <v>97217</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523967</v>
+        <v>523351</v>
       </c>
       <c r="R71" t="n">
-        <v>6845175</v>
+        <v>6845393</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755788</v>
+        <v>125755630</v>
       </c>
       <c r="B72" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,21 +7519,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523460</v>
+        <v>523671</v>
       </c>
       <c r="R72" t="n">
-        <v>6845221</v>
+        <v>6845353</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755709</v>
+        <v>125755629</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,21 +7616,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7640,10 +7640,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523598</v>
+        <v>523679</v>
       </c>
       <c r="R73" t="n">
-        <v>6845380</v>
+        <v>6845347</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7695,17 +7695,17 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755630</v>
+        <v>125733520</v>
       </c>
       <c r="B74" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,34 +7713,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523671</v>
+        <v>523552</v>
       </c>
       <c r="R74" t="n">
-        <v>6845353</v>
+        <v>6845072</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,22 +7787,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755629</v>
+        <v>125733632</v>
       </c>
       <c r="B75" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7810,34 +7810,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523679</v>
+        <v>523458</v>
       </c>
       <c r="R75" t="n">
-        <v>6845347</v>
+        <v>6845126</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7884,19 +7884,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755761</v>
+        <v>125738012</v>
       </c>
       <c r="B76" t="n">
         <v>57651</v>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523387</v>
+        <v>523967</v>
       </c>
       <c r="R76" t="n">
-        <v>6845410</v>
+        <v>6845175</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7986,12 +7986,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8001,7 +8001,7 @@
         <v>125735686</v>
       </c>
       <c r="B77" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755701</v>
+        <v>125755541</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8110,21 +8110,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8134,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523839</v>
+        <v>523757</v>
       </c>
       <c r="R78" t="n">
-        <v>6845286</v>
+        <v>6845248</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,7 +8196,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755707</v>
+        <v>125755701</v>
       </c>
       <c r="B79" t="n">
         <v>78972</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523644</v>
+        <v>523839</v>
       </c>
       <c r="R79" t="n">
-        <v>6845389</v>
+        <v>6845286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8286,39 +8286,39 @@
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755794</v>
+        <v>125755707</v>
       </c>
       <c r="B80" t="n">
-        <v>91642</v>
+        <v>78972</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8328,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523385</v>
+        <v>523644</v>
       </c>
       <c r="R80" t="n">
-        <v>6845416</v>
+        <v>6845389</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8364,11 +8364,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8395,32 +8390,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755714</v>
+        <v>125755794</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>91642</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8430,10 +8425,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523383</v>
+        <v>523385</v>
       </c>
       <c r="R81" t="n">
-        <v>6845391</v>
+        <v>6845416</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8468,6 +8463,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -8485,17 +8485,17 @@
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755541</v>
+        <v>125755714</v>
       </c>
       <c r="B82" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8503,21 +8503,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8527,10 +8527,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523757</v>
+        <v>523383</v>
       </c>
       <c r="R82" t="n">
-        <v>6845248</v>
+        <v>6845391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125732736</v>
+        <v>125755789</v>
       </c>
       <c r="B83" t="n">
-        <v>78730</v>
+        <v>78639</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,37 +8600,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523551</v>
+        <v>523480</v>
       </c>
       <c r="R83" t="n">
-        <v>6845080</v>
+        <v>6845112</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,19 +8674,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125737510</v>
+        <v>125755621</v>
       </c>
       <c r="B84" t="n">
         <v>78731</v>
@@ -8717,17 +8717,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523957</v>
+        <v>523920</v>
       </c>
       <c r="R84" t="n">
-        <v>6845190</v>
+        <v>6845217</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8771,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755621</v>
+        <v>125755702</v>
       </c>
       <c r="B85" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523920</v>
+        <v>523829</v>
       </c>
       <c r="R85" t="n">
-        <v>6845217</v>
+        <v>6845308</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755789</v>
+        <v>125737510</v>
       </c>
       <c r="B86" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523480</v>
+        <v>523957</v>
       </c>
       <c r="R86" t="n">
-        <v>6845112</v>
+        <v>6845190</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755702</v>
+        <v>125732736</v>
       </c>
       <c r="B87" t="n">
-        <v>78972</v>
+        <v>78730</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8988,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523829</v>
+        <v>523551</v>
       </c>
       <c r="R87" t="n">
-        <v>6845308</v>
+        <v>6845080</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9465,7 +9465,7 @@
         <v>125755654</v>
       </c>
       <c r="B92" t="n">
-        <v>98338</v>
+        <v>98339</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125737769</v>
+        <v>125755781</v>
       </c>
       <c r="B95" t="n">
-        <v>79590</v>
+        <v>78639</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9777,21 +9777,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523967</v>
+        <v>523958</v>
       </c>
       <c r="R95" t="n">
-        <v>6845175</v>
+        <v>6845195</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,22 +9851,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755781</v>
+        <v>125755694</v>
       </c>
       <c r="B96" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523958</v>
+        <v>523979</v>
       </c>
       <c r="R96" t="n">
-        <v>6845195</v>
+        <v>6845154</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755774</v>
+        <v>125755610</v>
       </c>
       <c r="B97" t="n">
-        <v>92522</v>
+        <v>8447</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9971,34 +9971,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523526</v>
+        <v>523527</v>
       </c>
       <c r="R97" t="n">
-        <v>6845095</v>
+        <v>6845375</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10050,17 +10055,17 @@
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755694</v>
+        <v>125755624</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10068,21 +10073,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10092,10 +10097,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523979</v>
+        <v>523853</v>
       </c>
       <c r="R98" t="n">
-        <v>6845154</v>
+        <v>6845279</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10154,10 +10159,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755610</v>
+        <v>125755774</v>
       </c>
       <c r="B99" t="n">
-        <v>8447</v>
+        <v>92522</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10165,39 +10170,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523527</v>
+        <v>523526</v>
       </c>
       <c r="R99" t="n">
-        <v>6845375</v>
+        <v>6845095</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755624</v>
+        <v>125737769</v>
       </c>
       <c r="B100" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523853</v>
+        <v>523967</v>
       </c>
       <c r="R100" t="n">
-        <v>6845279</v>
+        <v>6845175</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755712</v>
+        <v>125737335</v>
       </c>
       <c r="B102" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,37 +10461,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523428</v>
+        <v>523835</v>
       </c>
       <c r="R102" t="n">
-        <v>6845361</v>
+        <v>6845199</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125737335</v>
+        <v>125734280</v>
       </c>
       <c r="B103" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,21 +10558,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -10582,7 +10582,7 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523835</v>
+        <v>523482</v>
       </c>
       <c r="R103" t="n">
         <v>6845199</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125734280</v>
+        <v>125755550</v>
       </c>
       <c r="B104" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,37 +10655,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523482</v>
+        <v>523604</v>
       </c>
       <c r="R104" t="n">
-        <v>6845199</v>
+        <v>6845013</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10729,22 +10729,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755620</v>
+        <v>125755547</v>
       </c>
       <c r="B105" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523925</v>
+        <v>523479</v>
       </c>
       <c r="R105" t="n">
-        <v>6845214</v>
+        <v>6845112</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,10 +10838,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755550</v>
+        <v>125755712</v>
       </c>
       <c r="B106" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10849,21 +10849,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -10873,10 +10873,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523604</v>
+        <v>523428</v>
       </c>
       <c r="R106" t="n">
-        <v>6845013</v>
+        <v>6845361</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10935,10 +10935,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755547</v>
+        <v>125755620</v>
       </c>
       <c r="B107" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,21 +10946,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10970,10 +10970,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523479</v>
+        <v>523925</v>
       </c>
       <c r="R107" t="n">
-        <v>6845112</v>
+        <v>6845214</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11032,7 +11032,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755713</v>
+        <v>125736699</v>
       </c>
       <c r="B108" t="n">
         <v>78972</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523332</v>
+        <v>523766</v>
       </c>
       <c r="R108" t="n">
-        <v>6845377</v>
+        <v>6845303</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,19 +11117,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755706</v>
+        <v>125755713</v>
       </c>
       <c r="B109" t="n">
         <v>78972</v>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523655</v>
+        <v>523332</v>
       </c>
       <c r="R109" t="n">
-        <v>6845374</v>
+        <v>6845377</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11219,17 +11219,17 @@
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125737839</v>
+        <v>125755706</v>
       </c>
       <c r="B110" t="n">
-        <v>79561</v>
+        <v>78972</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523967</v>
+        <v>523655</v>
       </c>
       <c r="R110" t="n">
-        <v>6845175</v>
+        <v>6845374</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,22 +11311,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125736699</v>
+        <v>125755617</v>
       </c>
       <c r="B111" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11334,21 +11334,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523766</v>
+        <v>523972</v>
       </c>
       <c r="R111" t="n">
-        <v>6845303</v>
+        <v>6845173</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,22 +11408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755617</v>
+        <v>125737839</v>
       </c>
       <c r="B112" t="n">
-        <v>78731</v>
+        <v>79561</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523972</v>
+        <v>523967</v>
       </c>
       <c r="R112" t="n">
-        <v>6845173</v>
+        <v>6845175</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11505,57 +11505,66 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B113" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R113" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11614,54 +11623,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B114" t="n">
-        <v>98338</v>
+        <v>78731</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R114" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125732643</v>
+        <v>125755555</v>
       </c>
       <c r="B115" t="n">
-        <v>79561</v>
+        <v>90270</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,34 +11731,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523617</v>
+        <v>523480</v>
       </c>
       <c r="R115" t="n">
-        <v>6845031</v>
+        <v>6845111</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11805,22 +11805,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125736623</v>
+        <v>125755601</v>
       </c>
       <c r="B116" t="n">
-        <v>78972</v>
+        <v>92714</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11828,34 +11828,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523689</v>
+        <v>523463</v>
       </c>
       <c r="R116" t="n">
-        <v>6845339</v>
+        <v>6845230</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11902,12 +11902,12 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
@@ -12016,7 +12016,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755619</v>
+        <v>125755631</v>
       </c>
       <c r="B118" t="n">
         <v>78731</v>
@@ -12051,10 +12051,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523952</v>
+        <v>523636</v>
       </c>
       <c r="R118" t="n">
-        <v>6845185</v>
+        <v>6845388</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12113,7 +12113,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755631</v>
+        <v>125755619</v>
       </c>
       <c r="B119" t="n">
         <v>78731</v>
@@ -12148,10 +12148,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523636</v>
+        <v>523952</v>
       </c>
       <c r="R119" t="n">
-        <v>6845388</v>
+        <v>6845185</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12210,10 +12210,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755555</v>
+        <v>125755784</v>
       </c>
       <c r="B120" t="n">
-        <v>90270</v>
+        <v>78639</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12221,21 +12221,21 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12245,10 +12245,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523480</v>
+        <v>523606</v>
       </c>
       <c r="R120" t="n">
-        <v>6845111</v>
+        <v>6845378</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12307,45 +12307,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755601</v>
+        <v>125755563</v>
       </c>
       <c r="B121" t="n">
-        <v>92714</v>
+        <v>56843</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523463</v>
+        <v>523483</v>
       </c>
       <c r="R121" t="n">
-        <v>6845230</v>
+        <v>6845365</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12404,10 +12413,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755784</v>
+        <v>125736623</v>
       </c>
       <c r="B122" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12415,34 +12424,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523606</v>
+        <v>523689</v>
       </c>
       <c r="R122" t="n">
-        <v>6845378</v>
+        <v>6845339</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12489,66 +12498,57 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755563</v>
+        <v>125732643</v>
       </c>
       <c r="B123" t="n">
-        <v>56843</v>
+        <v>79561</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523483</v>
+        <v>523617</v>
       </c>
       <c r="R123" t="n">
-        <v>6845365</v>
+        <v>6845031</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12595,22 +12595,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755557</v>
+        <v>125755780</v>
       </c>
       <c r="B124" t="n">
-        <v>91232</v>
+        <v>78639</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,21 +12618,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>353</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12642,10 +12642,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523340</v>
+        <v>523584</v>
       </c>
       <c r="R124" t="n">
-        <v>6845392</v>
+        <v>6845361</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755780</v>
+        <v>125755704</v>
       </c>
       <c r="B125" t="n">
-        <v>78639</v>
+        <v>78972</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523584</v>
+        <v>523760</v>
       </c>
       <c r="R125" t="n">
-        <v>6845361</v>
+        <v>6845283</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755704</v>
+        <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>78972</v>
+        <v>91232</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523760</v>
+        <v>523340</v>
       </c>
       <c r="R126" t="n">
-        <v>6845283</v>
+        <v>6845392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12891,7 +12891,7 @@
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
@@ -12988,17 +12988,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125734818</v>
+        <v>125732670</v>
       </c>
       <c r="B128" t="n">
-        <v>91252</v>
+        <v>79590</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R128" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125732670</v>
+        <v>125734818</v>
       </c>
       <c r="B129" t="n">
-        <v>79590</v>
+        <v>91252</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523617</v>
+        <v>523643</v>
       </c>
       <c r="R129" t="n">
-        <v>6845031</v>
+        <v>6845282</v>
       </c>
       <c r="S129" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755708</v>
+        <v>125755632</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1365,21 +1365,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523626</v>
+        <v>523621</v>
       </c>
       <c r="R9" t="n">
-        <v>6845380</v>
+        <v>6845375</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755716</v>
+        <v>125755708</v>
       </c>
       <c r="B10" t="n">
         <v>78972</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523477</v>
+        <v>523626</v>
       </c>
       <c r="R10" t="n">
-        <v>6845219</v>
+        <v>6845380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1548,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755698</v>
+        <v>125755716</v>
       </c>
       <c r="B11" t="n">
         <v>78972</v>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523867</v>
+        <v>523477</v>
       </c>
       <c r="R11" t="n">
-        <v>6845227</v>
+        <v>6845219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1645,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755711</v>
+        <v>125755698</v>
       </c>
       <c r="B12" t="n">
         <v>78972</v>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523443</v>
+        <v>523867</v>
       </c>
       <c r="R12" t="n">
-        <v>6845363</v>
+        <v>6845227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125734647</v>
+        <v>125755711</v>
       </c>
       <c r="B13" t="n">
         <v>78972</v>
@@ -1773,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523611</v>
+        <v>523443</v>
       </c>
       <c r="R13" t="n">
-        <v>6845275</v>
+        <v>6845363</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,12 +1827,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1936,45 +1936,49 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755632</v>
+        <v>125735595</v>
       </c>
       <c r="B15" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523621</v>
+        <v>523492</v>
       </c>
       <c r="R15" t="n">
-        <v>6845375</v>
+        <v>6845165</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,64 +2025,60 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125735595</v>
+        <v>125734647</v>
       </c>
       <c r="B16" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523492</v>
+        <v>523611</v>
       </c>
       <c r="R16" t="n">
-        <v>6845165</v>
+        <v>6845275</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,12 +2122,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125734739</v>
+        <v>125755788</v>
       </c>
       <c r="B67" t="n">
-        <v>78731</v>
+        <v>78639</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,37 +7029,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523608</v>
+        <v>523460</v>
       </c>
       <c r="R67" t="n">
-        <v>6845309</v>
+        <v>6845221</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,22 +7103,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755788</v>
+        <v>125755761</v>
       </c>
       <c r="B68" t="n">
-        <v>78639</v>
+        <v>57651</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,34 +7126,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523460</v>
+        <v>523387</v>
       </c>
       <c r="R68" t="n">
-        <v>6845221</v>
+        <v>6845410</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,10 +7217,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755761</v>
+        <v>125755709</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,39 +7228,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523387</v>
+        <v>523598</v>
       </c>
       <c r="R69" t="n">
-        <v>6845410</v>
+        <v>6845380</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,32 +7314,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755709</v>
+        <v>125755598</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>97217</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523598</v>
+        <v>523351</v>
       </c>
       <c r="R70" t="n">
-        <v>6845380</v>
+        <v>6845393</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7411,32 +7411,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755598</v>
+        <v>125755630</v>
       </c>
       <c r="B71" t="n">
-        <v>97217</v>
+        <v>78731</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523351</v>
+        <v>523671</v>
       </c>
       <c r="R71" t="n">
-        <v>6845393</v>
+        <v>6845353</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755630</v>
+        <v>125755629</v>
       </c>
       <c r="B72" t="n">
         <v>78731</v>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523671</v>
+        <v>523679</v>
       </c>
       <c r="R72" t="n">
-        <v>6845353</v>
+        <v>6845347</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755629</v>
+        <v>125733520</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,34 +7616,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523679</v>
+        <v>523552</v>
       </c>
       <c r="R73" t="n">
-        <v>6845347</v>
+        <v>6845072</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,19 +7690,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125733520</v>
+        <v>125733632</v>
       </c>
       <c r="B74" t="n">
         <v>78972</v>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523552</v>
+        <v>523458</v>
       </c>
       <c r="R74" t="n">
-        <v>6845072</v>
+        <v>6845126</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125733632</v>
+        <v>125738012</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7810,34 +7810,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523458</v>
+        <v>523967</v>
       </c>
       <c r="R75" t="n">
-        <v>6845126</v>
+        <v>6845175</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7896,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125738012</v>
+        <v>125734739</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>78731</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7907,42 +7912,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523967</v>
+        <v>523608</v>
       </c>
       <c r="R76" t="n">
-        <v>6845175</v>
+        <v>6845309</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7986,12 +7986,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -1354,45 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755632</v>
+        <v>125735595</v>
       </c>
       <c r="B9" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523621</v>
+        <v>523492</v>
       </c>
       <c r="R9" t="n">
-        <v>6845375</v>
+        <v>6845165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,12 +1443,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1839,7 +1843,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125736051</v>
+        <v>125734647</v>
       </c>
       <c r="B14" t="n">
         <v>78972</v>
@@ -1870,17 +1874,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523418</v>
+        <v>523611</v>
       </c>
       <c r="R14" t="n">
-        <v>6845349</v>
+        <v>6845275</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,61 +1928,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B15" t="n">
-        <v>98339</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R15" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,10 +2037,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125734647</v>
+        <v>125755632</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,37 +2048,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523611</v>
+        <v>523621</v>
       </c>
       <c r="R16" t="n">
-        <v>6845275</v>
+        <v>6845375</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,12 +2122,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125737958</v>
+        <v>125733598</v>
       </c>
       <c r="B21" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,37 +2533,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523967</v>
+        <v>523483</v>
       </c>
       <c r="R21" t="n">
-        <v>6845175</v>
+        <v>6845118</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125733598</v>
+        <v>125737958</v>
       </c>
       <c r="B22" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,37 +2630,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523483</v>
+        <v>523967</v>
       </c>
       <c r="R22" t="n">
-        <v>6845118</v>
+        <v>6845175</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,12 +2704,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3308,32 +3308,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125737629</v>
+        <v>125755657</v>
       </c>
       <c r="B29" t="n">
-        <v>78972</v>
+        <v>91393</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523960</v>
+        <v>523463</v>
       </c>
       <c r="R29" t="n">
-        <v>6845161</v>
+        <v>6845211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125733581</v>
+        <v>125755549</v>
       </c>
       <c r="B30" t="n">
-        <v>78972</v>
+        <v>79590</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,34 +3416,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523528</v>
+        <v>523541</v>
       </c>
       <c r="R30" t="n">
-        <v>6845135</v>
+        <v>6845054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,22 +3490,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125735113</v>
+        <v>125755545</v>
       </c>
       <c r="B31" t="n">
-        <v>78731</v>
+        <v>79590</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,37 +3513,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523630</v>
+        <v>523465</v>
       </c>
       <c r="R31" t="n">
-        <v>6845423</v>
+        <v>6845109</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,22 +3587,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755549</v>
+        <v>125755634</v>
       </c>
       <c r="B32" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523541</v>
+        <v>523498</v>
       </c>
       <c r="R32" t="n">
-        <v>6845054</v>
+        <v>6845404</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755545</v>
+        <v>125737629</v>
       </c>
       <c r="B33" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523465</v>
+        <v>523960</v>
       </c>
       <c r="R33" t="n">
-        <v>6845109</v>
+        <v>6845161</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,22 +3781,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755634</v>
+        <v>125733581</v>
       </c>
       <c r="B34" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,34 +3804,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523498</v>
+        <v>523528</v>
       </c>
       <c r="R34" t="n">
-        <v>6845404</v>
+        <v>6845135</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3878,60 +3878,60 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755657</v>
+        <v>125735113</v>
       </c>
       <c r="B35" t="n">
-        <v>91393</v>
+        <v>78731</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523463</v>
+        <v>523630</v>
       </c>
       <c r="R35" t="n">
-        <v>6845211</v>
+        <v>6845423</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,12 +3975,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -6427,57 +6427,48 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755647</v>
+        <v>125735337</v>
       </c>
       <c r="B61" t="n">
-        <v>98339</v>
+        <v>78731</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523408</v>
+        <v>523593</v>
       </c>
       <c r="R61" t="n">
-        <v>6845401</v>
+        <v>6845417</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6521,60 +6512,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125735892</v>
+        <v>125734655</v>
       </c>
       <c r="B62" t="n">
-        <v>92522</v>
+        <v>78731</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523608</v>
+        <v>523492</v>
       </c>
       <c r="R62" t="n">
-        <v>6845376</v>
+        <v>6845165</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6618,22 +6609,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125736672</v>
+        <v>125734972</v>
       </c>
       <c r="B63" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6641,34 +6632,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523827</v>
+        <v>523675</v>
       </c>
       <c r="R63" t="n">
-        <v>6845310</v>
+        <v>6845339</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6727,48 +6718,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125735337</v>
+        <v>125755647</v>
       </c>
       <c r="B64" t="n">
-        <v>78731</v>
+        <v>98339</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523593</v>
+        <v>523408</v>
       </c>
       <c r="R64" t="n">
-        <v>6845417</v>
+        <v>6845401</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6812,22 +6812,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734655</v>
+        <v>125736672</v>
       </c>
       <c r="B65" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6835,37 +6835,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523492</v>
+        <v>523827</v>
       </c>
       <c r="R65" t="n">
-        <v>6845165</v>
+        <v>6845310</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6909,44 +6909,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125734972</v>
+        <v>125735892</v>
       </c>
       <c r="B66" t="n">
-        <v>78731</v>
+        <v>92522</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6956,10 +6956,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523675</v>
+        <v>523608</v>
       </c>
       <c r="R66" t="n">
-        <v>6845339</v>
+        <v>6845376</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755788</v>
+        <v>125734739</v>
       </c>
       <c r="B67" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,37 +7029,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523460</v>
+        <v>523608</v>
       </c>
       <c r="R67" t="n">
-        <v>6845221</v>
+        <v>6845309</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,22 +7103,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755761</v>
+        <v>125755788</v>
       </c>
       <c r="B68" t="n">
-        <v>57651</v>
+        <v>78639</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,39 +7126,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523387</v>
+        <v>523460</v>
       </c>
       <c r="R68" t="n">
-        <v>6845410</v>
+        <v>6845221</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7217,10 +7212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755709</v>
+        <v>125755761</v>
       </c>
       <c r="B69" t="n">
-        <v>78972</v>
+        <v>57651</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7228,34 +7223,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523598</v>
+        <v>523387</v>
       </c>
       <c r="R69" t="n">
-        <v>6845380</v>
+        <v>6845410</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,32 +7314,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755598</v>
+        <v>125755709</v>
       </c>
       <c r="B70" t="n">
-        <v>97217</v>
+        <v>78972</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7349,10 +7349,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523351</v>
+        <v>523598</v>
       </c>
       <c r="R70" t="n">
-        <v>6845393</v>
+        <v>6845380</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7411,32 +7411,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755630</v>
+        <v>125755598</v>
       </c>
       <c r="B71" t="n">
-        <v>78731</v>
+        <v>97217</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523671</v>
+        <v>523351</v>
       </c>
       <c r="R71" t="n">
-        <v>6845353</v>
+        <v>6845393</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7508,7 +7508,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755629</v>
+        <v>125755630</v>
       </c>
       <c r="B72" t="n">
         <v>78731</v>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523679</v>
+        <v>523671</v>
       </c>
       <c r="R72" t="n">
-        <v>6845347</v>
+        <v>6845353</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,10 +7605,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125733520</v>
+        <v>125755629</v>
       </c>
       <c r="B73" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,34 +7616,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523552</v>
+        <v>523679</v>
       </c>
       <c r="R73" t="n">
-        <v>6845072</v>
+        <v>6845347</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,19 +7690,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125733632</v>
+        <v>125733520</v>
       </c>
       <c r="B74" t="n">
         <v>78972</v>
@@ -7737,10 +7737,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523458</v>
+        <v>523552</v>
       </c>
       <c r="R74" t="n">
-        <v>6845126</v>
+        <v>6845072</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125738012</v>
+        <v>125733632</v>
       </c>
       <c r="B75" t="n">
-        <v>57651</v>
+        <v>78972</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7810,39 +7810,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523967</v>
+        <v>523458</v>
       </c>
       <c r="R75" t="n">
-        <v>6845175</v>
+        <v>6845126</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7901,10 +7896,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125734739</v>
+        <v>125738012</v>
       </c>
       <c r="B76" t="n">
-        <v>78731</v>
+        <v>57651</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,37 +7907,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523608</v>
+        <v>523967</v>
       </c>
       <c r="R76" t="n">
-        <v>6845309</v>
+        <v>6845175</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7986,61 +7986,57 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125735686</v>
+        <v>125755541</v>
       </c>
       <c r="B77" t="n">
-        <v>98339</v>
+        <v>79590</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523418</v>
+        <v>523757</v>
       </c>
       <c r="R77" t="n">
-        <v>6845349</v>
+        <v>6845248</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8087,22 +8083,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755541</v>
+        <v>125755701</v>
       </c>
       <c r="B78" t="n">
-        <v>79590</v>
+        <v>78972</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8110,21 +8106,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8134,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523757</v>
+        <v>523839</v>
       </c>
       <c r="R78" t="n">
-        <v>6845248</v>
+        <v>6845286</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8196,7 +8192,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B79" t="n">
         <v>78972</v>
@@ -8231,10 +8227,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R79" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8293,32 +8289,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755707</v>
+        <v>125755794</v>
       </c>
       <c r="B80" t="n">
-        <v>78972</v>
+        <v>91642</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8328,10 +8324,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523644</v>
+        <v>523385</v>
       </c>
       <c r="R80" t="n">
-        <v>6845389</v>
+        <v>6845416</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8364,6 +8360,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8390,32 +8391,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755794</v>
+        <v>125755714</v>
       </c>
       <c r="B81" t="n">
-        <v>91642</v>
+        <v>78972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8425,10 +8426,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523385</v>
+        <v>523383</v>
       </c>
       <c r="R81" t="n">
-        <v>6845416</v>
+        <v>6845391</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8461,11 +8462,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8492,45 +8488,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755714</v>
+        <v>125735686</v>
       </c>
       <c r="B82" t="n">
-        <v>78972</v>
+        <v>98339</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523383</v>
+        <v>523418</v>
       </c>
       <c r="R82" t="n">
-        <v>6845391</v>
+        <v>6845349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,22 +8577,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755789</v>
+        <v>125755621</v>
       </c>
       <c r="B83" t="n">
-        <v>78639</v>
+        <v>78731</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523480</v>
+        <v>523920</v>
       </c>
       <c r="R83" t="n">
-        <v>6845112</v>
+        <v>6845217</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755621</v>
+        <v>125755702</v>
       </c>
       <c r="B84" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523920</v>
+        <v>523829</v>
       </c>
       <c r="R84" t="n">
-        <v>6845217</v>
+        <v>6845308</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755702</v>
+        <v>125755789</v>
       </c>
       <c r="B85" t="n">
-        <v>78972</v>
+        <v>78639</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523829</v>
+        <v>523480</v>
       </c>
       <c r="R85" t="n">
-        <v>6845308</v>
+        <v>6845112</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9766,10 +9766,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755781</v>
+        <v>125737769</v>
       </c>
       <c r="B95" t="n">
-        <v>78639</v>
+        <v>79590</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9777,21 +9777,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523958</v>
+        <v>523967</v>
       </c>
       <c r="R95" t="n">
-        <v>6845195</v>
+        <v>6845175</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,44 +9851,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755694</v>
+        <v>125755774</v>
       </c>
       <c r="B96" t="n">
-        <v>78972</v>
+        <v>92522</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523979</v>
+        <v>523526</v>
       </c>
       <c r="R96" t="n">
-        <v>6845154</v>
+        <v>6845095</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9960,50 +9960,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755610</v>
+        <v>125755781</v>
       </c>
       <c r="B97" t="n">
-        <v>8447</v>
+        <v>78639</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523527</v>
+        <v>523958</v>
       </c>
       <c r="R97" t="n">
-        <v>6845375</v>
+        <v>6845195</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10062,10 +10057,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755624</v>
+        <v>125755694</v>
       </c>
       <c r="B98" t="n">
-        <v>78731</v>
+        <v>78972</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10073,21 +10068,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10097,10 +10092,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523853</v>
+        <v>523979</v>
       </c>
       <c r="R98" t="n">
-        <v>6845279</v>
+        <v>6845154</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10159,10 +10154,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755774</v>
+        <v>125755610</v>
       </c>
       <c r="B99" t="n">
-        <v>92522</v>
+        <v>8447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10170,34 +10165,39 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523526</v>
+        <v>523527</v>
       </c>
       <c r="R99" t="n">
-        <v>6845095</v>
+        <v>6845375</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125737769</v>
+        <v>125755624</v>
       </c>
       <c r="B100" t="n">
-        <v>79590</v>
+        <v>78731</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523967</v>
+        <v>523853</v>
       </c>
       <c r="R100" t="n">
-        <v>6845175</v>
+        <v>6845279</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10341,12 +10341,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125755643</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125755703</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125755705</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125737411</v>
+        <v>125734476</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,34 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523825</v>
+        <v>523492</v>
       </c>
       <c r="R5" t="n">
-        <v>6845311</v>
+        <v>6845165</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125734228</v>
+        <v>125737411</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523467</v>
+        <v>523825</v>
       </c>
       <c r="R6" t="n">
-        <v>6845121</v>
+        <v>6845311</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734476</v>
+        <v>125734228</v>
       </c>
       <c r="B7" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523492</v>
+        <v>523467</v>
       </c>
       <c r="R7" t="n">
-        <v>6845165</v>
+        <v>6845121</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1260,7 +1260,7 @@
         <v>125736529</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1354,49 +1354,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125735595</v>
+        <v>125755708</v>
       </c>
       <c r="B9" t="n">
-        <v>98339</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523492</v>
+        <v>523626</v>
       </c>
       <c r="R9" t="n">
-        <v>6845165</v>
+        <v>6845380</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1443,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755708</v>
+        <v>125755716</v>
       </c>
       <c r="B10" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1490,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523626</v>
+        <v>523477</v>
       </c>
       <c r="R10" t="n">
-        <v>6845380</v>
+        <v>6845219</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1552,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1587,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R11" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755698</v>
+        <v>125755711</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1684,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523867</v>
+        <v>523443</v>
       </c>
       <c r="R12" t="n">
-        <v>6845227</v>
+        <v>6845363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1746,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755711</v>
+        <v>125734647</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,17 +1773,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523443</v>
+        <v>523611</v>
       </c>
       <c r="R13" t="n">
-        <v>6845363</v>
+        <v>6845275</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1831,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125734647</v>
+        <v>125736051</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523611</v>
+        <v>523418</v>
       </c>
       <c r="R14" t="n">
-        <v>6845275</v>
+        <v>6845349</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125736051</v>
+        <v>125755632</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1951,34 +1947,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523418</v>
+        <v>523621</v>
       </c>
       <c r="R15" t="n">
-        <v>6845349</v>
+        <v>6845375</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2025,57 +2021,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755632</v>
+        <v>125735595</v>
       </c>
       <c r="B16" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523621</v>
+        <v>523492</v>
       </c>
       <c r="R16" t="n">
-        <v>6845375</v>
+        <v>6845165</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,22 +2122,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755785</v>
+        <v>125755693</v>
       </c>
       <c r="B17" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,21 +2145,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2169,10 +2169,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523467</v>
+        <v>523993</v>
       </c>
       <c r="R17" t="n">
-        <v>6845333</v>
+        <v>6845158</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2231,10 +2231,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755786</v>
+        <v>125755710</v>
       </c>
       <c r="B18" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523474</v>
+        <v>523572</v>
       </c>
       <c r="R18" t="n">
-        <v>6845244</v>
+        <v>6845367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2328,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755693</v>
+        <v>125755786</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2339,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2363,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523993</v>
+        <v>523474</v>
       </c>
       <c r="R19" t="n">
-        <v>6845158</v>
+        <v>6845244</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,10 +2425,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755710</v>
+        <v>125755785</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,21 +2436,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523572</v>
+        <v>523467</v>
       </c>
       <c r="R20" t="n">
-        <v>6845367</v>
+        <v>6845333</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125733598</v>
+        <v>125737958</v>
       </c>
       <c r="B21" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,37 +2533,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523483</v>
+        <v>523967</v>
       </c>
       <c r="R21" t="n">
-        <v>6845118</v>
+        <v>6845175</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2607,22 +2607,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125737958</v>
+        <v>125733598</v>
       </c>
       <c r="B22" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,37 +2630,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523967</v>
+        <v>523483</v>
       </c>
       <c r="R22" t="n">
-        <v>6845175</v>
+        <v>6845118</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,22 +2704,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755790</v>
+        <v>125755719</v>
       </c>
       <c r="B23" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,21 +2727,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2751,10 +2751,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523486</v>
+        <v>523554</v>
       </c>
       <c r="R23" t="n">
-        <v>6845100</v>
+        <v>6845068</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,10 +2813,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755593</v>
+        <v>125755790</v>
       </c>
       <c r="B24" t="n">
-        <v>57651</v>
+        <v>78640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,39 +2824,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523520</v>
+        <v>523486</v>
       </c>
       <c r="R24" t="n">
-        <v>6845094</v>
+        <v>6845100</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2889,11 +2884,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -2920,10 +2910,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755719</v>
+        <v>125755593</v>
       </c>
       <c r="B25" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,34 +2921,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523554</v>
+        <v>523520</v>
       </c>
       <c r="R25" t="n">
-        <v>6845068</v>
+        <v>6845094</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2991,6 +2986,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3020,7 +3020,7 @@
         <v>125736021</v>
       </c>
       <c r="B26" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>125735304</v>
       </c>
       <c r="B27" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>125733851</v>
       </c>
       <c r="B28" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>125755657</v>
       </c>
       <c r="B29" t="n">
-        <v>91393</v>
+        <v>91395</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755549</v>
+        <v>125733581</v>
       </c>
       <c r="B30" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,34 +3416,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523541</v>
+        <v>523528</v>
       </c>
       <c r="R30" t="n">
-        <v>6845054</v>
+        <v>6845135</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,22 +3490,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755545</v>
+        <v>125737629</v>
       </c>
       <c r="B31" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523465</v>
+        <v>523960</v>
       </c>
       <c r="R31" t="n">
-        <v>6845109</v>
+        <v>6845161</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3587,12 +3587,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3602,7 +3602,7 @@
         <v>125755634</v>
       </c>
       <c r="B32" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125737629</v>
+        <v>125735113</v>
       </c>
       <c r="B33" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523960</v>
+        <v>523630</v>
       </c>
       <c r="R33" t="n">
-        <v>6845161</v>
+        <v>6845423</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3781,22 +3781,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125733581</v>
+        <v>125755549</v>
       </c>
       <c r="B34" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,34 +3804,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523528</v>
+        <v>523541</v>
       </c>
       <c r="R34" t="n">
-        <v>6845135</v>
+        <v>6845054</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3878,22 +3878,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735113</v>
+        <v>125755545</v>
       </c>
       <c r="B35" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,37 +3901,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523630</v>
+        <v>523465</v>
       </c>
       <c r="R35" t="n">
-        <v>6845423</v>
+        <v>6845109</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,12 +3975,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -3990,7 +3990,7 @@
         <v>125755695</v>
       </c>
       <c r="B36" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4087,7 +4087,7 @@
         <v>125755565</v>
       </c>
       <c r="B37" t="n">
-        <v>91252</v>
+        <v>91254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4184,7 +4184,7 @@
         <v>125755625</v>
       </c>
       <c r="B38" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4281,7 +4281,7 @@
         <v>125755787</v>
       </c>
       <c r="B39" t="n">
-        <v>78639</v>
+        <v>78640</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4378,7 +4378,7 @@
         <v>125755544</v>
       </c>
       <c r="B40" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>125755539</v>
       </c>
       <c r="B41" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4569,10 +4569,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734860</v>
+        <v>125734662</v>
       </c>
       <c r="B42" t="n">
-        <v>78972</v>
+        <v>78731</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523673</v>
+        <v>523492</v>
       </c>
       <c r="R42" t="n">
-        <v>6845294</v>
+        <v>6845165</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125734662</v>
+        <v>125734860</v>
       </c>
       <c r="B43" t="n">
-        <v>78730</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523492</v>
+        <v>523673</v>
       </c>
       <c r="R43" t="n">
-        <v>6845165</v>
+        <v>6845294</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,12 +4751,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4766,7 +4766,7 @@
         <v>125735540</v>
       </c>
       <c r="B44" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4860,10 +4860,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125737014</v>
+        <v>125735128</v>
       </c>
       <c r="B45" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4871,34 +4871,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523854</v>
+        <v>523627</v>
       </c>
       <c r="R45" t="n">
-        <v>6845289</v>
+        <v>6845420</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -4957,32 +4957,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755658</v>
+        <v>125755626</v>
       </c>
       <c r="B46" t="n">
-        <v>91393</v>
+        <v>78732</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523487</v>
+        <v>523759</v>
       </c>
       <c r="R46" t="n">
-        <v>6845098</v>
+        <v>6845238</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5054,10 +5054,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755792</v>
+        <v>125737014</v>
       </c>
       <c r="B47" t="n">
-        <v>92516</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5065,37 +5065,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523992</v>
+        <v>523854</v>
       </c>
       <c r="R47" t="n">
-        <v>6845170</v>
+        <v>6845289</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5125,11 +5125,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5144,44 +5139,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755717</v>
+        <v>125755658</v>
       </c>
       <c r="B48" t="n">
-        <v>78972</v>
+        <v>91395</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5191,10 +5186,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523466</v>
+        <v>523487</v>
       </c>
       <c r="R48" t="n">
-        <v>6845180</v>
+        <v>6845098</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5253,32 +5248,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755552</v>
+        <v>125755792</v>
       </c>
       <c r="B49" t="n">
-        <v>91197</v>
+        <v>92518</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>4362</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5288,10 +5283,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523424</v>
+        <v>523992</v>
       </c>
       <c r="R49" t="n">
-        <v>6845383</v>
+        <v>6845170</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5324,6 +5319,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5350,10 +5350,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755626</v>
+        <v>125755717</v>
       </c>
       <c r="B50" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5361,21 +5361,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5385,10 +5385,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523759</v>
+        <v>523466</v>
       </c>
       <c r="R50" t="n">
-        <v>6845238</v>
+        <v>6845180</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5447,48 +5447,48 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125735128</v>
+        <v>125755552</v>
       </c>
       <c r="B51" t="n">
-        <v>79590</v>
+        <v>91199</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523627</v>
+        <v>523424</v>
       </c>
       <c r="R51" t="n">
-        <v>6845420</v>
+        <v>6845383</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,22 +5532,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125736099</v>
+        <v>125734241</v>
       </c>
       <c r="B52" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5579,10 +5579,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523514</v>
+        <v>523492</v>
       </c>
       <c r="R52" t="n">
-        <v>6845340</v>
+        <v>6845165</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,10 +5641,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125734241</v>
+        <v>125736099</v>
       </c>
       <c r="B53" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5676,10 +5676,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523492</v>
+        <v>523514</v>
       </c>
       <c r="R53" t="n">
-        <v>6845165</v>
+        <v>6845340</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5738,58 +5738,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125736061</v>
+        <v>125755542</v>
       </c>
       <c r="B54" t="n">
-        <v>56843</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523643</v>
+        <v>523670</v>
       </c>
       <c r="R54" t="n">
-        <v>6845391</v>
+        <v>6845353</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5833,22 +5823,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755542</v>
+        <v>125755543</v>
       </c>
       <c r="B55" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5880,10 +5870,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523670</v>
+        <v>523460</v>
       </c>
       <c r="R55" t="n">
-        <v>6845353</v>
+        <v>6845221</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5942,48 +5932,58 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755543</v>
+        <v>125736061</v>
       </c>
       <c r="B56" t="n">
-        <v>79590</v>
+        <v>56844</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523460</v>
+        <v>523643</v>
       </c>
       <c r="R56" t="n">
-        <v>6845221</v>
+        <v>6845391</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6027,22 +6027,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125732709</v>
+        <v>125755636</v>
       </c>
       <c r="B57" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6070,17 +6070,17 @@
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523548</v>
+        <v>523511</v>
       </c>
       <c r="R57" t="n">
-        <v>6845076</v>
+        <v>6845102</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6124,22 +6124,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755636</v>
+        <v>125755627</v>
       </c>
       <c r="B58" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523511</v>
+        <v>523755</v>
       </c>
       <c r="R58" t="n">
-        <v>6845102</v>
+        <v>6845251</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755627</v>
+        <v>125755628</v>
       </c>
       <c r="B59" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523755</v>
+        <v>523728</v>
       </c>
       <c r="R59" t="n">
-        <v>6845251</v>
+        <v>6845279</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,10 +6330,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755628</v>
+        <v>125732709</v>
       </c>
       <c r="B60" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523728</v>
+        <v>523548</v>
       </c>
       <c r="R60" t="n">
-        <v>6845279</v>
+        <v>6845076</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,60 +6415,69 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125735337</v>
+        <v>125755647</v>
       </c>
       <c r="B61" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523593</v>
+        <v>523408</v>
       </c>
       <c r="R61" t="n">
-        <v>6845417</v>
+        <v>6845401</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,60 +6521,60 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125734655</v>
+        <v>125735892</v>
       </c>
       <c r="B62" t="n">
-        <v>78731</v>
+        <v>92524</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523492</v>
+        <v>523608</v>
       </c>
       <c r="R62" t="n">
-        <v>6845165</v>
+        <v>6845376</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6609,22 +6618,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125734972</v>
+        <v>125736672</v>
       </c>
       <c r="B63" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6632,34 +6641,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523675</v>
+        <v>523827</v>
       </c>
       <c r="R63" t="n">
-        <v>6845339</v>
+        <v>6845310</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6718,57 +6727,48 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755647</v>
+        <v>125734972</v>
       </c>
       <c r="B64" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523408</v>
+        <v>523675</v>
       </c>
       <c r="R64" t="n">
-        <v>6845401</v>
+        <v>6845339</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6812,22 +6812,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125736672</v>
+        <v>125735337</v>
       </c>
       <c r="B65" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6835,34 +6835,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523827</v>
+        <v>523593</v>
       </c>
       <c r="R65" t="n">
-        <v>6845310</v>
+        <v>6845417</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6921,48 +6921,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125735892</v>
+        <v>125734655</v>
       </c>
       <c r="B66" t="n">
-        <v>92522</v>
+        <v>78732</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523608</v>
+        <v>523492</v>
       </c>
       <c r="R66" t="n">
-        <v>6845376</v>
+        <v>6845165</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,22 +7006,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125734739</v>
+        <v>125755630</v>
       </c>
       <c r="B67" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7049,17 +7049,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523608</v>
+        <v>523671</v>
       </c>
       <c r="R67" t="n">
-        <v>6845309</v>
+        <v>6845353</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,22 +7103,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755788</v>
+        <v>125755629</v>
       </c>
       <c r="B68" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523460</v>
+        <v>523679</v>
       </c>
       <c r="R68" t="n">
-        <v>6845221</v>
+        <v>6845347</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755761</v>
+        <v>125755709</v>
       </c>
       <c r="B69" t="n">
-        <v>57651</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,39 +7223,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523387</v>
+        <v>523598</v>
       </c>
       <c r="R69" t="n">
-        <v>6845410</v>
+        <v>6845380</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,10 +7309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755709</v>
+        <v>125755788</v>
       </c>
       <c r="B70" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7325,21 +7320,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7349,10 +7344,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523598</v>
+        <v>523460</v>
       </c>
       <c r="R70" t="n">
-        <v>6845380</v>
+        <v>6845221</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7411,45 +7406,50 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755598</v>
+        <v>125755761</v>
       </c>
       <c r="B71" t="n">
-        <v>97217</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523351</v>
+        <v>523387</v>
       </c>
       <c r="R71" t="n">
-        <v>6845393</v>
+        <v>6845410</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755630</v>
+        <v>125733520</v>
       </c>
       <c r="B72" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,34 +7519,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523671</v>
+        <v>523552</v>
       </c>
       <c r="R72" t="n">
-        <v>6845353</v>
+        <v>6845072</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,22 +7593,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755629</v>
+        <v>125733632</v>
       </c>
       <c r="B73" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,34 +7616,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523679</v>
+        <v>523458</v>
       </c>
       <c r="R73" t="n">
-        <v>6845347</v>
+        <v>6845126</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,57 +7690,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125733520</v>
+        <v>125755598</v>
       </c>
       <c r="B74" t="n">
-        <v>78972</v>
+        <v>97219</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523552</v>
+        <v>523351</v>
       </c>
       <c r="R74" t="n">
-        <v>6845072</v>
+        <v>6845393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,22 +7787,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125733632</v>
+        <v>125738012</v>
       </c>
       <c r="B75" t="n">
-        <v>78972</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7810,34 +7810,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523458</v>
+        <v>523967</v>
       </c>
       <c r="R75" t="n">
-        <v>6845126</v>
+        <v>6845175</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7896,10 +7901,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125738012</v>
+        <v>125734739</v>
       </c>
       <c r="B76" t="n">
-        <v>57651</v>
+        <v>78732</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7907,42 +7912,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523967</v>
+        <v>523608</v>
       </c>
       <c r="R76" t="n">
-        <v>6845175</v>
+        <v>6845309</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7986,22 +7986,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755541</v>
+        <v>125755701</v>
       </c>
       <c r="B77" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8009,21 +8009,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8033,10 +8033,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523757</v>
+        <v>523839</v>
       </c>
       <c r="R77" t="n">
-        <v>6845248</v>
+        <v>6845286</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8095,10 +8095,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755701</v>
+        <v>125755707</v>
       </c>
       <c r="B78" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8130,10 +8130,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523839</v>
+        <v>523644</v>
       </c>
       <c r="R78" t="n">
-        <v>6845286</v>
+        <v>6845389</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8192,32 +8192,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755707</v>
+        <v>125755794</v>
       </c>
       <c r="B79" t="n">
-        <v>78972</v>
+        <v>91644</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8227,10 +8227,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523644</v>
+        <v>523385</v>
       </c>
       <c r="R79" t="n">
-        <v>6845389</v>
+        <v>6845416</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8263,6 +8263,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8289,32 +8294,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755794</v>
+        <v>125755714</v>
       </c>
       <c r="B80" t="n">
-        <v>91642</v>
+        <v>78973</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8324,10 +8329,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523385</v>
+        <v>523383</v>
       </c>
       <c r="R80" t="n">
-        <v>6845416</v>
+        <v>6845391</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8360,11 +8365,6 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8391,10 +8391,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755714</v>
+        <v>125755541</v>
       </c>
       <c r="B81" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8402,21 +8402,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8426,10 +8426,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523383</v>
+        <v>523757</v>
       </c>
       <c r="R81" t="n">
-        <v>6845391</v>
+        <v>6845248</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8491,7 +8491,7 @@
         <v>125735686</v>
       </c>
       <c r="B82" t="n">
-        <v>98339</v>
+        <v>98341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8589,10 +8589,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755621</v>
+        <v>125755702</v>
       </c>
       <c r="B83" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,21 +8600,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8624,10 +8624,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523920</v>
+        <v>523829</v>
       </c>
       <c r="R83" t="n">
-        <v>6845217</v>
+        <v>6845308</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755702</v>
+        <v>125755789</v>
       </c>
       <c r="B84" t="n">
-        <v>78972</v>
+        <v>78640</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523829</v>
+        <v>523480</v>
       </c>
       <c r="R84" t="n">
-        <v>6845308</v>
+        <v>6845112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755789</v>
+        <v>125755621</v>
       </c>
       <c r="B85" t="n">
-        <v>78639</v>
+        <v>78732</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523480</v>
+        <v>523920</v>
       </c>
       <c r="R85" t="n">
-        <v>6845112</v>
+        <v>6845217</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,7 +8880,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125737510</v>
+        <v>125732736</v>
       </c>
       <c r="B86" t="n">
         <v>78731</v>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523957</v>
+        <v>523551</v>
       </c>
       <c r="R86" t="n">
-        <v>6845190</v>
+        <v>6845080</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -8977,10 +8977,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125732736</v>
+        <v>125737510</v>
       </c>
       <c r="B87" t="n">
-        <v>78730</v>
+        <v>78732</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523551</v>
+        <v>523957</v>
       </c>
       <c r="R87" t="n">
-        <v>6845080</v>
+        <v>6845190</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9074,10 +9074,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755783</v>
+        <v>125755700</v>
       </c>
       <c r="B88" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9085,21 +9085,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523644</v>
+        <v>523859</v>
       </c>
       <c r="R88" t="n">
-        <v>6845379</v>
+        <v>6845221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,10 +9171,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755700</v>
+        <v>125755697</v>
       </c>
       <c r="B89" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523859</v>
+        <v>523948</v>
       </c>
       <c r="R89" t="n">
-        <v>6845221</v>
+        <v>6845177</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9268,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755697</v>
+        <v>125755775</v>
       </c>
       <c r="B90" t="n">
-        <v>78972</v>
+        <v>92524</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523948</v>
+        <v>523541</v>
       </c>
       <c r="R90" t="n">
-        <v>6845177</v>
+        <v>6845044</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,45 +9365,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755775</v>
+        <v>125755654</v>
       </c>
       <c r="B91" t="n">
-        <v>92522</v>
+        <v>98341</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523541</v>
+        <v>523428</v>
       </c>
       <c r="R91" t="n">
-        <v>6845044</v>
+        <v>6845361</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9462,54 +9471,49 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755654</v>
+        <v>125732728</v>
       </c>
       <c r="B92" t="n">
-        <v>98339</v>
+        <v>92524</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523428</v>
+        <v>523590</v>
       </c>
       <c r="R92" t="n">
-        <v>6845361</v>
+        <v>6845030</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9556,22 +9560,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755553</v>
+        <v>125755783</v>
       </c>
       <c r="B93" t="n">
-        <v>79561</v>
+        <v>78640</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9579,21 +9583,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9603,10 +9607,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523626</v>
+        <v>523644</v>
       </c>
       <c r="R93" t="n">
-        <v>6845383</v>
+        <v>6845379</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9665,49 +9669,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125732728</v>
+        <v>125755553</v>
       </c>
       <c r="B94" t="n">
-        <v>92522</v>
+        <v>79562</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523590</v>
+        <v>523626</v>
       </c>
       <c r="R94" t="n">
-        <v>6845030</v>
+        <v>6845383</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9754,22 +9754,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125737769</v>
+        <v>125755781</v>
       </c>
       <c r="B95" t="n">
-        <v>79590</v>
+        <v>78640</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9777,21 +9777,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523967</v>
+        <v>523958</v>
       </c>
       <c r="R95" t="n">
-        <v>6845175</v>
+        <v>6845195</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9851,44 +9851,44 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755774</v>
+        <v>125755624</v>
       </c>
       <c r="B96" t="n">
-        <v>92522</v>
+        <v>78732</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523526</v>
+        <v>523853</v>
       </c>
       <c r="R96" t="n">
-        <v>6845095</v>
+        <v>6845279</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755781</v>
+        <v>125737769</v>
       </c>
       <c r="B97" t="n">
-        <v>78639</v>
+        <v>79591</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523958</v>
+        <v>523967</v>
       </c>
       <c r="R97" t="n">
-        <v>6845195</v>
+        <v>6845175</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10045,57 +10045,62 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755694</v>
+        <v>125755610</v>
       </c>
       <c r="B98" t="n">
-        <v>78972</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523979</v>
+        <v>523527</v>
       </c>
       <c r="R98" t="n">
-        <v>6845154</v>
+        <v>6845375</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10154,10 +10159,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755610</v>
+        <v>125755774</v>
       </c>
       <c r="B99" t="n">
-        <v>8447</v>
+        <v>92524</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10165,39 +10170,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523527</v>
+        <v>523526</v>
       </c>
       <c r="R99" t="n">
-        <v>6845375</v>
+        <v>6845095</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755624</v>
+        <v>125755694</v>
       </c>
       <c r="B100" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523853</v>
+        <v>523979</v>
       </c>
       <c r="R100" t="n">
-        <v>6845279</v>
+        <v>6845154</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125736651</v>
+        <v>125755712</v>
       </c>
       <c r="B101" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10388,10 +10388,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523722</v>
+        <v>523428</v>
       </c>
       <c r="R101" t="n">
-        <v>6845318</v>
+        <v>6845361</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10438,22 +10438,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125737335</v>
+        <v>125755550</v>
       </c>
       <c r="B102" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10481,17 +10481,17 @@
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523835</v>
+        <v>523604</v>
       </c>
       <c r="R102" t="n">
-        <v>6845199</v>
+        <v>6845013</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -10535,22 +10535,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125734280</v>
+        <v>125755547</v>
       </c>
       <c r="B103" t="n">
-        <v>78972</v>
+        <v>79591</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10558,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523482</v>
+        <v>523479</v>
       </c>
       <c r="R103" t="n">
-        <v>6845199</v>
+        <v>6845112</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,22 +10632,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B104" t="n">
-        <v>79590</v>
+        <v>79591</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10675,17 +10675,17 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R104" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10729,22 +10729,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125755547</v>
+        <v>125736651</v>
       </c>
       <c r="B105" t="n">
-        <v>79590</v>
+        <v>78973</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,21 +10752,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -10776,10 +10776,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523479</v>
+        <v>523722</v>
       </c>
       <c r="R105" t="n">
-        <v>6845112</v>
+        <v>6845318</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10826,22 +10826,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125755712</v>
+        <v>125734280</v>
       </c>
       <c r="B106" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10869,17 +10869,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523428</v>
+        <v>523482</v>
       </c>
       <c r="R106" t="n">
-        <v>6845361</v>
+        <v>6845199</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,12 +10923,12 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
@@ -10938,7 +10938,7 @@
         <v>125755620</v>
       </c>
       <c r="B107" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11032,10 +11032,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125736699</v>
+        <v>125755713</v>
       </c>
       <c r="B108" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523766</v>
+        <v>523332</v>
       </c>
       <c r="R108" t="n">
-        <v>6845303</v>
+        <v>6845377</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,22 +11117,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755713</v>
+        <v>125755706</v>
       </c>
       <c r="B109" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523332</v>
+        <v>523655</v>
       </c>
       <c r="R109" t="n">
-        <v>6845377</v>
+        <v>6845374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11226,10 +11226,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755706</v>
+        <v>125736699</v>
       </c>
       <c r="B110" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523655</v>
+        <v>523766</v>
       </c>
       <c r="R110" t="n">
-        <v>6845374</v>
+        <v>6845303</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,22 +11311,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755617</v>
+        <v>125737839</v>
       </c>
       <c r="B111" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11334,21 +11334,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523972</v>
+        <v>523967</v>
       </c>
       <c r="R111" t="n">
-        <v>6845173</v>
+        <v>6845175</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,22 +11408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125737839</v>
+        <v>125755617</v>
       </c>
       <c r="B112" t="n">
-        <v>79561</v>
+        <v>78732</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523967</v>
+        <v>523972</v>
       </c>
       <c r="R112" t="n">
-        <v>6845175</v>
+        <v>6845173</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11505,66 +11505,57 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B113" t="n">
-        <v>98339</v>
+        <v>78732</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R113" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11623,45 +11614,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B114" t="n">
-        <v>78731</v>
+        <v>98341</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R114" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11723,7 +11723,7 @@
         <v>125755555</v>
       </c>
       <c r="B115" t="n">
-        <v>90270</v>
+        <v>90272</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>125755601</v>
       </c>
       <c r="B116" t="n">
-        <v>92714</v>
+        <v>92716</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11914,50 +11914,45 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755608</v>
+        <v>125755784</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>78640</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>353</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523745</v>
+        <v>523606</v>
       </c>
       <c r="R117" t="n">
-        <v>6845284</v>
+        <v>6845378</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12016,45 +12011,54 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755631</v>
+        <v>125755563</v>
       </c>
       <c r="B118" t="n">
-        <v>78731</v>
+        <v>56844</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523636</v>
+        <v>523483</v>
       </c>
       <c r="R118" t="n">
-        <v>6845388</v>
+        <v>6845365</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12113,10 +12117,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755619</v>
+        <v>125732643</v>
       </c>
       <c r="B119" t="n">
-        <v>78731</v>
+        <v>79562</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12124,34 +12128,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523952</v>
+        <v>523617</v>
       </c>
       <c r="R119" t="n">
-        <v>6845185</v>
+        <v>6845031</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12198,57 +12202,62 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755784</v>
+        <v>125755608</v>
       </c>
       <c r="B120" t="n">
-        <v>78639</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523606</v>
+        <v>523745</v>
       </c>
       <c r="R120" t="n">
-        <v>6845378</v>
+        <v>6845284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12307,54 +12316,45 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755563</v>
+        <v>125736623</v>
       </c>
       <c r="B121" t="n">
-        <v>56843</v>
+        <v>78973</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523483</v>
+        <v>523689</v>
       </c>
       <c r="R121" t="n">
-        <v>6845365</v>
+        <v>6845339</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12401,22 +12401,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125736623</v>
+        <v>125755631</v>
       </c>
       <c r="B122" t="n">
-        <v>78972</v>
+        <v>78732</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12424,34 +12424,34 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523689</v>
+        <v>523636</v>
       </c>
       <c r="R122" t="n">
-        <v>6845339</v>
+        <v>6845388</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12498,22 +12498,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125732643</v>
+        <v>125755619</v>
       </c>
       <c r="B123" t="n">
-        <v>79561</v>
+        <v>78732</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,34 +12521,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523617</v>
+        <v>523952</v>
       </c>
       <c r="R123" t="n">
-        <v>6845031</v>
+        <v>6845185</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12595,22 +12595,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755780</v>
+        <v>125755704</v>
       </c>
       <c r="B124" t="n">
-        <v>78639</v>
+        <v>78973</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,21 +12618,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12642,10 +12642,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523584</v>
+        <v>523760</v>
       </c>
       <c r="R124" t="n">
-        <v>6845361</v>
+        <v>6845283</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755704</v>
+        <v>125734818</v>
       </c>
       <c r="B125" t="n">
-        <v>78972</v>
+        <v>91254</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,37 +12715,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523760</v>
+        <v>523643</v>
       </c>
       <c r="R125" t="n">
-        <v>6845283</v>
+        <v>6845282</v>
       </c>
       <c r="S125" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12789,12 +12789,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -12804,7 +12804,7 @@
         <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>91232</v>
+        <v>91234</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>125755715</v>
       </c>
       <c r="B127" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125732670</v>
+        <v>125755780</v>
       </c>
       <c r="B128" t="n">
-        <v>79590</v>
+        <v>78640</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,34 +13006,34 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523617</v>
+        <v>523584</v>
       </c>
       <c r="R128" t="n">
-        <v>6845031</v>
+        <v>6845361</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125734818</v>
+        <v>125732670</v>
       </c>
       <c r="B129" t="n">
-        <v>91252</v>
+        <v>79591</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,37 +13103,37 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R129" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S129" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -1354,45 +1354,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755708</v>
+        <v>125735595</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>98341</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523626</v>
+        <v>523492</v>
       </c>
       <c r="R9" t="n">
-        <v>6845380</v>
+        <v>6845165</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1439,19 +1443,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755716</v>
+        <v>125755708</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1486,10 +1490,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523477</v>
+        <v>523626</v>
       </c>
       <c r="R10" t="n">
-        <v>6845219</v>
+        <v>6845380</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,7 +1552,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755698</v>
+        <v>125755716</v>
       </c>
       <c r="B11" t="n">
         <v>78973</v>
@@ -1583,10 +1587,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523867</v>
+        <v>523477</v>
       </c>
       <c r="R11" t="n">
-        <v>6845227</v>
+        <v>6845219</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,7 +1649,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755711</v>
+        <v>125755698</v>
       </c>
       <c r="B12" t="n">
         <v>78973</v>
@@ -1680,10 +1684,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523443</v>
+        <v>523867</v>
       </c>
       <c r="R12" t="n">
-        <v>6845363</v>
+        <v>6845227</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1746,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125734647</v>
+        <v>125755711</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1773,17 +1777,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523611</v>
+        <v>523443</v>
       </c>
       <c r="R13" t="n">
-        <v>6845275</v>
+        <v>6845363</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1827,19 +1831,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125736051</v>
+        <v>125734647</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1870,17 +1874,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523418</v>
+        <v>523611</v>
       </c>
       <c r="R14" t="n">
-        <v>6845349</v>
+        <v>6845275</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,22 +1928,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755632</v>
+        <v>125736051</v>
       </c>
       <c r="B15" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,34 +1951,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523621</v>
+        <v>523418</v>
       </c>
       <c r="R15" t="n">
-        <v>6845375</v>
+        <v>6845349</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2021,61 +2025,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125735595</v>
+        <v>125755632</v>
       </c>
       <c r="B16" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523492</v>
+        <v>523621</v>
       </c>
       <c r="R16" t="n">
-        <v>6845165</v>
+        <v>6845375</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2122,12 +2122,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -4860,48 +4860,48 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125735128</v>
+        <v>125755658</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>91395</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523627</v>
+        <v>523487</v>
       </c>
       <c r="R45" t="n">
-        <v>6845420</v>
+        <v>6845098</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755626</v>
+        <v>125755792</v>
       </c>
       <c r="B46" t="n">
-        <v>78732</v>
+        <v>92518</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,21 +4968,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -4992,10 +4992,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523759</v>
+        <v>523992</v>
       </c>
       <c r="R46" t="n">
-        <v>6845238</v>
+        <v>6845170</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5028,6 +5028,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5054,10 +5059,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125737014</v>
+        <v>125755717</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5065,37 +5070,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523854</v>
+        <v>523466</v>
       </c>
       <c r="R47" t="n">
-        <v>6845289</v>
+        <v>6845180</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5139,44 +5144,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755658</v>
+        <v>125755552</v>
       </c>
       <c r="B48" t="n">
-        <v>91395</v>
+        <v>91199</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1503</v>
+        <v>5447</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5186,10 +5191,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523487</v>
+        <v>523424</v>
       </c>
       <c r="R48" t="n">
-        <v>6845098</v>
+        <v>6845383</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5248,10 +5253,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755792</v>
+        <v>125734241</v>
       </c>
       <c r="B49" t="n">
-        <v>92518</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5259,34 +5264,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523992</v>
+        <v>523492</v>
       </c>
       <c r="R49" t="n">
-        <v>6845170</v>
+        <v>6845165</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5321,11 +5326,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5338,19 +5338,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755717</v>
+        <v>125736099</v>
       </c>
       <c r="B50" t="n">
         <v>78973</v>
@@ -5381,14 +5381,14 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523466</v>
+        <v>523514</v>
       </c>
       <c r="R50" t="n">
-        <v>6845180</v>
+        <v>6845340</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5435,60 +5435,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755552</v>
+        <v>125735128</v>
       </c>
       <c r="B51" t="n">
-        <v>91199</v>
+        <v>79591</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523424</v>
+        <v>523627</v>
       </c>
       <c r="R51" t="n">
-        <v>6845383</v>
+        <v>6845420</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,22 +5532,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125734241</v>
+        <v>125755626</v>
       </c>
       <c r="B52" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5555,34 +5555,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523492</v>
+        <v>523759</v>
       </c>
       <c r="R52" t="n">
-        <v>6845165</v>
+        <v>6845238</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5629,22 +5629,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125736099</v>
+        <v>125737014</v>
       </c>
       <c r="B53" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5652,37 +5652,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523514</v>
+        <v>523854</v>
       </c>
       <c r="R53" t="n">
-        <v>6845340</v>
+        <v>6845289</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5726,12 +5726,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755630</v>
+        <v>125734739</v>
       </c>
       <c r="B67" t="n">
         <v>78732</v>
@@ -7049,17 +7049,17 @@
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523671</v>
+        <v>523608</v>
       </c>
       <c r="R67" t="n">
-        <v>6845353</v>
+        <v>6845309</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,22 +7103,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755629</v>
+        <v>125755709</v>
       </c>
       <c r="B68" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,21 +7126,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523679</v>
+        <v>523598</v>
       </c>
       <c r="R68" t="n">
-        <v>6845347</v>
+        <v>6845380</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,10 +7212,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755709</v>
+        <v>125755788</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,21 +7223,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7247,10 +7247,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523598</v>
+        <v>523460</v>
       </c>
       <c r="R69" t="n">
-        <v>6845380</v>
+        <v>6845221</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7309,10 +7309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755788</v>
+        <v>125755761</v>
       </c>
       <c r="B70" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7320,34 +7320,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523460</v>
+        <v>523387</v>
       </c>
       <c r="R70" t="n">
-        <v>6845221</v>
+        <v>6845410</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7406,10 +7411,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755761</v>
+        <v>125733520</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7417,39 +7422,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523387</v>
+        <v>523552</v>
       </c>
       <c r="R71" t="n">
-        <v>6845410</v>
+        <v>6845072</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,19 +7496,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125733520</v>
+        <v>125733632</v>
       </c>
       <c r="B72" t="n">
         <v>78973</v>
@@ -7543,10 +7543,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523552</v>
+        <v>523458</v>
       </c>
       <c r="R72" t="n">
-        <v>6845072</v>
+        <v>6845126</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7605,45 +7605,45 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125733632</v>
+        <v>125755598</v>
       </c>
       <c r="B73" t="n">
-        <v>78973</v>
+        <v>97219</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523458</v>
+        <v>523351</v>
       </c>
       <c r="R73" t="n">
-        <v>6845126</v>
+        <v>6845393</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7690,57 +7690,62 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755598</v>
+        <v>125738012</v>
       </c>
       <c r="B74" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523351</v>
+        <v>523967</v>
       </c>
       <c r="R74" t="n">
-        <v>6845393</v>
+        <v>6845175</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,22 +7792,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125738012</v>
+        <v>125755630</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7810,39 +7815,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523967</v>
+        <v>523671</v>
       </c>
       <c r="R75" t="n">
-        <v>6845175</v>
+        <v>6845353</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7889,19 +7889,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125734739</v>
+        <v>125755629</v>
       </c>
       <c r="B76" t="n">
         <v>78732</v>
@@ -7932,17 +7932,17 @@
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523608</v>
+        <v>523679</v>
       </c>
       <c r="R76" t="n">
-        <v>6845309</v>
+        <v>6845347</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -7986,12 +7986,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755789</v>
+        <v>125737510</v>
       </c>
       <c r="B84" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8697,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523480</v>
+        <v>523957</v>
       </c>
       <c r="R84" t="n">
-        <v>6845112</v>
+        <v>6845190</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8771,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755621</v>
+        <v>125755789</v>
       </c>
       <c r="B85" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8794,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8818,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523920</v>
+        <v>523480</v>
       </c>
       <c r="R85" t="n">
-        <v>6845217</v>
+        <v>6845112</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,10 +8880,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125732736</v>
+        <v>125755621</v>
       </c>
       <c r="B86" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,37 +8891,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523551</v>
+        <v>523920</v>
       </c>
       <c r="R86" t="n">
-        <v>6845080</v>
+        <v>6845217</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -8965,22 +8965,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125737510</v>
+        <v>125732736</v>
       </c>
       <c r="B87" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,21 +8988,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9012,10 +9012,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523957</v>
+        <v>523551</v>
       </c>
       <c r="R87" t="n">
-        <v>6845190</v>
+        <v>6845080</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9074,45 +9074,49 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755700</v>
+        <v>125732728</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>92524</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523859</v>
+        <v>523590</v>
       </c>
       <c r="R88" t="n">
-        <v>6845221</v>
+        <v>6845030</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9159,22 +9163,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755697</v>
+        <v>125755553</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9182,21 +9186,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9206,10 +9210,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523948</v>
+        <v>523626</v>
       </c>
       <c r="R89" t="n">
-        <v>6845177</v>
+        <v>6845383</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,32 +9272,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755775</v>
+        <v>125755700</v>
       </c>
       <c r="B90" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9307,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523541</v>
+        <v>523859</v>
       </c>
       <c r="R90" t="n">
-        <v>6845044</v>
+        <v>6845221</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,54 +9369,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755654</v>
+        <v>125755697</v>
       </c>
       <c r="B91" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523428</v>
+        <v>523948</v>
       </c>
       <c r="R91" t="n">
-        <v>6845361</v>
+        <v>6845177</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9471,7 +9466,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125732728</v>
+        <v>125755775</v>
       </c>
       <c r="B92" t="n">
         <v>92524</v>
@@ -9499,21 +9494,17 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523590</v>
+        <v>523541</v>
       </c>
       <c r="R92" t="n">
-        <v>6845030</v>
+        <v>6845044</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9560,12 +9551,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -9669,45 +9660,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755553</v>
+        <v>125755654</v>
       </c>
       <c r="B94" t="n">
-        <v>79562</v>
+        <v>98341</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523626</v>
+        <v>523428</v>
       </c>
       <c r="R94" t="n">
-        <v>6845383</v>
+        <v>6845361</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,32 +9766,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755781</v>
+        <v>125755774</v>
       </c>
       <c r="B95" t="n">
-        <v>78640</v>
+        <v>92524</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523958</v>
+        <v>523526</v>
       </c>
       <c r="R95" t="n">
-        <v>6845195</v>
+        <v>6845095</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9863,10 +9863,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755624</v>
+        <v>125755781</v>
       </c>
       <c r="B96" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523853</v>
+        <v>523958</v>
       </c>
       <c r="R96" t="n">
-        <v>6845279</v>
+        <v>6845195</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10159,32 +10159,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755774</v>
+        <v>125755694</v>
       </c>
       <c r="B99" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10194,10 +10194,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523526</v>
+        <v>523979</v>
       </c>
       <c r="R99" t="n">
-        <v>6845095</v>
+        <v>6845154</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755694</v>
+        <v>125755624</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10267,21 +10267,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10291,10 +10291,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523979</v>
+        <v>523853</v>
       </c>
       <c r="R100" t="n">
-        <v>6845154</v>
+        <v>6845279</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11517,45 +11517,54 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B113" t="n">
-        <v>78732</v>
+        <v>98341</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R113" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11614,54 +11623,45 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B114" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R114" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755555</v>
+        <v>125755784</v>
       </c>
       <c r="B115" t="n">
-        <v>90272</v>
+        <v>78640</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,21 +11731,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -11755,10 +11755,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523480</v>
+        <v>523606</v>
       </c>
       <c r="R115" t="n">
-        <v>6845111</v>
+        <v>6845378</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11817,45 +11817,54 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755601</v>
+        <v>125755563</v>
       </c>
       <c r="B116" t="n">
-        <v>92716</v>
+        <v>56844</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523463</v>
+        <v>523483</v>
       </c>
       <c r="R116" t="n">
-        <v>6845230</v>
+        <v>6845365</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11914,45 +11923,50 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755784</v>
+        <v>125755608</v>
       </c>
       <c r="B117" t="n">
-        <v>78640</v>
+        <v>8447</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>353</v>
+        <v>106545</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523606</v>
+        <v>523745</v>
       </c>
       <c r="R117" t="n">
-        <v>6845378</v>
+        <v>6845284</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12011,54 +12025,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755563</v>
+        <v>125736623</v>
       </c>
       <c r="B118" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523483</v>
+        <v>523689</v>
       </c>
       <c r="R118" t="n">
-        <v>6845365</v>
+        <v>6845339</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12105,22 +12110,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125732643</v>
+        <v>125755631</v>
       </c>
       <c r="B119" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12128,34 +12133,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523617</v>
+        <v>523636</v>
       </c>
       <c r="R119" t="n">
-        <v>6845031</v>
+        <v>6845388</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12202,62 +12207,57 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755608</v>
+        <v>125755619</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>78732</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523745</v>
+        <v>523952</v>
       </c>
       <c r="R120" t="n">
-        <v>6845284</v>
+        <v>6845185</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12316,10 +12316,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125736623</v>
+        <v>125755555</v>
       </c>
       <c r="B121" t="n">
-        <v>78973</v>
+        <v>90272</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12327,34 +12327,34 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523689</v>
+        <v>523480</v>
       </c>
       <c r="R121" t="n">
-        <v>6845339</v>
+        <v>6845111</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12401,22 +12401,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755631</v>
+        <v>125755601</v>
       </c>
       <c r="B122" t="n">
-        <v>78732</v>
+        <v>92716</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523636</v>
+        <v>523463</v>
       </c>
       <c r="R122" t="n">
-        <v>6845388</v>
+        <v>6845230</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12510,10 +12510,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755619</v>
+        <v>125732643</v>
       </c>
       <c r="B123" t="n">
-        <v>78732</v>
+        <v>79562</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,34 +12521,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523952</v>
+        <v>523617</v>
       </c>
       <c r="R123" t="n">
-        <v>6845185</v>
+        <v>6845031</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12595,12 +12595,12 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755643</v>
+        <v>125737411</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523816</v>
+        <v>523825</v>
       </c>
       <c r="R2" t="n">
-        <v>6845298</v>
+        <v>6845311</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755703</v>
+        <v>125734228</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523783</v>
+        <v>523467</v>
       </c>
       <c r="R3" t="n">
-        <v>6845289</v>
+        <v>6845121</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755705</v>
+        <v>125736529</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523728</v>
+        <v>523524</v>
       </c>
       <c r="R4" t="n">
-        <v>6845268</v>
+        <v>6845323</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125737411</v>
+        <v>125755703</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523825</v>
+        <v>523783</v>
       </c>
       <c r="R6" t="n">
-        <v>6845311</v>
+        <v>6845289</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,19 +1148,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734228</v>
+        <v>125755705</v>
       </c>
       <c r="B7" t="n">
         <v>78973</v>
@@ -1191,14 +1191,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523467</v>
+        <v>523728</v>
       </c>
       <c r="R7" t="n">
-        <v>6845121</v>
+        <v>6845268</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125736529</v>
+        <v>125755643</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,34 +1268,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523524</v>
+        <v>523816</v>
       </c>
       <c r="R8" t="n">
-        <v>6845323</v>
+        <v>6845298</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1342,64 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125735595</v>
+        <v>125734647</v>
       </c>
       <c r="B9" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523492</v>
+        <v>523611</v>
       </c>
       <c r="R9" t="n">
-        <v>6845165</v>
+        <v>6845275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1443,19 +1439,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755708</v>
+        <v>125736051</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1486,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523626</v>
+        <v>523418</v>
       </c>
       <c r="R10" t="n">
-        <v>6845380</v>
+        <v>6845349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1540,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755716</v>
+        <v>125755632</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1563,21 +1559,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1587,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523477</v>
+        <v>523621</v>
       </c>
       <c r="R11" t="n">
-        <v>6845219</v>
+        <v>6845375</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1649,45 +1645,49 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755698</v>
+        <v>125735595</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523867</v>
+        <v>523492</v>
       </c>
       <c r="R12" t="n">
-        <v>6845227</v>
+        <v>6845165</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,19 +1734,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755711</v>
+        <v>125755708</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1781,10 +1781,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523443</v>
+        <v>523626</v>
       </c>
       <c r="R13" t="n">
-        <v>6845363</v>
+        <v>6845380</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1843,7 +1843,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125734647</v>
+        <v>125755698</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1874,17 +1874,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523611</v>
+        <v>523867</v>
       </c>
       <c r="R14" t="n">
-        <v>6845275</v>
+        <v>6845227</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,19 +1928,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125736051</v>
+        <v>125755711</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1971,14 +1971,14 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523418</v>
+        <v>523443</v>
       </c>
       <c r="R15" t="n">
-        <v>6845349</v>
+        <v>6845363</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2025,22 +2025,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755632</v>
+        <v>125755716</v>
       </c>
       <c r="B16" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2048,21 +2048,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523621</v>
+        <v>523477</v>
       </c>
       <c r="R16" t="n">
-        <v>6845375</v>
+        <v>6845219</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,7 +2134,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755693</v>
+        <v>125733598</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,17 +2165,17 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523993</v>
+        <v>523483</v>
       </c>
       <c r="R17" t="n">
-        <v>6845158</v>
+        <v>6845118</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755710</v>
+        <v>125737958</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523572</v>
+        <v>523967</v>
       </c>
       <c r="R18" t="n">
-        <v>6845367</v>
+        <v>6845175</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2316,12 +2316,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2515,17 +2515,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125737958</v>
+        <v>125755693</v>
       </c>
       <c r="B21" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2533,21 +2533,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2557,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523967</v>
+        <v>523993</v>
       </c>
       <c r="R21" t="n">
-        <v>6845175</v>
+        <v>6845158</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2607,19 +2607,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125733598</v>
+        <v>125755710</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2650,17 +2650,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523483</v>
+        <v>523572</v>
       </c>
       <c r="R22" t="n">
-        <v>6845118</v>
+        <v>6845367</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,19 +2704,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755719</v>
+        <v>125735304</v>
       </c>
       <c r="B23" t="n">
         <v>78973</v>
@@ -2747,17 +2747,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523554</v>
+        <v>523580</v>
       </c>
       <c r="R23" t="n">
-        <v>6845068</v>
+        <v>6845417</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2801,22 +2801,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755790</v>
+        <v>125733851</v>
       </c>
       <c r="B24" t="n">
-        <v>78640</v>
+        <v>91256</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,37 +2824,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523486</v>
+        <v>523470</v>
       </c>
       <c r="R24" t="n">
-        <v>6845100</v>
+        <v>6845106</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2898,22 +2898,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755593</v>
+        <v>125736021</v>
       </c>
       <c r="B25" t="n">
-        <v>57652</v>
+        <v>79591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,39 +2921,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523520</v>
+        <v>523418</v>
       </c>
       <c r="R25" t="n">
-        <v>6845094</v>
+        <v>6845349</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -2988,11 +2983,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3005,22 +2995,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125736021</v>
+        <v>125755790</v>
       </c>
       <c r="B26" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,34 +3018,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523418</v>
+        <v>523486</v>
       </c>
       <c r="R26" t="n">
-        <v>6845349</v>
+        <v>6845100</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3102,19 +3092,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125735304</v>
+        <v>125755719</v>
       </c>
       <c r="B27" t="n">
         <v>78973</v>
@@ -3145,17 +3135,17 @@
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523580</v>
+        <v>523554</v>
       </c>
       <c r="R27" t="n">
-        <v>6845417</v>
+        <v>6845068</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3199,22 +3189,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125733851</v>
+        <v>125755593</v>
       </c>
       <c r="B28" t="n">
-        <v>91254</v>
+        <v>57652</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,37 +3212,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523470</v>
+        <v>523520</v>
       </c>
       <c r="R28" t="n">
-        <v>6845106</v>
+        <v>6845094</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3282,6 +3277,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3296,57 +3296,57 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755657</v>
+        <v>125733581</v>
       </c>
       <c r="B29" t="n">
-        <v>91395</v>
+        <v>78973</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523463</v>
+        <v>523528</v>
       </c>
       <c r="R29" t="n">
-        <v>6845211</v>
+        <v>6845135</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,19 +3393,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125733581</v>
+        <v>125737629</v>
       </c>
       <c r="B30" t="n">
         <v>78973</v>
@@ -3436,14 +3436,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523528</v>
+        <v>523960</v>
       </c>
       <c r="R30" t="n">
-        <v>6845135</v>
+        <v>6845161</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125737629</v>
+        <v>125735113</v>
       </c>
       <c r="B31" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,37 +3513,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523960</v>
+        <v>523630</v>
       </c>
       <c r="R31" t="n">
-        <v>6845161</v>
+        <v>6845423</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,44 +3587,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755634</v>
+        <v>125755657</v>
       </c>
       <c r="B32" t="n">
-        <v>78732</v>
+        <v>91397</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523498</v>
+        <v>523463</v>
       </c>
       <c r="R32" t="n">
-        <v>6845404</v>
+        <v>6845211</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125735113</v>
+        <v>125755545</v>
       </c>
       <c r="B33" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523630</v>
+        <v>523465</v>
       </c>
       <c r="R33" t="n">
-        <v>6845423</v>
+        <v>6845109</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3781,12 +3781,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3890,10 +3890,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755545</v>
+        <v>125755634</v>
       </c>
       <c r="B35" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3901,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3925,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523465</v>
+        <v>523498</v>
       </c>
       <c r="R35" t="n">
-        <v>6845109</v>
+        <v>6845404</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,10 +3987,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755695</v>
+        <v>125755565</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523990</v>
+        <v>523551</v>
       </c>
       <c r="R36" t="n">
-        <v>6845162</v>
+        <v>6845103</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755565</v>
+        <v>125755625</v>
       </c>
       <c r="B37" t="n">
-        <v>91254</v>
+        <v>78732</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523551</v>
+        <v>523850</v>
       </c>
       <c r="R37" t="n">
-        <v>6845103</v>
+        <v>6845286</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755625</v>
+        <v>125755695</v>
       </c>
       <c r="B38" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523850</v>
+        <v>523990</v>
       </c>
       <c r="R38" t="n">
-        <v>6845286</v>
+        <v>6845162</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755787</v>
+        <v>125734860</v>
       </c>
       <c r="B39" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,37 +4289,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523457</v>
+        <v>523673</v>
       </c>
       <c r="R39" t="n">
-        <v>6845237</v>
+        <v>6845294</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B40" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R40" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755539</v>
+        <v>125755787</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523924</v>
+        <v>523457</v>
       </c>
       <c r="R41" t="n">
-        <v>6845215</v>
+        <v>6845237</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125734860</v>
+        <v>125755539</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523673</v>
+        <v>523924</v>
       </c>
       <c r="R43" t="n">
-        <v>6845294</v>
+        <v>6845215</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125735540</v>
+        <v>125755544</v>
       </c>
       <c r="B44" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,37 +4774,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523479</v>
+        <v>523483</v>
       </c>
       <c r="R44" t="n">
-        <v>6845406</v>
+        <v>6845181</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4848,57 +4848,57 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755658</v>
+        <v>125734241</v>
       </c>
       <c r="B45" t="n">
-        <v>91395</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523487</v>
+        <v>523492</v>
       </c>
       <c r="R45" t="n">
-        <v>6845098</v>
+        <v>6845165</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755792</v>
+        <v>125735128</v>
       </c>
       <c r="B46" t="n">
-        <v>92518</v>
+        <v>79591</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523992</v>
+        <v>523627</v>
       </c>
       <c r="R46" t="n">
-        <v>6845170</v>
+        <v>6845420</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5028,11 +5028,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5047,19 +5042,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755717</v>
+        <v>125736099</v>
       </c>
       <c r="B47" t="n">
         <v>78973</v>
@@ -5090,14 +5085,14 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523466</v>
+        <v>523514</v>
       </c>
       <c r="R47" t="n">
-        <v>6845180</v>
+        <v>6845340</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5144,44 +5139,44 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755552</v>
+        <v>125755717</v>
       </c>
       <c r="B48" t="n">
-        <v>91199</v>
+        <v>78973</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5191,10 +5186,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523424</v>
+        <v>523466</v>
       </c>
       <c r="R48" t="n">
-        <v>6845383</v>
+        <v>6845180</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5253,10 +5248,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125734241</v>
+        <v>125755626</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5264,34 +5259,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523492</v>
+        <v>523759</v>
       </c>
       <c r="R49" t="n">
-        <v>6845165</v>
+        <v>6845238</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5338,22 +5333,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125736099</v>
+        <v>125737014</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5361,37 +5356,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523514</v>
+        <v>523854</v>
       </c>
       <c r="R50" t="n">
-        <v>6845340</v>
+        <v>6845289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5435,60 +5430,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125735128</v>
+        <v>125755658</v>
       </c>
       <c r="B51" t="n">
-        <v>79591</v>
+        <v>91397</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523627</v>
+        <v>523487</v>
       </c>
       <c r="R51" t="n">
-        <v>6845420</v>
+        <v>6845098</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5532,22 +5527,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755626</v>
+        <v>125755792</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>92520</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5555,21 +5550,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5579,10 +5574,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523759</v>
+        <v>523992</v>
       </c>
       <c r="R52" t="n">
-        <v>6845238</v>
+        <v>6845170</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5617,6 +5612,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -5634,55 +5634,55 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125737014</v>
+        <v>125755552</v>
       </c>
       <c r="B53" t="n">
-        <v>78732</v>
+        <v>91201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>5447</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523854</v>
+        <v>523424</v>
       </c>
       <c r="R53" t="n">
-        <v>6845289</v>
+        <v>6845383</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -5726,60 +5726,70 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755542</v>
+        <v>125736061</v>
       </c>
       <c r="B54" t="n">
-        <v>79591</v>
+        <v>56844</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523670</v>
+        <v>523643</v>
       </c>
       <c r="R54" t="n">
-        <v>6845353</v>
+        <v>6845391</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5823,22 +5833,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755543</v>
+        <v>125732709</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5846,37 +5856,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523460</v>
+        <v>523548</v>
       </c>
       <c r="R55" t="n">
-        <v>6845221</v>
+        <v>6845076</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5920,70 +5930,60 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125736061</v>
+        <v>125755542</v>
       </c>
       <c r="B56" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523643</v>
+        <v>523670</v>
       </c>
       <c r="R56" t="n">
-        <v>6845391</v>
+        <v>6845353</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6027,22 +6027,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755636</v>
+        <v>125755543</v>
       </c>
       <c r="B57" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6050,21 +6050,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6074,10 +6074,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523511</v>
+        <v>523460</v>
       </c>
       <c r="R57" t="n">
-        <v>6845102</v>
+        <v>6845221</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6136,7 +6136,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755627</v>
+        <v>125755636</v>
       </c>
       <c r="B58" t="n">
         <v>78732</v>
@@ -6171,10 +6171,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523755</v>
+        <v>523511</v>
       </c>
       <c r="R58" t="n">
-        <v>6845251</v>
+        <v>6845102</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,7 +6233,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755628</v>
+        <v>125755627</v>
       </c>
       <c r="B59" t="n">
         <v>78732</v>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523728</v>
+        <v>523755</v>
       </c>
       <c r="R59" t="n">
-        <v>6845279</v>
+        <v>6845251</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,7 +6330,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125732709</v>
+        <v>125755628</v>
       </c>
       <c r="B60" t="n">
         <v>78732</v>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523548</v>
+        <v>523728</v>
       </c>
       <c r="R60" t="n">
-        <v>6845076</v>
+        <v>6845279</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,69 +6415,60 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755647</v>
+        <v>125735892</v>
       </c>
       <c r="B61" t="n">
-        <v>98341</v>
+        <v>92526</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523408</v>
+        <v>523608</v>
       </c>
       <c r="R61" t="n">
-        <v>6845401</v>
+        <v>6845376</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6521,57 +6512,57 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125735892</v>
+        <v>125736672</v>
       </c>
       <c r="B62" t="n">
-        <v>92524</v>
+        <v>78973</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523608</v>
+        <v>523827</v>
       </c>
       <c r="R62" t="n">
-        <v>6845376</v>
+        <v>6845310</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6630,10 +6621,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125736672</v>
+        <v>125735337</v>
       </c>
       <c r="B63" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6641,34 +6632,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523827</v>
+        <v>523593</v>
       </c>
       <c r="R63" t="n">
-        <v>6845310</v>
+        <v>6845417</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6727,7 +6718,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125734972</v>
+        <v>125734655</v>
       </c>
       <c r="B64" t="n">
         <v>78732</v>
@@ -6758,17 +6749,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523675</v>
+        <v>523492</v>
       </c>
       <c r="R64" t="n">
-        <v>6845339</v>
+        <v>6845165</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6812,19 +6803,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125735337</v>
+        <v>125734972</v>
       </c>
       <c r="B65" t="n">
         <v>78732</v>
@@ -6859,10 +6850,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523593</v>
+        <v>523675</v>
       </c>
       <c r="R65" t="n">
-        <v>6845417</v>
+        <v>6845339</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -6921,45 +6912,54 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125734655</v>
+        <v>125755647</v>
       </c>
       <c r="B66" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523492</v>
+        <v>523408</v>
       </c>
       <c r="R66" t="n">
-        <v>6845165</v>
+        <v>6845401</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7006,22 +7006,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125734739</v>
+        <v>125738012</v>
       </c>
       <c r="B67" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,37 +7029,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523608</v>
+        <v>523967</v>
       </c>
       <c r="R67" t="n">
-        <v>6845309</v>
+        <v>6845175</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,19 +7108,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755709</v>
+        <v>125733520</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7146,14 +7151,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523598</v>
+        <v>523552</v>
       </c>
       <c r="R68" t="n">
-        <v>6845380</v>
+        <v>6845072</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7200,22 +7205,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755788</v>
+        <v>125733632</v>
       </c>
       <c r="B69" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,34 +7228,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523460</v>
+        <v>523458</v>
       </c>
       <c r="R69" t="n">
-        <v>6845221</v>
+        <v>6845126</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7297,22 +7302,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755761</v>
+        <v>125734739</v>
       </c>
       <c r="B70" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7320,42 +7325,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523387</v>
+        <v>523608</v>
       </c>
       <c r="R70" t="n">
-        <v>6845410</v>
+        <v>6845309</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7399,19 +7399,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125733520</v>
+        <v>125755709</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7442,14 +7442,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523552</v>
+        <v>523598</v>
       </c>
       <c r="R71" t="n">
-        <v>6845072</v>
+        <v>6845380</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125733632</v>
+        <v>125755788</v>
       </c>
       <c r="B72" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,34 +7519,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523458</v>
+        <v>523460</v>
       </c>
       <c r="R72" t="n">
-        <v>6845126</v>
+        <v>6845221</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,57 +7593,62 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755598</v>
+        <v>125755761</v>
       </c>
       <c r="B73" t="n">
-        <v>97219</v>
+        <v>57652</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523351</v>
+        <v>523387</v>
       </c>
       <c r="R73" t="n">
-        <v>6845393</v>
+        <v>6845410</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7702,50 +7707,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125738012</v>
+        <v>125755598</v>
       </c>
       <c r="B74" t="n">
-        <v>57652</v>
+        <v>97221</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523967</v>
+        <v>523351</v>
       </c>
       <c r="R74" t="n">
-        <v>6845175</v>
+        <v>6845393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7792,12 +7792,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7998,45 +7998,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755701</v>
+        <v>125735686</v>
       </c>
       <c r="B77" t="n">
-        <v>78973</v>
+        <v>98343</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523839</v>
+        <v>523418</v>
       </c>
       <c r="R77" t="n">
-        <v>6845286</v>
+        <v>6845349</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8083,44 +8087,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755707</v>
+        <v>125755794</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>91646</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8130,10 +8134,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523644</v>
+        <v>523385</v>
       </c>
       <c r="R78" t="n">
-        <v>6845389</v>
+        <v>6845416</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8168,6 +8172,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8185,39 +8194,39 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755794</v>
+        <v>125755701</v>
       </c>
       <c r="B79" t="n">
-        <v>91644</v>
+        <v>78973</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8227,10 +8236,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523385</v>
+        <v>523839</v>
       </c>
       <c r="R79" t="n">
-        <v>6845416</v>
+        <v>6845286</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8263,11 +8272,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8294,7 +8298,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755714</v>
+        <v>125755707</v>
       </c>
       <c r="B80" t="n">
         <v>78973</v>
@@ -8329,10 +8333,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523383</v>
+        <v>523644</v>
       </c>
       <c r="R80" t="n">
-        <v>6845391</v>
+        <v>6845389</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8488,49 +8492,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125735686</v>
+        <v>125755714</v>
       </c>
       <c r="B82" t="n">
-        <v>98341</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523418</v>
+        <v>523383</v>
       </c>
       <c r="R82" t="n">
-        <v>6845349</v>
+        <v>6845391</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,22 +8577,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755702</v>
+        <v>125737510</v>
       </c>
       <c r="B83" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8600,37 +8600,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523829</v>
+        <v>523957</v>
       </c>
       <c r="R83" t="n">
-        <v>6845308</v>
+        <v>6845190</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,19 +8674,19 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125737510</v>
+        <v>125755621</v>
       </c>
       <c r="B84" t="n">
         <v>78732</v>
@@ -8717,17 +8717,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523957</v>
+        <v>523920</v>
       </c>
       <c r="R84" t="n">
-        <v>6845190</v>
+        <v>6845217</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8771,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755789</v>
+        <v>125732736</v>
       </c>
       <c r="B85" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,37 +8794,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523480</v>
+        <v>523551</v>
       </c>
       <c r="R85" t="n">
-        <v>6845112</v>
+        <v>6845080</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8868,22 +8868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755621</v>
+        <v>125755789</v>
       </c>
       <c r="B86" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523920</v>
+        <v>523480</v>
       </c>
       <c r="R86" t="n">
-        <v>6845217</v>
+        <v>6845112</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8970,17 +8970,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125732736</v>
+        <v>125755702</v>
       </c>
       <c r="B87" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8988,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523551</v>
+        <v>523829</v>
       </c>
       <c r="R87" t="n">
-        <v>6845080</v>
+        <v>6845308</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,12 +9062,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9077,7 +9077,7 @@
         <v>125732728</v>
       </c>
       <c r="B88" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9175,10 +9175,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755553</v>
+        <v>125755700</v>
       </c>
       <c r="B89" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9186,21 +9186,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9210,10 +9210,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523626</v>
+        <v>523859</v>
       </c>
       <c r="R89" t="n">
-        <v>6845383</v>
+        <v>6845221</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9272,10 +9272,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755700</v>
+        <v>125755783</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9283,21 +9283,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9307,10 +9307,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523859</v>
+        <v>523644</v>
       </c>
       <c r="R90" t="n">
-        <v>6845221</v>
+        <v>6845379</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
@@ -9469,7 +9469,7 @@
         <v>125755775</v>
       </c>
       <c r="B92" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9556,52 +9556,61 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755783</v>
+        <v>125755654</v>
       </c>
       <c r="B93" t="n">
-        <v>78640</v>
+        <v>98343</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523644</v>
+        <v>523428</v>
       </c>
       <c r="R93" t="n">
-        <v>6845379</v>
+        <v>6845361</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9660,54 +9669,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755654</v>
+        <v>125755553</v>
       </c>
       <c r="B94" t="n">
-        <v>98341</v>
+        <v>79562</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523428</v>
+        <v>523626</v>
       </c>
       <c r="R94" t="n">
-        <v>6845361</v>
+        <v>6845383</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,32 +9766,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755774</v>
+        <v>125755781</v>
       </c>
       <c r="B95" t="n">
-        <v>92524</v>
+        <v>78640</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523526</v>
+        <v>523958</v>
       </c>
       <c r="R95" t="n">
-        <v>6845095</v>
+        <v>6845195</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755781</v>
+        <v>125755694</v>
       </c>
       <c r="B96" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523958</v>
+        <v>523979</v>
       </c>
       <c r="R96" t="n">
-        <v>6845195</v>
+        <v>6845154</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10057,10 +10057,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755610</v>
+        <v>125755774</v>
       </c>
       <c r="B98" t="n">
-        <v>8447</v>
+        <v>92526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10068,39 +10068,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523527</v>
+        <v>523526</v>
       </c>
       <c r="R98" t="n">
-        <v>6845375</v>
+        <v>6845095</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10152,52 +10147,57 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755694</v>
+        <v>125755610</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523979</v>
+        <v>523527</v>
       </c>
       <c r="R99" t="n">
-        <v>6845154</v>
+        <v>6845375</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755712</v>
+        <v>125755550</v>
       </c>
       <c r="B101" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10364,21 +10364,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10388,10 +10388,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523428</v>
+        <v>523604</v>
       </c>
       <c r="R101" t="n">
-        <v>6845361</v>
+        <v>6845013</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10450,10 +10450,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755550</v>
+        <v>125755712</v>
       </c>
       <c r="B102" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523604</v>
+        <v>523428</v>
       </c>
       <c r="R102" t="n">
-        <v>6845013</v>
+        <v>6845361</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125737335</v>
+        <v>125755620</v>
       </c>
       <c r="B104" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,37 +10655,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523835</v>
+        <v>523925</v>
       </c>
       <c r="R104" t="n">
-        <v>6845199</v>
+        <v>6845214</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -10729,19 +10729,19 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125736651</v>
+        <v>125734280</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10772,17 +10772,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523722</v>
+        <v>523482</v>
       </c>
       <c r="R105" t="n">
-        <v>6845318</v>
+        <v>6845199</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10826,19 +10826,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125734280</v>
+        <v>125736651</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10869,17 +10869,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523482</v>
+        <v>523722</v>
       </c>
       <c r="R106" t="n">
-        <v>6845199</v>
+        <v>6845318</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,22 +10923,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755620</v>
+        <v>125737335</v>
       </c>
       <c r="B107" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,37 +10946,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523925</v>
+        <v>523835</v>
       </c>
       <c r="R107" t="n">
-        <v>6845214</v>
+        <v>6845199</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11020,19 +11020,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755713</v>
+        <v>125736699</v>
       </c>
       <c r="B108" t="n">
         <v>78973</v>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523332</v>
+        <v>523766</v>
       </c>
       <c r="R108" t="n">
-        <v>6845377</v>
+        <v>6845303</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,22 +11117,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755706</v>
+        <v>125737839</v>
       </c>
       <c r="B109" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523655</v>
+        <v>523967</v>
       </c>
       <c r="R109" t="n">
-        <v>6845374</v>
+        <v>6845175</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11214,19 +11214,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125736699</v>
+        <v>125755713</v>
       </c>
       <c r="B110" t="n">
         <v>78973</v>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523766</v>
+        <v>523332</v>
       </c>
       <c r="R110" t="n">
-        <v>6845303</v>
+        <v>6845377</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,22 +11311,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125737839</v>
+        <v>125755706</v>
       </c>
       <c r="B111" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11334,21 +11334,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523967</v>
+        <v>523655</v>
       </c>
       <c r="R111" t="n">
-        <v>6845175</v>
+        <v>6845374</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,12 +11408,12 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
@@ -11517,54 +11517,45 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B113" t="n">
-        <v>98341</v>
+        <v>78732</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R113" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11623,45 +11614,54 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B114" t="n">
-        <v>78732</v>
+        <v>98343</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R114" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755784</v>
+        <v>125736623</v>
       </c>
       <c r="B115" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,34 +11731,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523606</v>
+        <v>523689</v>
       </c>
       <c r="R115" t="n">
-        <v>6845378</v>
+        <v>6845339</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11805,66 +11805,57 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755563</v>
+        <v>125732643</v>
       </c>
       <c r="B116" t="n">
-        <v>56844</v>
+        <v>79562</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523483</v>
+        <v>523617</v>
       </c>
       <c r="R116" t="n">
-        <v>6845365</v>
+        <v>6845031</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11911,62 +11902,57 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755608</v>
+        <v>125755555</v>
       </c>
       <c r="B117" t="n">
-        <v>8447</v>
+        <v>90274</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>106545</v>
+        <v>1962</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523745</v>
+        <v>523480</v>
       </c>
       <c r="R117" t="n">
-        <v>6845284</v>
+        <v>6845111</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12025,10 +12011,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125736623</v>
+        <v>125755601</v>
       </c>
       <c r="B118" t="n">
-        <v>78973</v>
+        <v>92718</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12036,34 +12022,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523689</v>
+        <v>523463</v>
       </c>
       <c r="R118" t="n">
-        <v>6845339</v>
+        <v>6845230</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12110,22 +12096,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755631</v>
+        <v>125755784</v>
       </c>
       <c r="B119" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12133,21 +12119,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12157,10 +12143,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523636</v>
+        <v>523606</v>
       </c>
       <c r="R119" t="n">
-        <v>6845388</v>
+        <v>6845378</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12212,52 +12198,57 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755619</v>
+        <v>125755608</v>
       </c>
       <c r="B120" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523952</v>
+        <v>523745</v>
       </c>
       <c r="R120" t="n">
-        <v>6845185</v>
+        <v>6845284</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12316,45 +12307,54 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755555</v>
+        <v>125755563</v>
       </c>
       <c r="B121" t="n">
-        <v>90272</v>
+        <v>56844</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523480</v>
+        <v>523483</v>
       </c>
       <c r="R121" t="n">
-        <v>6845111</v>
+        <v>6845365</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12413,10 +12413,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755601</v>
+        <v>125755631</v>
       </c>
       <c r="B122" t="n">
-        <v>92716</v>
+        <v>78732</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12424,21 +12424,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2079</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12448,10 +12448,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523463</v>
+        <v>523636</v>
       </c>
       <c r="R122" t="n">
-        <v>6845230</v>
+        <v>6845388</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12510,10 +12510,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125732643</v>
+        <v>125755619</v>
       </c>
       <c r="B123" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,34 +12521,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523617</v>
+        <v>523952</v>
       </c>
       <c r="R123" t="n">
-        <v>6845031</v>
+        <v>6845185</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12595,22 +12595,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755704</v>
+        <v>125734818</v>
       </c>
       <c r="B124" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,37 +12618,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523760</v>
+        <v>523643</v>
       </c>
       <c r="R124" t="n">
-        <v>6845283</v>
+        <v>6845282</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125734818</v>
+        <v>125732670</v>
       </c>
       <c r="B125" t="n">
-        <v>91254</v>
+        <v>79591</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,37 +12715,37 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>5442</v>
+        <v>6453</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R125" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S125" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T125" t="inlineStr">
         <is>
@@ -12789,12 +12789,12 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
@@ -12804,7 +12804,7 @@
         <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755715</v>
+        <v>125755780</v>
       </c>
       <c r="B127" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523450</v>
+        <v>523584</v>
       </c>
       <c r="R127" t="n">
-        <v>6845349</v>
+        <v>6845361</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12988,17 +12988,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755780</v>
+        <v>125755704</v>
       </c>
       <c r="B128" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523584</v>
+        <v>523760</v>
       </c>
       <c r="R128" t="n">
-        <v>6845361</v>
+        <v>6845283</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13092,10 +13092,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125732670</v>
+        <v>125755715</v>
       </c>
       <c r="B129" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,34 +13103,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523617</v>
+        <v>523450</v>
       </c>
       <c r="R129" t="n">
-        <v>6845031</v>
+        <v>6845349</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125734860</v>
+        <v>125734662</v>
       </c>
       <c r="B39" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,37 +4289,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523673</v>
+        <v>523492</v>
       </c>
       <c r="R39" t="n">
-        <v>6845294</v>
+        <v>6845165</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4363,22 +4363,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B40" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,37 +4386,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R40" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4460,22 +4460,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755787</v>
+        <v>125755544</v>
       </c>
       <c r="B41" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,21 +4483,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4507,10 +4507,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523457</v>
+        <v>523483</v>
       </c>
       <c r="R41" t="n">
-        <v>6845237</v>
+        <v>6845181</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4562,17 +4562,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734662</v>
+        <v>125734860</v>
       </c>
       <c r="B42" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4580,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523492</v>
+        <v>523673</v>
       </c>
       <c r="R42" t="n">
-        <v>6845165</v>
+        <v>6845294</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4654,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755539</v>
+        <v>125735540</v>
       </c>
       <c r="B43" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523924</v>
+        <v>523479</v>
       </c>
       <c r="R43" t="n">
-        <v>6845215</v>
+        <v>6845406</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755544</v>
+        <v>125755787</v>
       </c>
       <c r="B44" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,21 +4774,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4798,10 +4798,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523483</v>
+        <v>523457</v>
       </c>
       <c r="R44" t="n">
-        <v>6845181</v>
+        <v>6845237</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4853,17 +4853,17 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125734241</v>
+        <v>125735128</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523492</v>
+        <v>523627</v>
       </c>
       <c r="R45" t="n">
-        <v>6845165</v>
+        <v>6845420</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,22 +4945,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125735128</v>
+        <v>125736099</v>
       </c>
       <c r="B46" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4968,37 +4968,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523627</v>
+        <v>523514</v>
       </c>
       <c r="R46" t="n">
-        <v>6845420</v>
+        <v>6845340</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5042,22 +5042,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125736099</v>
+        <v>125737014</v>
       </c>
       <c r="B47" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5065,37 +5065,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523514</v>
+        <v>523854</v>
       </c>
       <c r="R47" t="n">
-        <v>6845340</v>
+        <v>6845289</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5139,12 +5139,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125737014</v>
+        <v>125734241</v>
       </c>
       <c r="B50" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5356,37 +5356,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523854</v>
+        <v>523492</v>
       </c>
       <c r="R50" t="n">
-        <v>6845289</v>
+        <v>6845165</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5430,12 +5430,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -7018,10 +7018,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125738012</v>
+        <v>125755630</v>
       </c>
       <c r="B67" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,39 +7029,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523967</v>
+        <v>523671</v>
       </c>
       <c r="R67" t="n">
-        <v>6845175</v>
+        <v>6845353</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7108,22 +7103,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125733520</v>
+        <v>125755629</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7131,34 +7126,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523552</v>
+        <v>523679</v>
       </c>
       <c r="R68" t="n">
-        <v>6845072</v>
+        <v>6845347</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7205,22 +7200,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125733632</v>
+        <v>125755761</v>
       </c>
       <c r="B69" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7228,34 +7223,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523458</v>
+        <v>523387</v>
       </c>
       <c r="R69" t="n">
-        <v>6845126</v>
+        <v>6845410</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7302,22 +7302,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125734739</v>
+        <v>125733520</v>
       </c>
       <c r="B70" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7325,37 +7325,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523608</v>
+        <v>523552</v>
       </c>
       <c r="R70" t="n">
-        <v>6845309</v>
+        <v>6845072</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7399,19 +7399,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755709</v>
+        <v>125733632</v>
       </c>
       <c r="B71" t="n">
         <v>78973</v>
@@ -7442,14 +7442,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523598</v>
+        <v>523458</v>
       </c>
       <c r="R71" t="n">
-        <v>6845380</v>
+        <v>6845126</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,22 +7496,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755788</v>
+        <v>125738012</v>
       </c>
       <c r="B72" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,34 +7519,39 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523460</v>
+        <v>523967</v>
       </c>
       <c r="R72" t="n">
-        <v>6845221</v>
+        <v>6845175</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7593,22 +7598,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755761</v>
+        <v>125734739</v>
       </c>
       <c r="B73" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,42 +7621,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523387</v>
+        <v>523608</v>
       </c>
       <c r="R73" t="n">
-        <v>6845410</v>
+        <v>6845309</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7695,44 +7695,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755598</v>
+        <v>125755709</v>
       </c>
       <c r="B74" t="n">
-        <v>97221</v>
+        <v>78973</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7742,10 +7742,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523351</v>
+        <v>523598</v>
       </c>
       <c r="R74" t="n">
-        <v>6845393</v>
+        <v>6845380</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7804,10 +7804,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755630</v>
+        <v>125755788</v>
       </c>
       <c r="B75" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7815,21 +7815,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7839,10 +7839,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523671</v>
+        <v>523460</v>
       </c>
       <c r="R75" t="n">
-        <v>6845353</v>
+        <v>6845221</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7894,39 +7894,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755629</v>
+        <v>125755598</v>
       </c>
       <c r="B76" t="n">
-        <v>78732</v>
+        <v>97221</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523679</v>
+        <v>523351</v>
       </c>
       <c r="R76" t="n">
-        <v>6845347</v>
+        <v>6845393</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9074,49 +9074,45 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125732728</v>
+        <v>125755700</v>
       </c>
       <c r="B88" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523590</v>
+        <v>523859</v>
       </c>
       <c r="R88" t="n">
-        <v>6845030</v>
+        <v>6845221</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9163,22 +9159,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755700</v>
+        <v>125755783</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9186,21 +9182,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9210,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523859</v>
+        <v>523644</v>
       </c>
       <c r="R89" t="n">
-        <v>6845221</v>
+        <v>6845379</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9265,17 +9261,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755783</v>
+        <v>125755697</v>
       </c>
       <c r="B90" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9283,21 +9279,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9307,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523644</v>
+        <v>523948</v>
       </c>
       <c r="R90" t="n">
-        <v>6845379</v>
+        <v>6845177</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9362,39 +9358,39 @@
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755697</v>
+        <v>125755775</v>
       </c>
       <c r="B91" t="n">
-        <v>78973</v>
+        <v>92526</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9404,10 +9400,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523948</v>
+        <v>523541</v>
       </c>
       <c r="R91" t="n">
-        <v>6845177</v>
+        <v>6845044</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9459,14 +9455,14 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755775</v>
+        <v>125732728</v>
       </c>
       <c r="B92" t="n">
         <v>92526</v>
@@ -9494,17 +9490,21 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523541</v>
+        <v>523590</v>
       </c>
       <c r="R92" t="n">
-        <v>6845044</v>
+        <v>6845030</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9551,12 +9551,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -11129,10 +11129,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125737839</v>
+        <v>125755617</v>
       </c>
       <c r="B109" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523967</v>
+        <v>523972</v>
       </c>
       <c r="R109" t="n">
-        <v>6845175</v>
+        <v>6845173</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11214,22 +11214,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755713</v>
+        <v>125737839</v>
       </c>
       <c r="B110" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523332</v>
+        <v>523967</v>
       </c>
       <c r="R110" t="n">
-        <v>6845377</v>
+        <v>6845175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,19 +11311,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755706</v>
+        <v>125755713</v>
       </c>
       <c r="B111" t="n">
         <v>78973</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523655</v>
+        <v>523332</v>
       </c>
       <c r="R111" t="n">
-        <v>6845374</v>
+        <v>6845377</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11420,10 +11420,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755617</v>
+        <v>125755706</v>
       </c>
       <c r="B112" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523972</v>
+        <v>523655</v>
       </c>
       <c r="R112" t="n">
-        <v>6845173</v>
+        <v>6845374</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12607,10 +12607,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125734818</v>
+        <v>125755557</v>
       </c>
       <c r="B124" t="n">
-        <v>91256</v>
+        <v>91236</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,37 +12618,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523643</v>
+        <v>523340</v>
       </c>
       <c r="R124" t="n">
-        <v>6845282</v>
+        <v>6845392</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125732670</v>
+        <v>125755780</v>
       </c>
       <c r="B125" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,34 +12715,34 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523617</v>
+        <v>523584</v>
       </c>
       <c r="R125" t="n">
-        <v>6845031</v>
+        <v>6845361</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12789,22 +12789,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755557</v>
+        <v>125755704</v>
       </c>
       <c r="B126" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523340</v>
+        <v>523760</v>
       </c>
       <c r="R126" t="n">
-        <v>6845392</v>
+        <v>6845283</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755780</v>
+        <v>125755715</v>
       </c>
       <c r="B127" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523584</v>
+        <v>523450</v>
       </c>
       <c r="R127" t="n">
-        <v>6845361</v>
+        <v>6845349</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12988,17 +12988,17 @@
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125755704</v>
+        <v>125734818</v>
       </c>
       <c r="B128" t="n">
-        <v>78973</v>
+        <v>91256</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523760</v>
+        <v>523643</v>
       </c>
       <c r="R128" t="n">
-        <v>6845283</v>
+        <v>6845282</v>
       </c>
       <c r="S128" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,22 +13080,22 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>125755715</v>
+        <v>125732670</v>
       </c>
       <c r="B129" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13103,34 +13103,34 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>523450</v>
+        <v>523617</v>
       </c>
       <c r="R129" t="n">
-        <v>6845349</v>
+        <v>6845031</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13177,12 +13177,12 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125737411</v>
+        <v>125755703</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523825</v>
+        <v>523783</v>
       </c>
       <c r="R2" t="n">
-        <v>6845311</v>
+        <v>6845289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125734228</v>
+        <v>125755705</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -803,14 +803,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523467</v>
+        <v>523728</v>
       </c>
       <c r="R3" t="n">
-        <v>6845121</v>
+        <v>6845268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125736529</v>
+        <v>125737411</v>
       </c>
       <c r="B4" t="n">
         <v>78973</v>
@@ -900,14 +900,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523524</v>
+        <v>523825</v>
       </c>
       <c r="R4" t="n">
-        <v>6845323</v>
+        <v>6845311</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125734476</v>
+        <v>125736529</v>
       </c>
       <c r="B5" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523492</v>
+        <v>523524</v>
       </c>
       <c r="R5" t="n">
-        <v>6845165</v>
+        <v>6845323</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755703</v>
+        <v>125734228</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523783</v>
+        <v>523467</v>
       </c>
       <c r="R6" t="n">
-        <v>6845289</v>
+        <v>6845121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755705</v>
+        <v>125734476</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,34 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523728</v>
+        <v>523492</v>
       </c>
       <c r="R7" t="n">
-        <v>6845268</v>
+        <v>6845165</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1245,12 +1245,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125734647</v>
+        <v>125755708</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523611</v>
+        <v>523626</v>
       </c>
       <c r="R9" t="n">
-        <v>6845275</v>
+        <v>6845380</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,19 +1439,19 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125736051</v>
+        <v>125755711</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1482,14 +1482,14 @@
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523418</v>
+        <v>523443</v>
       </c>
       <c r="R10" t="n">
-        <v>6845349</v>
+        <v>6845363</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755632</v>
+        <v>125734647</v>
       </c>
       <c r="B11" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523621</v>
+        <v>523611</v>
       </c>
       <c r="R11" t="n">
-        <v>6845375</v>
+        <v>6845275</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,12 +1633,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1648,7 +1648,7 @@
         <v>125735595</v>
       </c>
       <c r="B12" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755708</v>
+        <v>125736051</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1777,14 +1777,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523626</v>
+        <v>523418</v>
       </c>
       <c r="R13" t="n">
-        <v>6845380</v>
+        <v>6845349</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1831,22 +1831,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755698</v>
+        <v>125755632</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,21 +1854,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1878,10 +1878,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523867</v>
+        <v>523621</v>
       </c>
       <c r="R14" t="n">
-        <v>6845227</v>
+        <v>6845375</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1940,7 +1940,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755711</v>
+        <v>125755716</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1975,10 +1975,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523443</v>
+        <v>523477</v>
       </c>
       <c r="R15" t="n">
-        <v>6845363</v>
+        <v>6845219</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,7 +2037,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2072,10 +2072,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R16" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2134,10 +2134,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125733598</v>
+        <v>125737958</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,37 +2145,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523483</v>
+        <v>523967</v>
       </c>
       <c r="R17" t="n">
-        <v>6845118</v>
+        <v>6845175</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2219,22 +2219,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125737958</v>
+        <v>125755710</v>
       </c>
       <c r="B18" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2242,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523967</v>
+        <v>523572</v>
       </c>
       <c r="R18" t="n">
-        <v>6845175</v>
+        <v>6845367</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2316,12 +2316,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2418,7 +2418,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755710</v>
+        <v>125733598</v>
       </c>
       <c r="B22" t="n">
         <v>78973</v>
@@ -2650,17 +2650,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523572</v>
+        <v>523483</v>
       </c>
       <c r="R22" t="n">
-        <v>6845367</v>
+        <v>6845118</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,22 +2704,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125735304</v>
+        <v>125736021</v>
       </c>
       <c r="B23" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2727,37 +2727,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523580</v>
+        <v>523418</v>
       </c>
       <c r="R23" t="n">
-        <v>6845417</v>
+        <v>6845349</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2801,22 +2801,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125733851</v>
+        <v>125755719</v>
       </c>
       <c r="B24" t="n">
-        <v>91256</v>
+        <v>78973</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,37 +2824,37 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523470</v>
+        <v>523554</v>
       </c>
       <c r="R24" t="n">
-        <v>6845106</v>
+        <v>6845068</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -2898,22 +2898,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125736021</v>
+        <v>125735304</v>
       </c>
       <c r="B25" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,37 +2921,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523418</v>
+        <v>523580</v>
       </c>
       <c r="R25" t="n">
-        <v>6845349</v>
+        <v>6845417</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -2995,22 +2995,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755790</v>
+        <v>125733851</v>
       </c>
       <c r="B26" t="n">
-        <v>78640</v>
+        <v>91258</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,37 +3018,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523486</v>
+        <v>523470</v>
       </c>
       <c r="R26" t="n">
-        <v>6845100</v>
+        <v>6845106</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3092,22 +3092,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755719</v>
+        <v>125755790</v>
       </c>
       <c r="B27" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,21 +3115,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523554</v>
+        <v>523486</v>
       </c>
       <c r="R27" t="n">
-        <v>6845068</v>
+        <v>6845100</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3308,45 +3308,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125733581</v>
+        <v>125755657</v>
       </c>
       <c r="B29" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523528</v>
+        <v>523463</v>
       </c>
       <c r="R29" t="n">
-        <v>6845135</v>
+        <v>6845211</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3393,22 +3393,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125737629</v>
+        <v>125755549</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523960</v>
+        <v>523541</v>
       </c>
       <c r="R30" t="n">
-        <v>6845161</v>
+        <v>6845054</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3490,22 +3490,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125735113</v>
+        <v>125755545</v>
       </c>
       <c r="B31" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,37 +3513,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523630</v>
+        <v>523465</v>
       </c>
       <c r="R31" t="n">
-        <v>6845423</v>
+        <v>6845109</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3587,57 +3587,57 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755657</v>
+        <v>125733581</v>
       </c>
       <c r="B32" t="n">
-        <v>91397</v>
+        <v>78973</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523463</v>
+        <v>523528</v>
       </c>
       <c r="R32" t="n">
-        <v>6845211</v>
+        <v>6845135</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3684,22 +3684,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755545</v>
+        <v>125737629</v>
       </c>
       <c r="B33" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523465</v>
+        <v>523960</v>
       </c>
       <c r="R33" t="n">
-        <v>6845109</v>
+        <v>6845161</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3781,22 +3781,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755549</v>
+        <v>125755634</v>
       </c>
       <c r="B34" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3804,21 +3804,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523541</v>
+        <v>523498</v>
       </c>
       <c r="R34" t="n">
-        <v>6845054</v>
+        <v>6845404</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125755634</v>
+        <v>125735113</v>
       </c>
       <c r="B35" t="n">
         <v>78732</v>
@@ -3921,17 +3921,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523498</v>
+        <v>523630</v>
       </c>
       <c r="R35" t="n">
-        <v>6845404</v>
+        <v>6845423</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -3975,22 +3975,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755565</v>
+        <v>125755695</v>
       </c>
       <c r="B36" t="n">
-        <v>91256</v>
+        <v>78973</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,21 +3998,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4022,10 +4022,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523551</v>
+        <v>523990</v>
       </c>
       <c r="R36" t="n">
-        <v>6845103</v>
+        <v>6845162</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,10 +4084,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755625</v>
+        <v>125755565</v>
       </c>
       <c r="B37" t="n">
-        <v>78732</v>
+        <v>91258</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4095,21 +4095,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4119,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523850</v>
+        <v>523551</v>
       </c>
       <c r="R37" t="n">
-        <v>6845286</v>
+        <v>6845103</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4181,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755695</v>
+        <v>125755625</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4192,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4216,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523990</v>
+        <v>523850</v>
       </c>
       <c r="R38" t="n">
-        <v>6845162</v>
+        <v>6845286</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,10 +4278,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125734662</v>
+        <v>125755544</v>
       </c>
       <c r="B39" t="n">
-        <v>78731</v>
+        <v>79591</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,34 +4289,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523492</v>
+        <v>523483</v>
       </c>
       <c r="R39" t="n">
-        <v>6845165</v>
+        <v>6845181</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4363,12 +4363,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4472,10 +4472,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4483,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R41" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,12 +4557,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4666,10 +4666,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125735540</v>
+        <v>125755787</v>
       </c>
       <c r="B43" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,37 +4677,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523479</v>
+        <v>523457</v>
       </c>
       <c r="R43" t="n">
-        <v>6845406</v>
+        <v>6845237</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4751,22 +4751,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755787</v>
+        <v>125734662</v>
       </c>
       <c r="B44" t="n">
-        <v>78640</v>
+        <v>78731</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,34 +4774,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523457</v>
+        <v>523492</v>
       </c>
       <c r="R44" t="n">
-        <v>6845237</v>
+        <v>6845165</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4848,22 +4848,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125735128</v>
+        <v>125734241</v>
       </c>
       <c r="B45" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523627</v>
+        <v>523492</v>
       </c>
       <c r="R45" t="n">
-        <v>6845420</v>
+        <v>6845165</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4945,12 +4945,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5054,7 +5054,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125737014</v>
+        <v>125755626</v>
       </c>
       <c r="B47" t="n">
         <v>78732</v>
@@ -5085,17 +5085,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523854</v>
+        <v>523759</v>
       </c>
       <c r="R47" t="n">
-        <v>6845289</v>
+        <v>6845238</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5139,22 +5139,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755717</v>
+        <v>125735128</v>
       </c>
       <c r="B48" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5162,37 +5162,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523466</v>
+        <v>523627</v>
       </c>
       <c r="R48" t="n">
-        <v>6845180</v>
+        <v>6845420</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5236,19 +5236,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125755626</v>
+        <v>125737014</v>
       </c>
       <c r="B49" t="n">
         <v>78732</v>
@@ -5279,17 +5279,17 @@
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523759</v>
+        <v>523854</v>
       </c>
       <c r="R49" t="n">
-        <v>6845238</v>
+        <v>6845289</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5333,57 +5333,57 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125734241</v>
+        <v>125755658</v>
       </c>
       <c r="B50" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523492</v>
+        <v>523487</v>
       </c>
       <c r="R50" t="n">
-        <v>6845165</v>
+        <v>6845098</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5430,44 +5430,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755658</v>
+        <v>125755717</v>
       </c>
       <c r="B51" t="n">
-        <v>91397</v>
+        <v>78973</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1503</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5477,10 +5477,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523487</v>
+        <v>523466</v>
       </c>
       <c r="R51" t="n">
-        <v>6845098</v>
+        <v>6845180</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5532,7 +5532,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5542,7 +5542,7 @@
         <v>125755792</v>
       </c>
       <c r="B52" t="n">
-        <v>92520</v>
+        <v>92522</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5634,7 +5634,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5644,7 +5644,7 @@
         <v>125755552</v>
       </c>
       <c r="B53" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5738,58 +5738,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125736061</v>
+        <v>125755543</v>
       </c>
       <c r="B54" t="n">
-        <v>56844</v>
+        <v>79591</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523643</v>
+        <v>523460</v>
       </c>
       <c r="R54" t="n">
-        <v>6845391</v>
+        <v>6845221</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -5833,22 +5823,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125732709</v>
+        <v>125755542</v>
       </c>
       <c r="B55" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5856,37 +5846,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523548</v>
+        <v>523670</v>
       </c>
       <c r="R55" t="n">
-        <v>6845076</v>
+        <v>6845353</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5930,22 +5920,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755542</v>
+        <v>125755636</v>
       </c>
       <c r="B56" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5953,21 +5943,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5977,10 +5967,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523670</v>
+        <v>523511</v>
       </c>
       <c r="R56" t="n">
-        <v>6845353</v>
+        <v>6845102</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6039,10 +6029,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755543</v>
+        <v>125755627</v>
       </c>
       <c r="B57" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6050,21 +6040,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6074,10 +6064,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523460</v>
+        <v>523755</v>
       </c>
       <c r="R57" t="n">
-        <v>6845221</v>
+        <v>6845251</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6136,7 +6126,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755636</v>
+        <v>125755628</v>
       </c>
       <c r="B58" t="n">
         <v>78732</v>
@@ -6171,10 +6161,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523511</v>
+        <v>523728</v>
       </c>
       <c r="R58" t="n">
-        <v>6845102</v>
+        <v>6845279</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6233,48 +6223,58 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755627</v>
+        <v>125736061</v>
       </c>
       <c r="B59" t="n">
-        <v>78732</v>
+        <v>56844</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523755</v>
+        <v>523643</v>
       </c>
       <c r="R59" t="n">
-        <v>6845251</v>
+        <v>6845391</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6318,19 +6318,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755628</v>
+        <v>125732709</v>
       </c>
       <c r="B60" t="n">
         <v>78732</v>
@@ -6361,17 +6361,17 @@
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523728</v>
+        <v>523548</v>
       </c>
       <c r="R60" t="n">
-        <v>6845279</v>
+        <v>6845076</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,60 +6415,69 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125735892</v>
+        <v>125755647</v>
       </c>
       <c r="B61" t="n">
-        <v>92526</v>
+        <v>98345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523608</v>
+        <v>523408</v>
       </c>
       <c r="R61" t="n">
-        <v>6845376</v>
+        <v>6845401</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6512,12 +6521,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6621,32 +6630,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125735337</v>
+        <v>125735892</v>
       </c>
       <c r="B63" t="n">
-        <v>78732</v>
+        <v>92528</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6656,10 +6665,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523593</v>
+        <v>523608</v>
       </c>
       <c r="R63" t="n">
-        <v>6845417</v>
+        <v>6845376</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -6718,7 +6727,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125734655</v>
+        <v>125735337</v>
       </c>
       <c r="B64" t="n">
         <v>78732</v>
@@ -6749,17 +6758,17 @@
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523492</v>
+        <v>523593</v>
       </c>
       <c r="R64" t="n">
-        <v>6845165</v>
+        <v>6845417</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6803,19 +6812,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734972</v>
+        <v>125734655</v>
       </c>
       <c r="B65" t="n">
         <v>78732</v>
@@ -6846,17 +6855,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523675</v>
+        <v>523492</v>
       </c>
       <c r="R65" t="n">
-        <v>6845339</v>
+        <v>6845165</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -6900,69 +6909,60 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125755647</v>
+        <v>125734972</v>
       </c>
       <c r="B66" t="n">
-        <v>98343</v>
+        <v>78732</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523408</v>
+        <v>523675</v>
       </c>
       <c r="R66" t="n">
-        <v>6845401</v>
+        <v>6845339</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7006,22 +7006,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755630</v>
+        <v>125755788</v>
       </c>
       <c r="B67" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,21 +7029,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7053,10 +7053,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523671</v>
+        <v>523460</v>
       </c>
       <c r="R67" t="n">
-        <v>6845353</v>
+        <v>6845221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7115,10 +7115,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755629</v>
+        <v>125733632</v>
       </c>
       <c r="B68" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7126,34 +7126,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523679</v>
+        <v>523458</v>
       </c>
       <c r="R68" t="n">
-        <v>6845347</v>
+        <v>6845126</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7200,22 +7200,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755761</v>
+        <v>125755630</v>
       </c>
       <c r="B69" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,39 +7223,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523387</v>
+        <v>523671</v>
       </c>
       <c r="R69" t="n">
-        <v>6845410</v>
+        <v>6845353</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,10 +7309,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125733520</v>
+        <v>125755629</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7325,34 +7320,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523552</v>
+        <v>523679</v>
       </c>
       <c r="R70" t="n">
-        <v>6845072</v>
+        <v>6845347</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7399,22 +7394,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125733632</v>
+        <v>125738012</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>57652</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7422,34 +7417,39 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523458</v>
+        <v>523967</v>
       </c>
       <c r="R71" t="n">
-        <v>6845126</v>
+        <v>6845175</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125738012</v>
+        <v>125734739</v>
       </c>
       <c r="B72" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,42 +7519,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523967</v>
+        <v>523608</v>
       </c>
       <c r="R72" t="n">
-        <v>6845175</v>
+        <v>6845309</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7598,60 +7593,60 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125734739</v>
+        <v>125755598</v>
       </c>
       <c r="B73" t="n">
-        <v>78732</v>
+        <v>97223</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523608</v>
+        <v>523351</v>
       </c>
       <c r="R73" t="n">
-        <v>6845309</v>
+        <v>6845393</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7695,19 +7690,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755709</v>
+        <v>125733520</v>
       </c>
       <c r="B74" t="n">
         <v>78973</v>
@@ -7738,14 +7733,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523598</v>
+        <v>523552</v>
       </c>
       <c r="R74" t="n">
-        <v>6845380</v>
+        <v>6845072</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7792,22 +7787,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755788</v>
+        <v>125755761</v>
       </c>
       <c r="B75" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7815,34 +7810,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523460</v>
+        <v>523387</v>
       </c>
       <c r="R75" t="n">
-        <v>6845221</v>
+        <v>6845410</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7894,39 +7894,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755598</v>
+        <v>125755709</v>
       </c>
       <c r="B76" t="n">
-        <v>97221</v>
+        <v>78973</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7936,10 +7936,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523351</v>
+        <v>523598</v>
       </c>
       <c r="R76" t="n">
-        <v>6845393</v>
+        <v>6845380</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7998,49 +7998,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125735686</v>
+        <v>125755794</v>
       </c>
       <c r="B77" t="n">
-        <v>98343</v>
+        <v>91648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>4217</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523418</v>
+        <v>523385</v>
       </c>
       <c r="R77" t="n">
-        <v>6845349</v>
+        <v>6845416</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8075,6 +8071,11 @@
           <t>2025-06-06</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -8087,44 +8088,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755794</v>
+        <v>125755714</v>
       </c>
       <c r="B78" t="n">
-        <v>91646</v>
+        <v>78973</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8134,10 +8135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523385</v>
+        <v>523383</v>
       </c>
       <c r="R78" t="n">
-        <v>6845416</v>
+        <v>6845391</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8172,11 +8173,6 @@
           <t>2025-06-06</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -8194,7 +8190,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -8492,45 +8488,49 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755714</v>
+        <v>125735686</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>98345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523383</v>
+        <v>523418</v>
       </c>
       <c r="R82" t="n">
-        <v>6845391</v>
+        <v>6845349</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8577,12 +8577,12 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
@@ -8686,10 +8686,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755621</v>
+        <v>125755789</v>
       </c>
       <c r="B84" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,21 +8697,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8721,10 +8721,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523920</v>
+        <v>523480</v>
       </c>
       <c r="R84" t="n">
-        <v>6845217</v>
+        <v>6845112</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8783,10 +8783,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125732736</v>
+        <v>125755702</v>
       </c>
       <c r="B85" t="n">
-        <v>78731</v>
+        <v>78973</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,37 +8794,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523551</v>
+        <v>523829</v>
       </c>
       <c r="R85" t="n">
-        <v>6845080</v>
+        <v>6845308</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8868,22 +8868,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755789</v>
+        <v>125755621</v>
       </c>
       <c r="B86" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,21 +8891,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8915,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523480</v>
+        <v>523920</v>
       </c>
       <c r="R86" t="n">
-        <v>6845112</v>
+        <v>6845217</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8970,17 +8970,17 @@
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755702</v>
+        <v>125732736</v>
       </c>
       <c r="B87" t="n">
-        <v>78973</v>
+        <v>78731</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8988,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523829</v>
+        <v>523551</v>
       </c>
       <c r="R87" t="n">
-        <v>6845308</v>
+        <v>6845080</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,19 +9062,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755700</v>
+        <v>125755697</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9109,10 +9109,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523859</v>
+        <v>523948</v>
       </c>
       <c r="R88" t="n">
-        <v>6845221</v>
+        <v>6845177</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,10 +9171,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755783</v>
+        <v>125755700</v>
       </c>
       <c r="B89" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9182,21 +9182,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9206,10 +9206,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523644</v>
+        <v>523859</v>
       </c>
       <c r="R89" t="n">
-        <v>6845379</v>
+        <v>6845221</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9261,17 +9261,17 @@
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755697</v>
+        <v>125755783</v>
       </c>
       <c r="B90" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9279,21 +9279,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9303,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523948</v>
+        <v>523644</v>
       </c>
       <c r="R90" t="n">
-        <v>6845177</v>
+        <v>6845379</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9368,7 +9368,7 @@
         <v>125755775</v>
       </c>
       <c r="B91" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -9465,7 +9465,7 @@
         <v>125732728</v>
       </c>
       <c r="B92" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9563,54 +9563,45 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755654</v>
+        <v>125755553</v>
       </c>
       <c r="B93" t="n">
-        <v>98343</v>
+        <v>79562</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523428</v>
+        <v>523626</v>
       </c>
       <c r="R93" t="n">
-        <v>6845361</v>
+        <v>6845383</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9669,45 +9660,54 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755553</v>
+        <v>125755654</v>
       </c>
       <c r="B94" t="n">
-        <v>79562</v>
+        <v>98345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523626</v>
+        <v>523428</v>
       </c>
       <c r="R94" t="n">
-        <v>6845383</v>
+        <v>6845361</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,10 +9766,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755781</v>
+        <v>125755624</v>
       </c>
       <c r="B95" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9777,21 +9777,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9801,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523958</v>
+        <v>523853</v>
       </c>
       <c r="R95" t="n">
-        <v>6845195</v>
+        <v>6845279</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755694</v>
+        <v>125737769</v>
       </c>
       <c r="B96" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9874,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9898,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523979</v>
+        <v>523967</v>
       </c>
       <c r="R96" t="n">
-        <v>6845154</v>
+        <v>6845175</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,22 +9948,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125737769</v>
+        <v>125755781</v>
       </c>
       <c r="B97" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9971,21 +9971,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -9995,10 +9995,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523967</v>
+        <v>523958</v>
       </c>
       <c r="R97" t="n">
-        <v>6845175</v>
+        <v>6845195</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10045,44 +10045,44 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755774</v>
+        <v>125755694</v>
       </c>
       <c r="B98" t="n">
-        <v>92526</v>
+        <v>78973</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10092,10 +10092,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523526</v>
+        <v>523979</v>
       </c>
       <c r="R98" t="n">
-        <v>6845095</v>
+        <v>6845154</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10147,17 +10147,17 @@
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755610</v>
+        <v>125755774</v>
       </c>
       <c r="B99" t="n">
-        <v>8447</v>
+        <v>92528</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10165,39 +10165,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P99" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523527</v>
+        <v>523526</v>
       </c>
       <c r="R99" t="n">
-        <v>6845375</v>
+        <v>6845095</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10256,45 +10251,50 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755624</v>
+        <v>125755610</v>
       </c>
       <c r="B100" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523853</v>
+        <v>523527</v>
       </c>
       <c r="R100" t="n">
-        <v>6845279</v>
+        <v>6845375</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10353,7 +10353,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B101" t="n">
         <v>79591</v>
@@ -10384,17 +10384,17 @@
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R101" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,22 +10438,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755712</v>
+        <v>125755550</v>
       </c>
       <c r="B102" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,21 +10461,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10485,10 +10485,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523428</v>
+        <v>523604</v>
       </c>
       <c r="R102" t="n">
-        <v>6845361</v>
+        <v>6845013</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755620</v>
+        <v>125755712</v>
       </c>
       <c r="B104" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10655,21 +10655,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -10679,10 +10679,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523925</v>
+        <v>523428</v>
       </c>
       <c r="R104" t="n">
-        <v>6845214</v>
+        <v>6845361</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10741,7 +10741,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125734280</v>
+        <v>125736651</v>
       </c>
       <c r="B105" t="n">
         <v>78973</v>
@@ -10772,17 +10772,17 @@
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523482</v>
+        <v>523722</v>
       </c>
       <c r="R105" t="n">
-        <v>6845199</v>
+        <v>6845318</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -10826,19 +10826,19 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125736651</v>
+        <v>125734280</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10869,17 +10869,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523722</v>
+        <v>523482</v>
       </c>
       <c r="R106" t="n">
-        <v>6845318</v>
+        <v>6845199</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,22 +10923,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125737335</v>
+        <v>125755620</v>
       </c>
       <c r="B107" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,37 +10946,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523835</v>
+        <v>523925</v>
       </c>
       <c r="R107" t="n">
-        <v>6845199</v>
+        <v>6845214</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11020,22 +11020,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125736699</v>
+        <v>125755617</v>
       </c>
       <c r="B108" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11043,21 +11043,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523766</v>
+        <v>523972</v>
       </c>
       <c r="R108" t="n">
-        <v>6845303</v>
+        <v>6845173</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,22 +11117,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755617</v>
+        <v>125755706</v>
       </c>
       <c r="B109" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11140,21 +11140,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11164,10 +11164,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523972</v>
+        <v>523655</v>
       </c>
       <c r="R109" t="n">
-        <v>6845173</v>
+        <v>6845374</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11226,10 +11226,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125737839</v>
+        <v>125755713</v>
       </c>
       <c r="B110" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11237,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11261,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523967</v>
+        <v>523332</v>
       </c>
       <c r="R110" t="n">
-        <v>6845175</v>
+        <v>6845377</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,19 +11311,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125755713</v>
+        <v>125736699</v>
       </c>
       <c r="B111" t="n">
         <v>78973</v>
@@ -11358,10 +11358,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523332</v>
+        <v>523766</v>
       </c>
       <c r="R111" t="n">
-        <v>6845377</v>
+        <v>6845303</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11408,22 +11408,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125755706</v>
+        <v>125737839</v>
       </c>
       <c r="B112" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,21 +11431,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11455,10 +11455,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523655</v>
+        <v>523967</v>
       </c>
       <c r="R112" t="n">
-        <v>6845374</v>
+        <v>6845175</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11505,12 +11505,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -11617,7 +11617,7 @@
         <v>125755651</v>
       </c>
       <c r="B114" t="n">
-        <v>98343</v>
+        <v>98345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11720,10 +11720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125736623</v>
+        <v>125755631</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,34 +11731,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523689</v>
+        <v>523636</v>
       </c>
       <c r="R115" t="n">
-        <v>6845339</v>
+        <v>6845388</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11805,22 +11805,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125732643</v>
+        <v>125755619</v>
       </c>
       <c r="B116" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11828,34 +11828,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523617</v>
+        <v>523952</v>
       </c>
       <c r="R116" t="n">
-        <v>6845031</v>
+        <v>6845185</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11902,22 +11902,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125755555</v>
+        <v>125732643</v>
       </c>
       <c r="B117" t="n">
-        <v>90274</v>
+        <v>79562</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11925,34 +11925,34 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523480</v>
+        <v>523617</v>
       </c>
       <c r="R117" t="n">
-        <v>6845111</v>
+        <v>6845031</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -11999,22 +11999,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755601</v>
+        <v>125755784</v>
       </c>
       <c r="B118" t="n">
-        <v>92718</v>
+        <v>78640</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12022,21 +12022,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12046,10 +12046,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523463</v>
+        <v>523606</v>
       </c>
       <c r="R118" t="n">
-        <v>6845230</v>
+        <v>6845378</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12108,10 +12108,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755784</v>
+        <v>125755555</v>
       </c>
       <c r="B119" t="n">
-        <v>78640</v>
+        <v>90276</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12119,21 +12119,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>353</v>
+        <v>1962</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12143,10 +12143,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523606</v>
+        <v>523480</v>
       </c>
       <c r="R119" t="n">
-        <v>6845378</v>
+        <v>6845111</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12198,57 +12198,52 @@
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755608</v>
+        <v>125755601</v>
       </c>
       <c r="B120" t="n">
-        <v>8447</v>
+        <v>92720</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>2079</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523745</v>
+        <v>523463</v>
       </c>
       <c r="R120" t="n">
-        <v>6845284</v>
+        <v>6845230</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12413,45 +12408,50 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755631</v>
+        <v>125755608</v>
       </c>
       <c r="B122" t="n">
-        <v>78732</v>
+        <v>8447</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523636</v>
+        <v>523745</v>
       </c>
       <c r="R122" t="n">
-        <v>6845388</v>
+        <v>6845284</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12510,10 +12510,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125755619</v>
+        <v>125736623</v>
       </c>
       <c r="B123" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,34 +12521,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523952</v>
+        <v>523689</v>
       </c>
       <c r="R123" t="n">
-        <v>6845185</v>
+        <v>6845339</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12595,22 +12595,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755557</v>
+        <v>125755704</v>
       </c>
       <c r="B124" t="n">
-        <v>91236</v>
+        <v>78973</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12618,21 +12618,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -12642,10 +12642,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523340</v>
+        <v>523760</v>
       </c>
       <c r="R124" t="n">
-        <v>6845392</v>
+        <v>6845283</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755780</v>
+        <v>125755715</v>
       </c>
       <c r="B125" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523584</v>
+        <v>523450</v>
       </c>
       <c r="R125" t="n">
-        <v>6845361</v>
+        <v>6845349</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12794,17 +12794,17 @@
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Anders Heggestad, Håkan Thenander, Philipp Weiss</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755704</v>
+        <v>125755557</v>
       </c>
       <c r="B126" t="n">
-        <v>78973</v>
+        <v>91238</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523760</v>
+        <v>523340</v>
       </c>
       <c r="R126" t="n">
-        <v>6845283</v>
+        <v>6845392</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755715</v>
+        <v>125755780</v>
       </c>
       <c r="B127" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523450</v>
+        <v>523584</v>
       </c>
       <c r="R127" t="n">
-        <v>6845349</v>
+        <v>6845361</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12998,7 +12998,7 @@
         <v>125734818</v>
       </c>
       <c r="B128" t="n">
-        <v>91256</v>
+        <v>91258</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125737411</v>
+        <v>125755643</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523825</v>
+        <v>523816</v>
       </c>
       <c r="R4" t="n">
-        <v>6845311</v>
+        <v>6845298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,19 +954,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125736529</v>
+        <v>125755708</v>
       </c>
       <c r="B5" t="n">
         <v>78973</v>
@@ -997,14 +997,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523524</v>
+        <v>523626</v>
       </c>
       <c r="R5" t="n">
-        <v>6845323</v>
+        <v>6845380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125734228</v>
+        <v>125755711</v>
       </c>
       <c r="B6" t="n">
         <v>78973</v>
@@ -1094,14 +1094,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523467</v>
+        <v>523443</v>
       </c>
       <c r="R6" t="n">
-        <v>6845121</v>
+        <v>6845363</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1148,22 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734476</v>
+        <v>125734647</v>
       </c>
       <c r="B7" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1171,37 +1171,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523492</v>
+        <v>523611</v>
       </c>
       <c r="R7" t="n">
-        <v>6845165</v>
+        <v>6845275</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755643</v>
+        <v>125755632</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>78732</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523816</v>
+        <v>523621</v>
       </c>
       <c r="R8" t="n">
-        <v>6845298</v>
+        <v>6845375</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755708</v>
+        <v>125755716</v>
       </c>
       <c r="B9" t="n">
         <v>78973</v>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523626</v>
+        <v>523477</v>
       </c>
       <c r="R9" t="n">
-        <v>6845380</v>
+        <v>6845219</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,7 +1451,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755711</v>
+        <v>125755698</v>
       </c>
       <c r="B10" t="n">
         <v>78973</v>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523443</v>
+        <v>523867</v>
       </c>
       <c r="R10" t="n">
-        <v>6845363</v>
+        <v>6845227</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,10 +1548,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125734647</v>
+        <v>125755786</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523611</v>
+        <v>523474</v>
       </c>
       <c r="R11" t="n">
-        <v>6845275</v>
+        <v>6845244</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,61 +1633,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125735595</v>
+        <v>125755785</v>
       </c>
       <c r="B12" t="n">
-        <v>98345</v>
+        <v>78640</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523492</v>
+        <v>523467</v>
       </c>
       <c r="R12" t="n">
-        <v>6845165</v>
+        <v>6845333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1734,19 +1730,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125736051</v>
+        <v>125755693</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1777,14 +1773,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523418</v>
+        <v>523993</v>
       </c>
       <c r="R13" t="n">
-        <v>6845349</v>
+        <v>6845158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1831,22 +1827,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755632</v>
+        <v>125733598</v>
       </c>
       <c r="B14" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1854,37 +1850,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523621</v>
+        <v>523483</v>
       </c>
       <c r="R14" t="n">
-        <v>6845375</v>
+        <v>6845118</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1928,19 +1924,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755716</v>
+        <v>125755710</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1975,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523477</v>
+        <v>523572</v>
       </c>
       <c r="R15" t="n">
-        <v>6845219</v>
+        <v>6845367</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2037,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755698</v>
+        <v>125735304</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2068,17 +2064,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523867</v>
+        <v>523580</v>
       </c>
       <c r="R16" t="n">
-        <v>6845227</v>
+        <v>6845417</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2122,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125737958</v>
+        <v>125733851</v>
       </c>
       <c r="B17" t="n">
-        <v>78732</v>
+        <v>91258</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2145,37 +2141,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523967</v>
+        <v>523470</v>
       </c>
       <c r="R17" t="n">
-        <v>6845175</v>
+        <v>6845106</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2219,22 +2215,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755710</v>
+        <v>125755790</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2242,21 +2238,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2266,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523572</v>
+        <v>523486</v>
       </c>
       <c r="R18" t="n">
-        <v>6845367</v>
+        <v>6845100</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2328,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755786</v>
+        <v>125755719</v>
       </c>
       <c r="B19" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2339,21 +2335,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2363,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523474</v>
+        <v>523554</v>
       </c>
       <c r="R19" t="n">
-        <v>6845244</v>
+        <v>6845068</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2425,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755785</v>
+        <v>125755593</v>
       </c>
       <c r="B20" t="n">
-        <v>78640</v>
+        <v>57652</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2436,34 +2432,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523467</v>
+        <v>523520</v>
       </c>
       <c r="R20" t="n">
-        <v>6845333</v>
+        <v>6845094</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2496,6 +2497,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2522,32 +2528,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755693</v>
+        <v>125755657</v>
       </c>
       <c r="B21" t="n">
-        <v>78973</v>
+        <v>91399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>1503</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2557,10 +2563,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523993</v>
+        <v>523463</v>
       </c>
       <c r="R21" t="n">
-        <v>6845158</v>
+        <v>6845211</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,10 +2625,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125733598</v>
+        <v>125755549</v>
       </c>
       <c r="B22" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2630,37 +2636,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523483</v>
+        <v>523541</v>
       </c>
       <c r="R22" t="n">
-        <v>6845118</v>
+        <v>6845054</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2704,19 +2710,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125736021</v>
+        <v>125755545</v>
       </c>
       <c r="B23" t="n">
         <v>79591</v>
@@ -2747,14 +2753,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523418</v>
+        <v>523465</v>
       </c>
       <c r="R23" t="n">
-        <v>6845349</v>
+        <v>6845109</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2801,22 +2807,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755719</v>
+        <v>125755634</v>
       </c>
       <c r="B24" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2824,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2848,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523554</v>
+        <v>523498</v>
       </c>
       <c r="R24" t="n">
-        <v>6845068</v>
+        <v>6845404</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2910,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125735304</v>
+        <v>125735113</v>
       </c>
       <c r="B25" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2921,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2945,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523580</v>
+        <v>523630</v>
       </c>
       <c r="R25" t="n">
-        <v>6845417</v>
+        <v>6845423</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3007,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125733851</v>
+        <v>125755695</v>
       </c>
       <c r="B26" t="n">
-        <v>91258</v>
+        <v>78973</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3018,37 +3024,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523470</v>
+        <v>523990</v>
       </c>
       <c r="R26" t="n">
-        <v>6845106</v>
+        <v>6845162</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3092,22 +3098,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755790</v>
+        <v>125755565</v>
       </c>
       <c r="B27" t="n">
-        <v>78640</v>
+        <v>91258</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3115,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>5442</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3139,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523486</v>
+        <v>523551</v>
       </c>
       <c r="R27" t="n">
-        <v>6845100</v>
+        <v>6845103</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3201,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755593</v>
+        <v>125755625</v>
       </c>
       <c r="B28" t="n">
-        <v>57652</v>
+        <v>78732</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3212,39 +3218,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523520</v>
+        <v>523850</v>
       </c>
       <c r="R28" t="n">
-        <v>6845094</v>
+        <v>6845286</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3277,11 +3278,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3308,32 +3304,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755657</v>
+        <v>125755539</v>
       </c>
       <c r="B29" t="n">
-        <v>91399</v>
+        <v>79591</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1503</v>
+        <v>6453</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523463</v>
+        <v>523924</v>
       </c>
       <c r="R29" t="n">
-        <v>6845211</v>
+        <v>6845215</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3405,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755549</v>
+        <v>125735540</v>
       </c>
       <c r="B30" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,37 +3412,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523541</v>
+        <v>523479</v>
       </c>
       <c r="R30" t="n">
-        <v>6845054</v>
+        <v>6845406</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3490,22 +3486,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755545</v>
+        <v>125755787</v>
       </c>
       <c r="B31" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3509,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523465</v>
+        <v>523457</v>
       </c>
       <c r="R31" t="n">
-        <v>6845109</v>
+        <v>6845237</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3599,10 +3595,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125733581</v>
+        <v>125755544</v>
       </c>
       <c r="B32" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,34 +3606,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523528</v>
+        <v>523483</v>
       </c>
       <c r="R32" t="n">
-        <v>6845135</v>
+        <v>6845181</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3684,19 +3680,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125737629</v>
+        <v>125734860</v>
       </c>
       <c r="B33" t="n">
         <v>78973</v>
@@ -3727,17 +3723,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523960</v>
+        <v>523673</v>
       </c>
       <c r="R33" t="n">
-        <v>6845161</v>
+        <v>6845294</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3781,19 +3777,19 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755634</v>
+        <v>125755626</v>
       </c>
       <c r="B34" t="n">
         <v>78732</v>
@@ -3828,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523498</v>
+        <v>523759</v>
       </c>
       <c r="R34" t="n">
-        <v>6845404</v>
+        <v>6845238</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3890,10 +3886,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735113</v>
+        <v>125735128</v>
       </c>
       <c r="B35" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3901,21 +3897,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3925,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523630</v>
+        <v>523627</v>
       </c>
       <c r="R35" t="n">
-        <v>6845423</v>
+        <v>6845420</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -3987,10 +3983,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755695</v>
+        <v>125737014</v>
       </c>
       <c r="B36" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3998,37 +3994,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523990</v>
+        <v>523854</v>
       </c>
       <c r="R36" t="n">
-        <v>6845162</v>
+        <v>6845289</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4072,44 +4068,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755565</v>
+        <v>125755658</v>
       </c>
       <c r="B37" t="n">
-        <v>91258</v>
+        <v>91399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5442</v>
+        <v>1503</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4119,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523551</v>
+        <v>523487</v>
       </c>
       <c r="R37" t="n">
-        <v>6845103</v>
+        <v>6845098</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,10 +4177,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125755625</v>
+        <v>125755717</v>
       </c>
       <c r="B38" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4192,21 +4188,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4216,10 +4212,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>523850</v>
+        <v>523466</v>
       </c>
       <c r="R38" t="n">
-        <v>6845286</v>
+        <v>6845180</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,10 +4274,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755544</v>
+        <v>125755792</v>
       </c>
       <c r="B39" t="n">
-        <v>79591</v>
+        <v>92522</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4289,21 +4285,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6453</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4313,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523483</v>
+        <v>523992</v>
       </c>
       <c r="R39" t="n">
-        <v>6845181</v>
+        <v>6845170</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4349,6 +4345,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4375,32 +4376,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755539</v>
+        <v>125755552</v>
       </c>
       <c r="B40" t="n">
-        <v>79591</v>
+        <v>91203</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4410,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523924</v>
+        <v>523424</v>
       </c>
       <c r="R40" t="n">
-        <v>6845215</v>
+        <v>6845383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125735540</v>
+        <v>125755543</v>
       </c>
       <c r="B41" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4483,37 +4484,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523479</v>
+        <v>523460</v>
       </c>
       <c r="R41" t="n">
-        <v>6845406</v>
+        <v>6845221</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4557,22 +4558,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125734860</v>
+        <v>125755542</v>
       </c>
       <c r="B42" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4580,37 +4581,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523673</v>
+        <v>523670</v>
       </c>
       <c r="R42" t="n">
-        <v>6845294</v>
+        <v>6845353</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4654,22 +4655,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755787</v>
+        <v>125755636</v>
       </c>
       <c r="B43" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4677,21 +4678,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4701,10 +4702,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523457</v>
+        <v>523511</v>
       </c>
       <c r="R43" t="n">
-        <v>6845237</v>
+        <v>6845102</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4763,10 +4764,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125734662</v>
+        <v>125755627</v>
       </c>
       <c r="B44" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4774,34 +4775,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523492</v>
+        <v>523755</v>
       </c>
       <c r="R44" t="n">
-        <v>6845165</v>
+        <v>6845251</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4848,22 +4849,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125734241</v>
+        <v>125755628</v>
       </c>
       <c r="B45" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4871,34 +4872,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523492</v>
+        <v>523728</v>
       </c>
       <c r="R45" t="n">
-        <v>6845165</v>
+        <v>6845279</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4945,60 +4946,70 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125736099</v>
+        <v>125736061</v>
       </c>
       <c r="B46" t="n">
-        <v>78973</v>
+        <v>56844</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523514</v>
+        <v>523643</v>
       </c>
       <c r="R46" t="n">
-        <v>6845340</v>
+        <v>6845391</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5042,19 +5053,19 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755626</v>
+        <v>125732709</v>
       </c>
       <c r="B47" t="n">
         <v>78732</v>
@@ -5085,17 +5096,17 @@
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523759</v>
+        <v>523548</v>
       </c>
       <c r="R47" t="n">
-        <v>6845238</v>
+        <v>6845076</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5139,60 +5150,69 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125735128</v>
+        <v>125755647</v>
       </c>
       <c r="B48" t="n">
-        <v>79591</v>
+        <v>98345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523627</v>
+        <v>523408</v>
       </c>
       <c r="R48" t="n">
-        <v>6845420</v>
+        <v>6845401</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5236,22 +5256,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125737014</v>
+        <v>125736672</v>
       </c>
       <c r="B49" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5259,21 +5279,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5283,10 +5303,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523854</v>
+        <v>523827</v>
       </c>
       <c r="R49" t="n">
-        <v>6845289</v>
+        <v>6845310</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5345,48 +5365,48 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125755658</v>
+        <v>125735892</v>
       </c>
       <c r="B50" t="n">
-        <v>91399</v>
+        <v>92528</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523487</v>
+        <v>523608</v>
       </c>
       <c r="R50" t="n">
-        <v>6845098</v>
+        <v>6845376</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5430,22 +5450,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125755717</v>
+        <v>125735337</v>
       </c>
       <c r="B51" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5453,37 +5473,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523466</v>
+        <v>523593</v>
       </c>
       <c r="R51" t="n">
-        <v>6845180</v>
+        <v>6845417</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5527,22 +5547,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755792</v>
+        <v>125734972</v>
       </c>
       <c r="B52" t="n">
-        <v>92522</v>
+        <v>78732</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5550,37 +5570,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523992</v>
+        <v>523675</v>
       </c>
       <c r="R52" t="n">
-        <v>6845170</v>
+        <v>6845339</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5610,11 +5630,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5629,44 +5644,44 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755552</v>
+        <v>125755788</v>
       </c>
       <c r="B53" t="n">
-        <v>91203</v>
+        <v>78640</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5676,10 +5691,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523424</v>
+        <v>523460</v>
       </c>
       <c r="R53" t="n">
-        <v>6845383</v>
+        <v>6845221</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5738,10 +5753,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755543</v>
+        <v>125755630</v>
       </c>
       <c r="B54" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5749,21 +5764,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5773,10 +5788,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523460</v>
+        <v>523671</v>
       </c>
       <c r="R54" t="n">
-        <v>6845221</v>
+        <v>6845353</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5835,10 +5850,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755542</v>
+        <v>125755629</v>
       </c>
       <c r="B55" t="n">
-        <v>79591</v>
+        <v>78732</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5846,21 +5861,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5870,10 +5885,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523670</v>
+        <v>523679</v>
       </c>
       <c r="R55" t="n">
-        <v>6845353</v>
+        <v>6845347</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5932,7 +5947,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755636</v>
+        <v>125734739</v>
       </c>
       <c r="B56" t="n">
         <v>78732</v>
@@ -5963,17 +5978,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523511</v>
+        <v>523608</v>
       </c>
       <c r="R56" t="n">
-        <v>6845102</v>
+        <v>6845309</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6017,44 +6032,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755627</v>
+        <v>125755598</v>
       </c>
       <c r="B57" t="n">
-        <v>78732</v>
+        <v>97223</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6064,10 +6079,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523755</v>
+        <v>523351</v>
       </c>
       <c r="R57" t="n">
-        <v>6845251</v>
+        <v>6845393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6126,10 +6141,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755628</v>
+        <v>125755761</v>
       </c>
       <c r="B58" t="n">
-        <v>78732</v>
+        <v>57652</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6137,34 +6152,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523728</v>
+        <v>523387</v>
       </c>
       <c r="R58" t="n">
-        <v>6845279</v>
+        <v>6845410</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6223,58 +6243,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125736061</v>
+        <v>125755709</v>
       </c>
       <c r="B59" t="n">
-        <v>56844</v>
+        <v>78973</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523643</v>
+        <v>523598</v>
       </c>
       <c r="R59" t="n">
-        <v>6845391</v>
+        <v>6845380</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6318,22 +6328,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125732709</v>
+        <v>125755714</v>
       </c>
       <c r="B60" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6341,37 +6351,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523548</v>
+        <v>523383</v>
       </c>
       <c r="R60" t="n">
-        <v>6845076</v>
+        <v>6845391</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6415,66 +6425,57 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125755647</v>
+        <v>125755701</v>
       </c>
       <c r="B61" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>523408</v>
+        <v>523839</v>
       </c>
       <c r="R61" t="n">
-        <v>6845401</v>
+        <v>6845286</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6533,7 +6534,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>125736672</v>
+        <v>125755707</v>
       </c>
       <c r="B62" t="n">
         <v>78973</v>
@@ -6564,17 +6565,17 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>523827</v>
+        <v>523644</v>
       </c>
       <c r="R62" t="n">
-        <v>6845310</v>
+        <v>6845389</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -6618,60 +6619,60 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125735892</v>
+        <v>125755541</v>
       </c>
       <c r="B63" t="n">
-        <v>92528</v>
+        <v>79591</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523608</v>
+        <v>523757</v>
       </c>
       <c r="R63" t="n">
-        <v>6845376</v>
+        <v>6845248</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -6715,60 +6716,60 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125735337</v>
+        <v>125755794</v>
       </c>
       <c r="B64" t="n">
-        <v>78732</v>
+        <v>91648</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>228912</v>
+        <v>4217</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523593</v>
+        <v>523385</v>
       </c>
       <c r="R64" t="n">
-        <v>6845417</v>
+        <v>6845416</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -6798,6 +6799,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6812,19 +6818,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125734655</v>
+        <v>125755621</v>
       </c>
       <c r="B65" t="n">
         <v>78732</v>
@@ -6855,14 +6861,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523492</v>
+        <v>523920</v>
       </c>
       <c r="R65" t="n">
-        <v>6845165</v>
+        <v>6845217</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6909,22 +6915,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125734972</v>
+        <v>125732736</v>
       </c>
       <c r="B66" t="n">
-        <v>78732</v>
+        <v>78731</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6932,21 +6938,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6956,10 +6962,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523675</v>
+        <v>523551</v>
       </c>
       <c r="R66" t="n">
-        <v>6845339</v>
+        <v>6845080</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7018,10 +7024,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125755788</v>
+        <v>125737510</v>
       </c>
       <c r="B67" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7029,37 +7035,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523460</v>
+        <v>523957</v>
       </c>
       <c r="R67" t="n">
-        <v>6845221</v>
+        <v>6845190</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7103,19 +7109,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125733632</v>
+        <v>125755702</v>
       </c>
       <c r="B68" t="n">
         <v>78973</v>
@@ -7146,14 +7152,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523458</v>
+        <v>523829</v>
       </c>
       <c r="R68" t="n">
-        <v>6845126</v>
+        <v>6845308</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7200,22 +7206,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755630</v>
+        <v>125755789</v>
       </c>
       <c r="B69" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7223,21 +7229,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7247,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523671</v>
+        <v>523480</v>
       </c>
       <c r="R69" t="n">
-        <v>6845353</v>
+        <v>6845112</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7309,10 +7315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755629</v>
+        <v>125755697</v>
       </c>
       <c r="B70" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7320,21 +7326,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7344,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523679</v>
+        <v>523948</v>
       </c>
       <c r="R70" t="n">
-        <v>6845347</v>
+        <v>6845177</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7406,10 +7412,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125738012</v>
+        <v>125755700</v>
       </c>
       <c r="B71" t="n">
-        <v>57652</v>
+        <v>78973</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7417,39 +7423,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523967</v>
+        <v>523859</v>
       </c>
       <c r="R71" t="n">
-        <v>6845175</v>
+        <v>6845221</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7496,22 +7497,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125734739</v>
+        <v>125755783</v>
       </c>
       <c r="B72" t="n">
-        <v>78732</v>
+        <v>78640</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7519,37 +7520,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523608</v>
+        <v>523644</v>
       </c>
       <c r="R72" t="n">
-        <v>6845309</v>
+        <v>6845379</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -7593,22 +7594,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755598</v>
+        <v>125755775</v>
       </c>
       <c r="B73" t="n">
-        <v>97223</v>
+        <v>92528</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7616,21 +7617,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221945</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7640,10 +7641,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523351</v>
+        <v>523541</v>
       </c>
       <c r="R73" t="n">
-        <v>6845393</v>
+        <v>6845044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7702,10 +7703,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125733520</v>
+        <v>125755553</v>
       </c>
       <c r="B74" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7713,34 +7714,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523552</v>
+        <v>523626</v>
       </c>
       <c r="R74" t="n">
-        <v>6845072</v>
+        <v>6845383</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7787,50 +7788,54 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755761</v>
+        <v>125755654</v>
       </c>
       <c r="B75" t="n">
-        <v>57652</v>
+        <v>98345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -7839,10 +7844,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523387</v>
+        <v>523428</v>
       </c>
       <c r="R75" t="n">
-        <v>6845410</v>
+        <v>6845361</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7901,10 +7906,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755709</v>
+        <v>125755624</v>
       </c>
       <c r="B76" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7912,21 +7917,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7936,10 +7941,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523598</v>
+        <v>523853</v>
       </c>
       <c r="R76" t="n">
-        <v>6845380</v>
+        <v>6845279</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -7998,32 +8003,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755794</v>
+        <v>125755781</v>
       </c>
       <c r="B77" t="n">
-        <v>91648</v>
+        <v>78640</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4217</v>
+        <v>353</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8033,10 +8038,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523385</v>
+        <v>523958</v>
       </c>
       <c r="R77" t="n">
-        <v>6845416</v>
+        <v>6845195</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8069,11 +8074,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8100,7 +8100,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755714</v>
+        <v>125755694</v>
       </c>
       <c r="B78" t="n">
         <v>78973</v>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523383</v>
+        <v>523979</v>
       </c>
       <c r="R78" t="n">
-        <v>6845391</v>
+        <v>6845154</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8197,32 +8197,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755701</v>
+        <v>125755774</v>
       </c>
       <c r="B79" t="n">
-        <v>78973</v>
+        <v>92528</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523839</v>
+        <v>523526</v>
       </c>
       <c r="R79" t="n">
-        <v>6845286</v>
+        <v>6845095</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8294,45 +8294,50 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755707</v>
+        <v>125755610</v>
       </c>
       <c r="B80" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523644</v>
+        <v>523527</v>
       </c>
       <c r="R80" t="n">
-        <v>6845389</v>
+        <v>6845375</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8391,10 +8396,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755541</v>
+        <v>125755712</v>
       </c>
       <c r="B81" t="n">
-        <v>79591</v>
+        <v>78973</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8402,21 +8407,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8426,10 +8431,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523757</v>
+        <v>523428</v>
       </c>
       <c r="R81" t="n">
-        <v>6845248</v>
+        <v>6845361</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8488,52 +8493,48 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125735686</v>
+        <v>125734280</v>
       </c>
       <c r="B82" t="n">
-        <v>98345</v>
+        <v>78973</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523418</v>
+        <v>523482</v>
       </c>
       <c r="R82" t="n">
-        <v>6845349</v>
+        <v>6845199</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8577,19 +8578,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125737510</v>
+        <v>125755620</v>
       </c>
       <c r="B83" t="n">
         <v>78732</v>
@@ -8620,17 +8621,17 @@
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523957</v>
+        <v>523925</v>
       </c>
       <c r="R83" t="n">
-        <v>6845190</v>
+        <v>6845214</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8674,22 +8675,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755789</v>
+        <v>125737335</v>
       </c>
       <c r="B84" t="n">
-        <v>78640</v>
+        <v>79591</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8697,37 +8698,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523480</v>
+        <v>523835</v>
       </c>
       <c r="R84" t="n">
-        <v>6845112</v>
+        <v>6845199</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8771,22 +8772,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755702</v>
+        <v>125755550</v>
       </c>
       <c r="B85" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8794,21 +8795,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8818,10 +8819,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523829</v>
+        <v>523604</v>
       </c>
       <c r="R85" t="n">
-        <v>6845308</v>
+        <v>6845013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8880,10 +8881,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755621</v>
+        <v>125755547</v>
       </c>
       <c r="B86" t="n">
-        <v>78732</v>
+        <v>79591</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8891,21 +8892,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8915,10 +8916,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523920</v>
+        <v>523479</v>
       </c>
       <c r="R86" t="n">
-        <v>6845217</v>
+        <v>6845112</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8977,10 +8978,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125732736</v>
+        <v>125755617</v>
       </c>
       <c r="B87" t="n">
-        <v>78731</v>
+        <v>78732</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8988,37 +8989,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523551</v>
+        <v>523972</v>
       </c>
       <c r="R87" t="n">
-        <v>6845080</v>
+        <v>6845173</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9062,19 +9063,19 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>125755697</v>
+        <v>125755706</v>
       </c>
       <c r="B88" t="n">
         <v>78973</v>
@@ -9109,10 +9110,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>523948</v>
+        <v>523655</v>
       </c>
       <c r="R88" t="n">
-        <v>6845177</v>
+        <v>6845374</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9171,7 +9172,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755700</v>
+        <v>125755713</v>
       </c>
       <c r="B89" t="n">
         <v>78973</v>
@@ -9206,10 +9207,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523859</v>
+        <v>523332</v>
       </c>
       <c r="R89" t="n">
-        <v>6845221</v>
+        <v>6845377</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9268,10 +9269,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755783</v>
+        <v>125755635</v>
       </c>
       <c r="B90" t="n">
-        <v>78640</v>
+        <v>78732</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9279,21 +9280,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9303,10 +9304,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523644</v>
+        <v>523464</v>
       </c>
       <c r="R90" t="n">
-        <v>6845379</v>
+        <v>6845115</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9365,45 +9366,54 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755775</v>
+        <v>125755651</v>
       </c>
       <c r="B91" t="n">
-        <v>92528</v>
+        <v>98345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523541</v>
+        <v>523420</v>
       </c>
       <c r="R91" t="n">
-        <v>6845044</v>
+        <v>6845370</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9462,49 +9472,45 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125732728</v>
+        <v>125755631</v>
       </c>
       <c r="B92" t="n">
-        <v>92528</v>
+        <v>78732</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523590</v>
+        <v>523636</v>
       </c>
       <c r="R92" t="n">
-        <v>6845030</v>
+        <v>6845388</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9551,22 +9557,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755553</v>
+        <v>125755619</v>
       </c>
       <c r="B93" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9574,21 +9580,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9598,10 +9604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523626</v>
+        <v>523952</v>
       </c>
       <c r="R93" t="n">
-        <v>6845383</v>
+        <v>6845185</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9660,54 +9666,45 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755654</v>
+        <v>125755784</v>
       </c>
       <c r="B94" t="n">
-        <v>98345</v>
+        <v>78640</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523428</v>
+        <v>523606</v>
       </c>
       <c r="R94" t="n">
-        <v>6845361</v>
+        <v>6845378</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9766,10 +9763,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755624</v>
+        <v>125755555</v>
       </c>
       <c r="B95" t="n">
-        <v>78732</v>
+        <v>90276</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9777,21 +9774,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9801,10 +9798,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523853</v>
+        <v>523480</v>
       </c>
       <c r="R95" t="n">
-        <v>6845279</v>
+        <v>6845111</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9863,10 +9860,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125737769</v>
+        <v>125755601</v>
       </c>
       <c r="B96" t="n">
-        <v>79591</v>
+        <v>92720</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9874,21 +9871,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6453</v>
+        <v>2079</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9898,10 +9895,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523967</v>
+        <v>523463</v>
       </c>
       <c r="R96" t="n">
-        <v>6845175</v>
+        <v>6845230</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9948,57 +9945,66 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>125755781</v>
+        <v>125755563</v>
       </c>
       <c r="B97" t="n">
-        <v>78640</v>
+        <v>56844</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>523958</v>
+        <v>523483</v>
       </c>
       <c r="R97" t="n">
-        <v>6845195</v>
+        <v>6845365</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10057,45 +10063,50 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>125755694</v>
+        <v>125755608</v>
       </c>
       <c r="B98" t="n">
-        <v>78973</v>
+        <v>8447</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>523979</v>
+        <v>523745</v>
       </c>
       <c r="R98" t="n">
-        <v>6845154</v>
+        <v>6845284</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10154,32 +10165,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755774</v>
+        <v>125755704</v>
       </c>
       <c r="B99" t="n">
-        <v>92528</v>
+        <v>78973</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10189,10 +10200,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523526</v>
+        <v>523760</v>
       </c>
       <c r="R99" t="n">
-        <v>6845095</v>
+        <v>6845283</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10251,50 +10262,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755610</v>
+        <v>125755715</v>
       </c>
       <c r="B100" t="n">
-        <v>8447</v>
+        <v>78973</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523527</v>
+        <v>523450</v>
       </c>
       <c r="R100" t="n">
-        <v>6845375</v>
+        <v>6845349</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10353,10 +10359,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125737335</v>
+        <v>125755557</v>
       </c>
       <c r="B101" t="n">
-        <v>79591</v>
+        <v>91238</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10364,37 +10370,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523835</v>
+        <v>523340</v>
       </c>
       <c r="R101" t="n">
-        <v>6845199</v>
+        <v>6845392</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -10438,22 +10444,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755550</v>
+        <v>125755780</v>
       </c>
       <c r="B102" t="n">
-        <v>79591</v>
+        <v>78640</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10461,21 +10467,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10485,10 +10491,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523604</v>
+        <v>523584</v>
       </c>
       <c r="R102" t="n">
-        <v>6845013</v>
+        <v>6845361</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10547,10 +10553,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755547</v>
+        <v>125734818</v>
       </c>
       <c r="B103" t="n">
-        <v>79591</v>
+        <v>91258</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10558,37 +10564,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6453</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523479</v>
+        <v>523643</v>
       </c>
       <c r="R103" t="n">
-        <v>6845112</v>
+        <v>6845282</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10632,19 +10638,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125755712</v>
+        <v>125737411</v>
       </c>
       <c r="B104" t="n">
         <v>78973</v>
@@ -10679,10 +10685,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523428</v>
+        <v>523825</v>
       </c>
       <c r="R104" t="n">
-        <v>6845361</v>
+        <v>6845311</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10729,22 +10735,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125736651</v>
+        <v>125734476</v>
       </c>
       <c r="B105" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10752,34 +10758,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523722</v>
+        <v>523492</v>
       </c>
       <c r="R105" t="n">
-        <v>6845318</v>
+        <v>6845165</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10838,7 +10844,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125734280</v>
+        <v>125736529</v>
       </c>
       <c r="B106" t="n">
         <v>78973</v>
@@ -10869,17 +10875,17 @@
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523482</v>
+        <v>523524</v>
       </c>
       <c r="R106" t="n">
-        <v>6845199</v>
+        <v>6845323</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -10923,22 +10929,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125755620</v>
+        <v>125734228</v>
       </c>
       <c r="B107" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10946,34 +10952,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523925</v>
+        <v>523467</v>
       </c>
       <c r="R107" t="n">
-        <v>6845214</v>
+        <v>6845121</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11020,57 +11026,61 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125755617</v>
+        <v>125735595</v>
       </c>
       <c r="B108" t="n">
-        <v>78732</v>
+        <v>98345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523972</v>
+        <v>523492</v>
       </c>
       <c r="R108" t="n">
-        <v>6845173</v>
+        <v>6845165</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11117,19 +11127,19 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125755706</v>
+        <v>125736051</v>
       </c>
       <c r="B109" t="n">
         <v>78973</v>
@@ -11160,14 +11170,14 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523655</v>
+        <v>523418</v>
       </c>
       <c r="R109" t="n">
-        <v>6845374</v>
+        <v>6845349</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11214,22 +11224,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>125755713</v>
+        <v>125737958</v>
       </c>
       <c r="B110" t="n">
-        <v>78973</v>
+        <v>78732</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11237,21 +11247,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11261,10 +11271,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>523332</v>
+        <v>523967</v>
       </c>
       <c r="R110" t="n">
-        <v>6845377</v>
+        <v>6845175</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11311,22 +11321,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>125736699</v>
+        <v>125736021</v>
       </c>
       <c r="B111" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11334,34 +11344,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>523766</v>
+        <v>523418</v>
       </c>
       <c r="R111" t="n">
-        <v>6845303</v>
+        <v>6845349</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11420,10 +11430,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>125737839</v>
+        <v>125733581</v>
       </c>
       <c r="B112" t="n">
-        <v>79562</v>
+        <v>78973</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11431,34 +11441,34 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>523967</v>
+        <v>523528</v>
       </c>
       <c r="R112" t="n">
-        <v>6845175</v>
+        <v>6845135</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -11517,10 +11527,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>125755635</v>
+        <v>125737629</v>
       </c>
       <c r="B113" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11528,21 +11538,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -11552,10 +11562,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>523464</v>
+        <v>523960</v>
       </c>
       <c r="R113" t="n">
-        <v>6845115</v>
+        <v>6845161</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -11602,66 +11612,57 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>125755651</v>
+        <v>125734662</v>
       </c>
       <c r="B114" t="n">
-        <v>98345</v>
+        <v>78731</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>523420</v>
+        <v>523492</v>
       </c>
       <c r="R114" t="n">
-        <v>6845370</v>
+        <v>6845165</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -11708,22 +11709,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125755631</v>
+        <v>125734241</v>
       </c>
       <c r="B115" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11731,34 +11732,34 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523636</v>
+        <v>523492</v>
       </c>
       <c r="R115" t="n">
-        <v>6845388</v>
+        <v>6845165</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11805,22 +11806,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125755619</v>
+        <v>125736099</v>
       </c>
       <c r="B116" t="n">
-        <v>78732</v>
+        <v>78973</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11828,34 +11829,34 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523952</v>
+        <v>523514</v>
       </c>
       <c r="R116" t="n">
-        <v>6845185</v>
+        <v>6845340</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11902,22 +11903,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>125732643</v>
+        <v>125734655</v>
       </c>
       <c r="B117" t="n">
-        <v>79562</v>
+        <v>78732</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11925,21 +11926,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -11949,10 +11950,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>523617</v>
+        <v>523492</v>
       </c>
       <c r="R117" t="n">
-        <v>6845031</v>
+        <v>6845165</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12011,10 +12012,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125755784</v>
+        <v>125733520</v>
       </c>
       <c r="B118" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12022,34 +12023,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523606</v>
+        <v>523552</v>
       </c>
       <c r="R118" t="n">
-        <v>6845378</v>
+        <v>6845072</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12096,22 +12097,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125755555</v>
+        <v>125738012</v>
       </c>
       <c r="B119" t="n">
-        <v>90276</v>
+        <v>57652</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12119,34 +12120,39 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523480</v>
+        <v>523967</v>
       </c>
       <c r="R119" t="n">
-        <v>6845111</v>
+        <v>6845175</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12193,22 +12199,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125755601</v>
+        <v>125733632</v>
       </c>
       <c r="B120" t="n">
-        <v>92720</v>
+        <v>78973</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12216,34 +12222,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523463</v>
+        <v>523458</v>
       </c>
       <c r="R120" t="n">
-        <v>6845230</v>
+        <v>6845126</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12290,66 +12296,61 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125755563</v>
+        <v>125735686</v>
       </c>
       <c r="B121" t="n">
-        <v>56844</v>
+        <v>98345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L121" t="inlineStr">
-        <is>
-          <t>hane</t>
+          <t>90</t>
         </is>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>523483</v>
+        <v>523418</v>
       </c>
       <c r="R121" t="n">
-        <v>6845365</v>
+        <v>6845349</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12396,22 +12397,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>125755608</v>
+        <v>125732728</v>
       </c>
       <c r="B122" t="n">
-        <v>8447</v>
+        <v>92528</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12419,39 +12420,38 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>106545</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
-      <c r="M122" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>11</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>523745</v>
+        <v>523590</v>
       </c>
       <c r="R122" t="n">
-        <v>6845284</v>
+        <v>6845030</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -12498,22 +12498,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>125736623</v>
+        <v>125737769</v>
       </c>
       <c r="B123" t="n">
-        <v>78973</v>
+        <v>79591</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12521,34 +12521,34 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>523689</v>
+        <v>523967</v>
       </c>
       <c r="R123" t="n">
-        <v>6845339</v>
+        <v>6845175</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -12607,7 +12607,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>125755704</v>
+        <v>125736651</v>
       </c>
       <c r="B124" t="n">
         <v>78973</v>
@@ -12642,10 +12642,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>523760</v>
+        <v>523722</v>
       </c>
       <c r="R124" t="n">
-        <v>6845283</v>
+        <v>6845318</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -12692,22 +12692,22 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125755715</v>
+        <v>125737839</v>
       </c>
       <c r="B125" t="n">
-        <v>78973</v>
+        <v>79562</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523450</v>
+        <v>523967</v>
       </c>
       <c r="R125" t="n">
-        <v>6845349</v>
+        <v>6845175</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12789,22 +12789,22 @@
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125755557</v>
+        <v>125736699</v>
       </c>
       <c r="B126" t="n">
-        <v>91238</v>
+        <v>78973</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523340</v>
+        <v>523766</v>
       </c>
       <c r="R126" t="n">
-        <v>6845392</v>
+        <v>6845303</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12886,22 +12886,22 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125755780</v>
+        <v>125736623</v>
       </c>
       <c r="B127" t="n">
-        <v>78640</v>
+        <v>78973</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,34 +12909,34 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523584</v>
+        <v>523689</v>
       </c>
       <c r="R127" t="n">
-        <v>6845361</v>
+        <v>6845339</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12983,22 +12983,22 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125734818</v>
+        <v>125732643</v>
       </c>
       <c r="B128" t="n">
-        <v>91258</v>
+        <v>79562</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,37 +13006,37 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523643</v>
+        <v>523617</v>
       </c>
       <c r="R128" t="n">
-        <v>6845282</v>
+        <v>6845031</v>
       </c>
       <c r="S128" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -13080,12 +13080,12 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755703</v>
+        <v>125755643</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523783</v>
+        <v>523816</v>
       </c>
       <c r="R2" t="n">
-        <v>6845289</v>
+        <v>6845298</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755705</v>
+        <v>125755703</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523728</v>
+        <v>523783</v>
       </c>
       <c r="R3" t="n">
-        <v>6845268</v>
+        <v>6845289</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755643</v>
+        <v>125755705</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523816</v>
+        <v>523728</v>
       </c>
       <c r="R4" t="n">
-        <v>6845298</v>
+        <v>6845268</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755708</v>
+        <v>125734647</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523626</v>
+        <v>523611</v>
       </c>
       <c r="R5" t="n">
-        <v>6845380</v>
+        <v>6845275</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755711</v>
+        <v>125755708</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523443</v>
+        <v>523626</v>
       </c>
       <c r="R6" t="n">
-        <v>6845363</v>
+        <v>6845380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125734647</v>
+        <v>125755716</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1191,17 +1191,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523611</v>
+        <v>523477</v>
       </c>
       <c r="R7" t="n">
-        <v>6845275</v>
+        <v>6845219</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1245,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755632</v>
+        <v>125755698</v>
       </c>
       <c r="B8" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1268,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523621</v>
+        <v>523867</v>
       </c>
       <c r="R8" t="n">
-        <v>6845375</v>
+        <v>6845227</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,10 +1354,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755716</v>
+        <v>125755711</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523477</v>
+        <v>523443</v>
       </c>
       <c r="R9" t="n">
-        <v>6845219</v>
+        <v>6845363</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,10 +1451,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755698</v>
+        <v>125755632</v>
       </c>
       <c r="B10" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,21 +1462,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523867</v>
+        <v>523621</v>
       </c>
       <c r="R10" t="n">
-        <v>6845227</v>
+        <v>6845375</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1551,7 +1551,7 @@
         <v>125755786</v>
       </c>
       <c r="B11" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125755785</v>
       </c>
       <c r="B12" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125755693</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125733598</v>
+        <v>125755710</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1870,17 +1870,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523483</v>
+        <v>523572</v>
       </c>
       <c r="R14" t="n">
-        <v>6845118</v>
+        <v>6845367</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1924,22 +1924,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755710</v>
+        <v>125733598</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1967,17 +1967,17 @@
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523572</v>
+        <v>523483</v>
       </c>
       <c r="R15" t="n">
-        <v>6845367</v>
+        <v>6845118</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2021,22 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125735304</v>
+        <v>125755719</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,17 +2064,17 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523580</v>
+        <v>523554</v>
       </c>
       <c r="R16" t="n">
-        <v>6845417</v>
+        <v>6845068</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2118,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125733851</v>
+        <v>125755593</v>
       </c>
       <c r="B17" t="n">
-        <v>91258</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,37 +2141,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523470</v>
+        <v>523520</v>
       </c>
       <c r="R17" t="n">
-        <v>6845106</v>
+        <v>6845094</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2201,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2215,12 +2225,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2230,7 +2240,7 @@
         <v>125755790</v>
       </c>
       <c r="B18" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2334,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125755719</v>
+        <v>125735304</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,17 +2365,17 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523554</v>
+        <v>523580</v>
       </c>
       <c r="R19" t="n">
-        <v>6845068</v>
+        <v>6845417</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2409,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755593</v>
+        <v>125733851</v>
       </c>
       <c r="B20" t="n">
-        <v>57652</v>
+        <v>91262</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2432,42 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523520</v>
+        <v>523470</v>
       </c>
       <c r="R20" t="n">
-        <v>6845094</v>
+        <v>6845106</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2497,11 +2502,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2516,60 +2516,60 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125755657</v>
+        <v>125735113</v>
       </c>
       <c r="B21" t="n">
-        <v>91399</v>
+        <v>78736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>523463</v>
+        <v>523630</v>
       </c>
       <c r="R21" t="n">
-        <v>6845211</v>
+        <v>6845423</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2613,44 +2613,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755549</v>
+        <v>125755657</v>
       </c>
       <c r="B22" t="n">
-        <v>79591</v>
+        <v>91403</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523541</v>
+        <v>523463</v>
       </c>
       <c r="R22" t="n">
-        <v>6845054</v>
+        <v>6845211</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2725,7 +2725,7 @@
         <v>125755545</v>
       </c>
       <c r="B23" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2819,10 +2819,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755634</v>
+        <v>125755549</v>
       </c>
       <c r="B24" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2830,21 +2830,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523498</v>
+        <v>523541</v>
       </c>
       <c r="R24" t="n">
-        <v>6845404</v>
+        <v>6845054</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125735113</v>
+        <v>125755634</v>
       </c>
       <c r="B25" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,17 +2947,17 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523630</v>
+        <v>523498</v>
       </c>
       <c r="R25" t="n">
-        <v>6845423</v>
+        <v>6845404</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3001,12 +3001,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3016,7 +3016,7 @@
         <v>125755695</v>
       </c>
       <c r="B26" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         <v>125755565</v>
       </c>
       <c r="B27" t="n">
-        <v>91258</v>
+        <v>91262</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>125755625</v>
       </c>
       <c r="B28" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         <v>125755539</v>
       </c>
       <c r="B29" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125735540</v>
+        <v>125755544</v>
       </c>
       <c r="B30" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,37 +3412,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523479</v>
+        <v>523483</v>
       </c>
       <c r="R30" t="n">
-        <v>6845406</v>
+        <v>6845181</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3486,22 +3486,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755787</v>
+        <v>125734860</v>
       </c>
       <c r="B31" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,37 +3509,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523457</v>
+        <v>523673</v>
       </c>
       <c r="R31" t="n">
-        <v>6845237</v>
+        <v>6845294</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B32" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,37 +3606,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R32" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3680,22 +3680,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125734860</v>
+        <v>125755787</v>
       </c>
       <c r="B33" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3703,37 +3703,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523673</v>
+        <v>523457</v>
       </c>
       <c r="R33" t="n">
-        <v>6845294</v>
+        <v>6845237</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3777,22 +3777,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755626</v>
+        <v>125735128</v>
       </c>
       <c r="B34" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3800,37 +3800,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523759</v>
+        <v>523627</v>
       </c>
       <c r="R34" t="n">
-        <v>6845238</v>
+        <v>6845420</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3874,22 +3874,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735128</v>
+        <v>125737014</v>
       </c>
       <c r="B35" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3897,34 +3897,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523627</v>
+        <v>523854</v>
       </c>
       <c r="R35" t="n">
-        <v>6845420</v>
+        <v>6845289</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -3983,48 +3983,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125737014</v>
+        <v>125755658</v>
       </c>
       <c r="B36" t="n">
-        <v>78732</v>
+        <v>91403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523854</v>
+        <v>523487</v>
       </c>
       <c r="R36" t="n">
-        <v>6845289</v>
+        <v>6845098</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4068,44 +4068,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125755658</v>
+        <v>125755792</v>
       </c>
       <c r="B37" t="n">
-        <v>91399</v>
+        <v>92526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1503</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>523487</v>
+        <v>523992</v>
       </c>
       <c r="R37" t="n">
-        <v>6845098</v>
+        <v>6845170</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4151,6 +4151,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4180,7 +4185,7 @@
         <v>125755717</v>
       </c>
       <c r="B38" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4274,32 +4279,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>125755792</v>
+        <v>125755552</v>
       </c>
       <c r="B39" t="n">
-        <v>92522</v>
+        <v>91207</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4309,10 +4314,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>523992</v>
+        <v>523424</v>
       </c>
       <c r="R39" t="n">
-        <v>6845170</v>
+        <v>6845383</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4345,11 +4350,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Gammal fruktkropp</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4376,32 +4376,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755552</v>
+        <v>125755626</v>
       </c>
       <c r="B40" t="n">
-        <v>91203</v>
+        <v>78736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4411,10 +4411,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523424</v>
+        <v>523759</v>
       </c>
       <c r="R40" t="n">
-        <v>6845383</v>
+        <v>6845238</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755543</v>
+        <v>125755636</v>
       </c>
       <c r="B41" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,21 +4484,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4508,10 +4508,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523460</v>
+        <v>523511</v>
       </c>
       <c r="R41" t="n">
-        <v>6845221</v>
+        <v>6845102</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4570,10 +4570,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755542</v>
+        <v>125755627</v>
       </c>
       <c r="B42" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523670</v>
+        <v>523755</v>
       </c>
       <c r="R42" t="n">
-        <v>6845353</v>
+        <v>6845251</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755636</v>
+        <v>125755628</v>
       </c>
       <c r="B43" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523511</v>
+        <v>523728</v>
       </c>
       <c r="R43" t="n">
-        <v>6845102</v>
+        <v>6845279</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4764,10 +4764,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755627</v>
+        <v>125755543</v>
       </c>
       <c r="B44" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4775,21 +4775,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4799,10 +4799,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523755</v>
+        <v>523460</v>
       </c>
       <c r="R44" t="n">
-        <v>6845251</v>
+        <v>6845221</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4861,48 +4861,58 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755628</v>
+        <v>125736061</v>
       </c>
       <c r="B45" t="n">
-        <v>78732</v>
+        <v>56848</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523728</v>
+        <v>523643</v>
       </c>
       <c r="R45" t="n">
-        <v>6845279</v>
+        <v>6845391</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4946,67 +4956,57 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125736061</v>
+        <v>125732709</v>
       </c>
       <c r="B46" t="n">
-        <v>56844</v>
+        <v>78736</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523643</v>
+        <v>523548</v>
       </c>
       <c r="R46" t="n">
-        <v>6845391</v>
+        <v>6845076</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5065,10 +5065,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125732709</v>
+        <v>125755542</v>
       </c>
       <c r="B47" t="n">
-        <v>78732</v>
+        <v>79595</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5076,37 +5076,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523548</v>
+        <v>523670</v>
       </c>
       <c r="R47" t="n">
-        <v>6845076</v>
+        <v>6845353</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5150,69 +5150,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125755647</v>
+        <v>125735337</v>
       </c>
       <c r="B48" t="n">
-        <v>98345</v>
+        <v>78736</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523408</v>
+        <v>523593</v>
       </c>
       <c r="R48" t="n">
-        <v>6845401</v>
+        <v>6845417</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5256,22 +5247,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125736672</v>
+        <v>125734972</v>
       </c>
       <c r="B49" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5279,34 +5270,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523827</v>
+        <v>523675</v>
       </c>
       <c r="R49" t="n">
-        <v>6845310</v>
+        <v>6845339</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5368,7 +5359,7 @@
         <v>125735892</v>
       </c>
       <c r="B50" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5462,10 +5453,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125735337</v>
+        <v>125736672</v>
       </c>
       <c r="B51" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5473,34 +5464,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523593</v>
+        <v>523827</v>
       </c>
       <c r="R51" t="n">
-        <v>6845417</v>
+        <v>6845310</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5559,48 +5550,57 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125734972</v>
+        <v>125755647</v>
       </c>
       <c r="B52" t="n">
-        <v>78732</v>
+        <v>98349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523675</v>
+        <v>523408</v>
       </c>
       <c r="R52" t="n">
-        <v>6845339</v>
+        <v>6845401</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5644,22 +5644,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755788</v>
+        <v>125755630</v>
       </c>
       <c r="B53" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523460</v>
+        <v>523671</v>
       </c>
       <c r="R53" t="n">
-        <v>6845221</v>
+        <v>6845353</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5753,10 +5753,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755630</v>
+        <v>125755629</v>
       </c>
       <c r="B54" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523671</v>
+        <v>523679</v>
       </c>
       <c r="R54" t="n">
-        <v>6845353</v>
+        <v>6845347</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5850,10 +5850,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755629</v>
+        <v>125734739</v>
       </c>
       <c r="B55" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5881,17 +5881,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523679</v>
+        <v>523608</v>
       </c>
       <c r="R55" t="n">
-        <v>6845347</v>
+        <v>6845309</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125734739</v>
+        <v>125755788</v>
       </c>
       <c r="B56" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5958,37 +5958,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523608</v>
+        <v>523460</v>
       </c>
       <c r="R56" t="n">
-        <v>6845309</v>
+        <v>6845221</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6032,44 +6032,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755598</v>
+        <v>125755709</v>
       </c>
       <c r="B57" t="n">
-        <v>97223</v>
+        <v>78977</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6079,10 +6079,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523351</v>
+        <v>523598</v>
       </c>
       <c r="R57" t="n">
-        <v>6845393</v>
+        <v>6845380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6144,7 +6144,7 @@
         <v>125755761</v>
       </c>
       <c r="B58" t="n">
-        <v>57652</v>
+        <v>57656</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6243,32 +6243,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755709</v>
+        <v>125755598</v>
       </c>
       <c r="B59" t="n">
-        <v>78973</v>
+        <v>97227</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6278,10 +6278,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523598</v>
+        <v>523351</v>
       </c>
       <c r="R59" t="n">
-        <v>6845380</v>
+        <v>6845393</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6340,10 +6340,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125755714</v>
+        <v>125755541</v>
       </c>
       <c r="B60" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6351,21 +6351,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>523383</v>
+        <v>523757</v>
       </c>
       <c r="R60" t="n">
-        <v>6845391</v>
+        <v>6845248</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6440,7 +6440,7 @@
         <v>125755701</v>
       </c>
       <c r="B61" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6537,7 +6537,7 @@
         <v>125755707</v>
       </c>
       <c r="B62" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6631,32 +6631,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>125755541</v>
+        <v>125755794</v>
       </c>
       <c r="B63" t="n">
-        <v>79591</v>
+        <v>91652</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6453</v>
+        <v>4217</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6666,10 +6666,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>523757</v>
+        <v>523385</v>
       </c>
       <c r="R63" t="n">
-        <v>6845248</v>
+        <v>6845416</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6702,6 +6702,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6728,32 +6733,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>125755794</v>
+        <v>125755714</v>
       </c>
       <c r="B64" t="n">
-        <v>91648</v>
+        <v>78977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4217</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6763,10 +6768,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>523385</v>
+        <v>523383</v>
       </c>
       <c r="R64" t="n">
-        <v>6845416</v>
+        <v>6845391</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6799,11 +6804,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6833,7 +6833,7 @@
         <v>125755621</v>
       </c>
       <c r="B65" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>125732736</v>
       </c>
       <c r="B66" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>125737510</v>
       </c>
       <c r="B67" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755702</v>
+        <v>125755789</v>
       </c>
       <c r="B68" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7132,21 +7132,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7156,10 +7156,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523829</v>
+        <v>523480</v>
       </c>
       <c r="R68" t="n">
-        <v>6845308</v>
+        <v>6845112</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,10 +7218,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755789</v>
+        <v>125755702</v>
       </c>
       <c r="B69" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7229,21 +7229,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523480</v>
+        <v>523829</v>
       </c>
       <c r="R69" t="n">
-        <v>6845112</v>
+        <v>6845308</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755697</v>
+        <v>125755700</v>
       </c>
       <c r="B70" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523948</v>
+        <v>523859</v>
       </c>
       <c r="R70" t="n">
-        <v>6845177</v>
+        <v>6845221</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755700</v>
+        <v>125755783</v>
       </c>
       <c r="B71" t="n">
-        <v>78973</v>
+        <v>78644</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523859</v>
+        <v>523644</v>
       </c>
       <c r="R71" t="n">
-        <v>6845221</v>
+        <v>6845379</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,45 +7509,54 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755783</v>
+        <v>125755654</v>
       </c>
       <c r="B72" t="n">
-        <v>78640</v>
+        <v>98349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523644</v>
+        <v>523428</v>
       </c>
       <c r="R72" t="n">
-        <v>6845379</v>
+        <v>6845361</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,32 +7615,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755775</v>
+        <v>125755697</v>
       </c>
       <c r="B73" t="n">
-        <v>92528</v>
+        <v>78977</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7641,10 +7650,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523541</v>
+        <v>523948</v>
       </c>
       <c r="R73" t="n">
-        <v>6845044</v>
+        <v>6845177</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7703,32 +7712,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755553</v>
+        <v>125755775</v>
       </c>
       <c r="B74" t="n">
-        <v>79562</v>
+        <v>92532</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7738,10 +7747,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523626</v>
+        <v>523541</v>
       </c>
       <c r="R74" t="n">
-        <v>6845383</v>
+        <v>6845044</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7800,54 +7809,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125755654</v>
+        <v>125755553</v>
       </c>
       <c r="B75" t="n">
-        <v>98345</v>
+        <v>79566</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>523428</v>
+        <v>523626</v>
       </c>
       <c r="R75" t="n">
-        <v>6845361</v>
+        <v>6845383</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755624</v>
+        <v>125755781</v>
       </c>
       <c r="B76" t="n">
-        <v>78732</v>
+        <v>78644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523853</v>
+        <v>523958</v>
       </c>
       <c r="R76" t="n">
-        <v>6845279</v>
+        <v>6845195</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8003,10 +8003,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755781</v>
+        <v>125755694</v>
       </c>
       <c r="B77" t="n">
-        <v>78640</v>
+        <v>78977</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8014,21 +8014,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523958</v>
+        <v>523979</v>
       </c>
       <c r="R77" t="n">
-        <v>6845195</v>
+        <v>6845154</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755694</v>
+        <v>125755774</v>
       </c>
       <c r="B78" t="n">
-        <v>78973</v>
+        <v>92532</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523979</v>
+        <v>523526</v>
       </c>
       <c r="R78" t="n">
-        <v>6845154</v>
+        <v>6845095</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8197,32 +8197,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755774</v>
+        <v>125755624</v>
       </c>
       <c r="B79" t="n">
-        <v>92528</v>
+        <v>78736</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523526</v>
+        <v>523853</v>
       </c>
       <c r="R79" t="n">
-        <v>6845095</v>
+        <v>6845279</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125755712</v>
+        <v>125734280</v>
       </c>
       <c r="B81" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8427,17 +8427,17 @@
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523428</v>
+        <v>523482</v>
       </c>
       <c r="R81" t="n">
-        <v>6845361</v>
+        <v>6845199</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8481,22 +8481,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125734280</v>
+        <v>125755550</v>
       </c>
       <c r="B82" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8504,37 +8504,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523482</v>
+        <v>523604</v>
       </c>
       <c r="R82" t="n">
-        <v>6845199</v>
+        <v>6845013</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8578,22 +8578,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755620</v>
+        <v>125755712</v>
       </c>
       <c r="B83" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8601,21 +8601,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523925</v>
+        <v>523428</v>
       </c>
       <c r="R83" t="n">
-        <v>6845214</v>
+        <v>6845361</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8687,10 +8687,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125737335</v>
+        <v>125755547</v>
       </c>
       <c r="B84" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8718,17 +8718,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523835</v>
+        <v>523479</v>
       </c>
       <c r="R84" t="n">
-        <v>6845199</v>
+        <v>6845112</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -8772,22 +8772,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B85" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8815,17 +8815,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R85" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8869,22 +8869,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755547</v>
+        <v>125755620</v>
       </c>
       <c r="B86" t="n">
-        <v>79591</v>
+        <v>78736</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8892,21 +8892,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523479</v>
+        <v>523925</v>
       </c>
       <c r="R86" t="n">
-        <v>6845112</v>
+        <v>6845214</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,10 +8978,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>125755617</v>
+        <v>125755713</v>
       </c>
       <c r="B87" t="n">
-        <v>78732</v>
+        <v>78977</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8989,21 +8989,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9013,10 +9013,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>523972</v>
+        <v>523332</v>
       </c>
       <c r="R87" t="n">
-        <v>6845173</v>
+        <v>6845377</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9078,7 +9078,7 @@
         <v>125755706</v>
       </c>
       <c r="B88" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9172,10 +9172,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>125755713</v>
+        <v>125755617</v>
       </c>
       <c r="B89" t="n">
-        <v>78973</v>
+        <v>78736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9183,21 +9183,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9207,10 +9207,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>523332</v>
+        <v>523972</v>
       </c>
       <c r="R89" t="n">
-        <v>6845377</v>
+        <v>6845173</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9272,7 +9272,7 @@
         <v>125755635</v>
       </c>
       <c r="B90" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>125755651</v>
       </c>
       <c r="B91" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9472,10 +9472,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755631</v>
+        <v>125755555</v>
       </c>
       <c r="B92" t="n">
-        <v>78732</v>
+        <v>90280</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9483,21 +9483,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>1962</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523636</v>
+        <v>523480</v>
       </c>
       <c r="R92" t="n">
-        <v>6845388</v>
+        <v>6845111</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755619</v>
+        <v>125755601</v>
       </c>
       <c r="B93" t="n">
-        <v>78732</v>
+        <v>92724</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9580,21 +9580,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523952</v>
+        <v>523463</v>
       </c>
       <c r="R93" t="n">
-        <v>6845185</v>
+        <v>6845230</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9666,10 +9666,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755784</v>
+        <v>125755631</v>
       </c>
       <c r="B94" t="n">
-        <v>78640</v>
+        <v>78736</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9677,21 +9677,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523606</v>
+        <v>523636</v>
       </c>
       <c r="R94" t="n">
-        <v>6845378</v>
+        <v>6845388</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9763,10 +9763,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755555</v>
+        <v>125755619</v>
       </c>
       <c r="B95" t="n">
-        <v>90276</v>
+        <v>78736</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9774,21 +9774,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1962</v>
+        <v>228912</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523480</v>
+        <v>523952</v>
       </c>
       <c r="R95" t="n">
-        <v>6845111</v>
+        <v>6845185</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755601</v>
+        <v>125755784</v>
       </c>
       <c r="B96" t="n">
-        <v>92720</v>
+        <v>78644</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9871,21 +9871,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2079</v>
+        <v>353</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523463</v>
+        <v>523606</v>
       </c>
       <c r="R96" t="n">
-        <v>6845230</v>
+        <v>6845378</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -9960,7 +9960,7 @@
         <v>125755563</v>
       </c>
       <c r="B97" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10165,10 +10165,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>125755704</v>
+        <v>125755557</v>
       </c>
       <c r="B99" t="n">
-        <v>78973</v>
+        <v>91242</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10176,21 +10176,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10200,10 +10200,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>523760</v>
+        <v>523340</v>
       </c>
       <c r="R99" t="n">
-        <v>6845283</v>
+        <v>6845392</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125755715</v>
+        <v>125734818</v>
       </c>
       <c r="B100" t="n">
-        <v>78973</v>
+        <v>91262</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10273,37 +10273,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523450</v>
+        <v>523643</v>
       </c>
       <c r="R100" t="n">
-        <v>6845349</v>
+        <v>6845282</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10347,22 +10347,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>125755557</v>
+        <v>125755704</v>
       </c>
       <c r="B101" t="n">
-        <v>91238</v>
+        <v>78977</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10370,21 +10370,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10394,10 +10394,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>523340</v>
+        <v>523760</v>
       </c>
       <c r="R101" t="n">
-        <v>6845392</v>
+        <v>6845283</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10459,7 +10459,7 @@
         <v>125755780</v>
       </c>
       <c r="B102" t="n">
-        <v>78640</v>
+        <v>78644</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125734818</v>
+        <v>125755715</v>
       </c>
       <c r="B103" t="n">
-        <v>91258</v>
+        <v>78977</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10564,37 +10564,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523643</v>
+        <v>523450</v>
       </c>
       <c r="R103" t="n">
-        <v>6845282</v>
+        <v>6845349</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10638,22 +10638,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>125737411</v>
+        <v>125736529</v>
       </c>
       <c r="B104" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10681,14 +10681,14 @@
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>523825</v>
+        <v>523524</v>
       </c>
       <c r="R104" t="n">
-        <v>6845311</v>
+        <v>6845323</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -10747,10 +10747,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>125734476</v>
+        <v>125737411</v>
       </c>
       <c r="B105" t="n">
-        <v>79591</v>
+        <v>78977</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10758,34 +10758,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>523492</v>
+        <v>523825</v>
       </c>
       <c r="R105" t="n">
-        <v>6845165</v>
+        <v>6845311</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -10844,10 +10844,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>125736529</v>
+        <v>125734228</v>
       </c>
       <c r="B106" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>523524</v>
+        <v>523467</v>
       </c>
       <c r="R106" t="n">
-        <v>6845323</v>
+        <v>6845121</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -10941,10 +10941,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>125734228</v>
+        <v>125734476</v>
       </c>
       <c r="B107" t="n">
-        <v>78973</v>
+        <v>79595</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10952,21 +10952,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -10976,10 +10976,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>523467</v>
+        <v>523492</v>
       </c>
       <c r="R107" t="n">
-        <v>6845121</v>
+        <v>6845165</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11038,49 +11038,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B108" t="n">
-        <v>98345</v>
+        <v>78977</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R108" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11139,45 +11135,49 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125736051</v>
+        <v>125735595</v>
       </c>
       <c r="B109" t="n">
-        <v>78973</v>
+        <v>98349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523418</v>
+        <v>523492</v>
       </c>
       <c r="R109" t="n">
-        <v>6845349</v>
+        <v>6845165</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11239,7 +11239,7 @@
         <v>125737958</v>
       </c>
       <c r="B110" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
         <v>125736021</v>
       </c>
       <c r="B111" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11433,7 +11433,7 @@
         <v>125733581</v>
       </c>
       <c r="B112" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>125737629</v>
       </c>
       <c r="B113" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -11627,7 +11627,7 @@
         <v>125734662</v>
       </c>
       <c r="B114" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -11721,10 +11721,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>125734241</v>
+        <v>125736099</v>
       </c>
       <c r="B115" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -11756,10 +11756,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>523492</v>
+        <v>523514</v>
       </c>
       <c r="R115" t="n">
-        <v>6845165</v>
+        <v>6845340</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -11818,10 +11818,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>125736099</v>
+        <v>125734241</v>
       </c>
       <c r="B116" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11853,10 +11853,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>523514</v>
+        <v>523492</v>
       </c>
       <c r="R116" t="n">
-        <v>6845340</v>
+        <v>6845165</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -11918,7 +11918,7 @@
         <v>125734655</v>
       </c>
       <c r="B117" t="n">
-        <v>78732</v>
+        <v>78736</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -12012,10 +12012,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125733520</v>
+        <v>125738012</v>
       </c>
       <c r="B118" t="n">
-        <v>78973</v>
+        <v>57656</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12023,34 +12023,39 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523552</v>
+        <v>523967</v>
       </c>
       <c r="R118" t="n">
-        <v>6845072</v>
+        <v>6845175</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12109,10 +12114,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125738012</v>
+        <v>125733520</v>
       </c>
       <c r="B119" t="n">
-        <v>57652</v>
+        <v>78977</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -12120,39 +12125,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523967</v>
+        <v>523552</v>
       </c>
       <c r="R119" t="n">
-        <v>6845175</v>
+        <v>6845072</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12214,7 +12214,7 @@
         <v>125733632</v>
       </c>
       <c r="B120" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>125735686</v>
       </c>
       <c r="B121" t="n">
-        <v>98345</v>
+        <v>98349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12412,7 +12412,7 @@
         <v>125732728</v>
       </c>
       <c r="B122" t="n">
-        <v>92528</v>
+        <v>92532</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>125737769</v>
       </c>
       <c r="B123" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>125736651</v>
       </c>
       <c r="B124" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -12704,10 +12704,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>125737839</v>
+        <v>125736699</v>
       </c>
       <c r="B125" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -12715,21 +12715,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -12739,10 +12739,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>523967</v>
+        <v>523766</v>
       </c>
       <c r="R125" t="n">
-        <v>6845175</v>
+        <v>6845303</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125736699</v>
+        <v>125737839</v>
       </c>
       <c r="B126" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -12812,21 +12812,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -12836,10 +12836,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>523766</v>
+        <v>523967</v>
       </c>
       <c r="R126" t="n">
-        <v>6845303</v>
+        <v>6845175</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125736623</v>
+        <v>125732643</v>
       </c>
       <c r="B127" t="n">
-        <v>78973</v>
+        <v>79566</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523689</v>
+        <v>523617</v>
       </c>
       <c r="R127" t="n">
-        <v>6845339</v>
+        <v>6845031</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125732643</v>
+        <v>125736623</v>
       </c>
       <c r="B128" t="n">
-        <v>79562</v>
+        <v>78977</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523617</v>
+        <v>523689</v>
       </c>
       <c r="R128" t="n">
-        <v>6845031</v>
+        <v>6845339</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13095,7 +13095,7 @@
         <v>125732670</v>
       </c>
       <c r="B129" t="n">
-        <v>79591</v>
+        <v>79595</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125734647</v>
+        <v>125755708</v>
       </c>
       <c r="B5" t="n">
         <v>78977</v>
@@ -997,17 +997,17 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523611</v>
+        <v>523626</v>
       </c>
       <c r="R5" t="n">
-        <v>6845275</v>
+        <v>6845380</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1051,19 +1051,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755708</v>
+        <v>125755716</v>
       </c>
       <c r="B6" t="n">
         <v>78977</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523626</v>
+        <v>523477</v>
       </c>
       <c r="R6" t="n">
-        <v>6845380</v>
+        <v>6845219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R7" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755698</v>
+        <v>125755711</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523867</v>
+        <v>523443</v>
       </c>
       <c r="R8" t="n">
-        <v>6845227</v>
+        <v>6845363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755711</v>
+        <v>125734647</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523443</v>
+        <v>523611</v>
       </c>
       <c r="R9" t="n">
-        <v>6845363</v>
+        <v>6845275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,12 +1439,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755719</v>
+        <v>125755790</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,21 +2044,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523554</v>
+        <v>523486</v>
       </c>
       <c r="R16" t="n">
-        <v>6845068</v>
+        <v>6845100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755593</v>
+        <v>125755719</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,39 +2141,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523520</v>
+        <v>523554</v>
       </c>
       <c r="R17" t="n">
-        <v>6845094</v>
+        <v>6845068</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2206,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2237,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755790</v>
+        <v>125755593</v>
       </c>
       <c r="B18" t="n">
-        <v>78644</v>
+        <v>57656</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2248,34 +2238,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523486</v>
+        <v>523520</v>
       </c>
       <c r="R18" t="n">
-        <v>6845100</v>
+        <v>6845094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2308,6 +2303,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3304,10 +3304,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125755539</v>
+        <v>125755787</v>
       </c>
       <c r="B29" t="n">
-        <v>79595</v>
+        <v>78644</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3315,21 +3315,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>523924</v>
+        <v>523457</v>
       </c>
       <c r="R29" t="n">
-        <v>6845215</v>
+        <v>6845237</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3401,7 +3401,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755544</v>
+        <v>125755539</v>
       </c>
       <c r="B30" t="n">
         <v>79595</v>
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523483</v>
+        <v>523924</v>
       </c>
       <c r="R30" t="n">
-        <v>6845181</v>
+        <v>6845215</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125734860</v>
+        <v>125755544</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,37 +3509,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523673</v>
+        <v>523483</v>
       </c>
       <c r="R31" t="n">
-        <v>6845294</v>
+        <v>6845181</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,19 +3583,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125735540</v>
+        <v>125734860</v>
       </c>
       <c r="B32" t="n">
         <v>78977</v>
@@ -3630,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523479</v>
+        <v>523673</v>
       </c>
       <c r="R32" t="n">
-        <v>6845406</v>
+        <v>6845294</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3692,10 +3692,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755787</v>
+        <v>125735540</v>
       </c>
       <c r="B33" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3703,37 +3703,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523457</v>
+        <v>523479</v>
       </c>
       <c r="R33" t="n">
-        <v>6845237</v>
+        <v>6845406</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3777,60 +3777,60 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125735128</v>
+        <v>125755658</v>
       </c>
       <c r="B34" t="n">
-        <v>79595</v>
+        <v>91403</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523627</v>
+        <v>523487</v>
       </c>
       <c r="R34" t="n">
-        <v>6845420</v>
+        <v>6845098</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3874,22 +3874,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125737014</v>
+        <v>125735128</v>
       </c>
       <c r="B35" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3897,34 +3897,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523854</v>
+        <v>523627</v>
       </c>
       <c r="R35" t="n">
-        <v>6845289</v>
+        <v>6845420</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -3983,48 +3983,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125755658</v>
+        <v>125737014</v>
       </c>
       <c r="B36" t="n">
-        <v>91403</v>
+        <v>78736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523487</v>
+        <v>523854</v>
       </c>
       <c r="R36" t="n">
-        <v>6845098</v>
+        <v>6845289</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4068,12 +4068,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4473,7 +4473,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125755636</v>
+        <v>125732709</v>
       </c>
       <c r="B41" t="n">
         <v>78736</v>
@@ -4504,17 +4504,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523511</v>
+        <v>523548</v>
       </c>
       <c r="R41" t="n">
-        <v>6845102</v>
+        <v>6845076</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4558,22 +4558,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755627</v>
+        <v>125755542</v>
       </c>
       <c r="B42" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4581,21 +4581,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523755</v>
+        <v>523670</v>
       </c>
       <c r="R42" t="n">
-        <v>6845251</v>
+        <v>6845353</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,10 +4667,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755628</v>
+        <v>125755543</v>
       </c>
       <c r="B43" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4678,21 +4678,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4702,10 +4702,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523728</v>
+        <v>523460</v>
       </c>
       <c r="R43" t="n">
-        <v>6845279</v>
+        <v>6845221</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4764,48 +4764,58 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755543</v>
+        <v>125736061</v>
       </c>
       <c r="B44" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523460</v>
+        <v>523643</v>
       </c>
       <c r="R44" t="n">
-        <v>6845221</v>
+        <v>6845391</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4849,70 +4859,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125736061</v>
+        <v>125755636</v>
       </c>
       <c r="B45" t="n">
-        <v>56848</v>
+        <v>78736</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523643</v>
+        <v>523511</v>
       </c>
       <c r="R45" t="n">
-        <v>6845391</v>
+        <v>6845102</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4956,19 +4956,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125732709</v>
+        <v>125755627</v>
       </c>
       <c r="B46" t="n">
         <v>78736</v>
@@ -4999,17 +4999,17 @@
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523548</v>
+        <v>523755</v>
       </c>
       <c r="R46" t="n">
-        <v>6845076</v>
+        <v>6845251</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5053,22 +5053,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755542</v>
+        <v>125755628</v>
       </c>
       <c r="B47" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5076,21 +5076,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5100,10 +5100,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523670</v>
+        <v>523728</v>
       </c>
       <c r="R47" t="n">
-        <v>6845353</v>
+        <v>6845279</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5656,10 +5656,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755630</v>
+        <v>125755788</v>
       </c>
       <c r="B53" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523671</v>
+        <v>523460</v>
       </c>
       <c r="R53" t="n">
-        <v>6845353</v>
+        <v>6845221</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5753,32 +5753,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755629</v>
+        <v>125755598</v>
       </c>
       <c r="B54" t="n">
-        <v>78736</v>
+        <v>97227</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523679</v>
+        <v>523351</v>
       </c>
       <c r="R54" t="n">
-        <v>6845347</v>
+        <v>6845393</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5850,7 +5850,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125734739</v>
+        <v>125755630</v>
       </c>
       <c r="B55" t="n">
         <v>78736</v>
@@ -5881,17 +5881,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523608</v>
+        <v>523671</v>
       </c>
       <c r="R55" t="n">
-        <v>6845309</v>
+        <v>6845353</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5935,22 +5935,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755788</v>
+        <v>125755629</v>
       </c>
       <c r="B56" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5958,21 +5958,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5982,10 +5982,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523460</v>
+        <v>523679</v>
       </c>
       <c r="R56" t="n">
-        <v>6845221</v>
+        <v>6845347</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6243,48 +6243,48 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125755598</v>
+        <v>125734739</v>
       </c>
       <c r="B59" t="n">
-        <v>97227</v>
+        <v>78736</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>221945</v>
+        <v>228912</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523351</v>
+        <v>523608</v>
       </c>
       <c r="R59" t="n">
-        <v>6845393</v>
+        <v>6845309</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6328,12 +6328,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755781</v>
+        <v>125755624</v>
       </c>
       <c r="B76" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523958</v>
+        <v>523853</v>
       </c>
       <c r="R76" t="n">
-        <v>6845195</v>
+        <v>6845279</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8003,32 +8003,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125755694</v>
+        <v>125755774</v>
       </c>
       <c r="B77" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8038,10 +8038,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>523979</v>
+        <v>523526</v>
       </c>
       <c r="R77" t="n">
-        <v>6845154</v>
+        <v>6845095</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8100,32 +8100,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755774</v>
+        <v>125755781</v>
       </c>
       <c r="B78" t="n">
-        <v>92532</v>
+        <v>78644</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523526</v>
+        <v>523958</v>
       </c>
       <c r="R78" t="n">
-        <v>6845095</v>
+        <v>6845195</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8197,10 +8197,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755624</v>
+        <v>125755694</v>
       </c>
       <c r="B79" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8208,21 +8208,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8232,10 +8232,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523853</v>
+        <v>523979</v>
       </c>
       <c r="R79" t="n">
-        <v>6845279</v>
+        <v>6845154</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8493,7 +8493,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>125755550</v>
+        <v>125737335</v>
       </c>
       <c r="B82" t="n">
         <v>79595</v>
@@ -8524,17 +8524,17 @@
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>523604</v>
+        <v>523835</v>
       </c>
       <c r="R82" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -8578,22 +8578,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755712</v>
+        <v>125755550</v>
       </c>
       <c r="B83" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8601,21 +8601,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8625,10 +8625,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523428</v>
+        <v>523604</v>
       </c>
       <c r="R83" t="n">
-        <v>6845361</v>
+        <v>6845013</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8687,10 +8687,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>125755547</v>
+        <v>125755712</v>
       </c>
       <c r="B84" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8698,21 +8698,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8722,10 +8722,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>523479</v>
+        <v>523428</v>
       </c>
       <c r="R84" t="n">
-        <v>6845112</v>
+        <v>6845361</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8784,7 +8784,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125737335</v>
+        <v>125755547</v>
       </c>
       <c r="B85" t="n">
         <v>79595</v>
@@ -8815,17 +8815,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523835</v>
+        <v>523479</v>
       </c>
       <c r="R85" t="n">
-        <v>6845199</v>
+        <v>6845112</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -8869,12 +8869,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125732643</v>
+        <v>125736623</v>
       </c>
       <c r="B127" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523617</v>
+        <v>523689</v>
       </c>
       <c r="R127" t="n">
-        <v>6845031</v>
+        <v>6845339</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125736623</v>
+        <v>125732643</v>
       </c>
       <c r="B128" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523689</v>
+        <v>523617</v>
       </c>
       <c r="R128" t="n">
-        <v>6845339</v>
+        <v>6845031</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125755643</v>
+        <v>125755703</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>523816</v>
+        <v>523783</v>
       </c>
       <c r="R2" t="n">
-        <v>6845298</v>
+        <v>6845289</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125755703</v>
+        <v>125755705</v>
       </c>
       <c r="B3" t="n">
         <v>78977</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>523783</v>
+        <v>523728</v>
       </c>
       <c r="R3" t="n">
-        <v>6845289</v>
+        <v>6845268</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125755705</v>
+        <v>125755643</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>523728</v>
+        <v>523816</v>
       </c>
       <c r="R4" t="n">
-        <v>6845268</v>
+        <v>6845298</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755708</v>
+        <v>125755632</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523626</v>
+        <v>523621</v>
       </c>
       <c r="R5" t="n">
-        <v>6845380</v>
+        <v>6845375</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755716</v>
+        <v>125755708</v>
       </c>
       <c r="B6" t="n">
         <v>78977</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523477</v>
+        <v>523626</v>
       </c>
       <c r="R6" t="n">
-        <v>6845219</v>
+        <v>6845380</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755698</v>
+        <v>125755716</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523867</v>
+        <v>523477</v>
       </c>
       <c r="R7" t="n">
-        <v>6845227</v>
+        <v>6845219</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755711</v>
+        <v>125755698</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523443</v>
+        <v>523867</v>
       </c>
       <c r="R8" t="n">
-        <v>6845363</v>
+        <v>6845227</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125734647</v>
+        <v>125755711</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523611</v>
+        <v>523443</v>
       </c>
       <c r="R9" t="n">
-        <v>6845275</v>
+        <v>6845363</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125755632</v>
+        <v>125734647</v>
       </c>
       <c r="B10" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523621</v>
+        <v>523611</v>
       </c>
       <c r="R10" t="n">
-        <v>6845375</v>
+        <v>6845275</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125755786</v>
+        <v>125733598</v>
       </c>
       <c r="B11" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523474</v>
+        <v>523483</v>
       </c>
       <c r="R11" t="n">
-        <v>6845244</v>
+        <v>6845118</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755785</v>
+        <v>125755693</v>
       </c>
       <c r="B12" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523467</v>
+        <v>523993</v>
       </c>
       <c r="R12" t="n">
-        <v>6845333</v>
+        <v>6845158</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755693</v>
+        <v>125755710</v>
       </c>
       <c r="B13" t="n">
         <v>78977</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523993</v>
+        <v>523572</v>
       </c>
       <c r="R13" t="n">
-        <v>6845158</v>
+        <v>6845367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755710</v>
+        <v>125755786</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523572</v>
+        <v>523474</v>
       </c>
       <c r="R14" t="n">
-        <v>6845367</v>
+        <v>6845244</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125733598</v>
+        <v>125755785</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,37 +1947,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523483</v>
+        <v>523467</v>
       </c>
       <c r="R15" t="n">
-        <v>6845118</v>
+        <v>6845333</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2021,12 +2021,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2130,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755719</v>
+        <v>125755593</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,34 +2141,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523554</v>
+        <v>523520</v>
       </c>
       <c r="R17" t="n">
-        <v>6845068</v>
+        <v>6845094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2201,6 +2206,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2227,10 +2237,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125755593</v>
+        <v>125735304</v>
       </c>
       <c r="B18" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2238,42 +2248,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523520</v>
+        <v>523580</v>
       </c>
       <c r="R18" t="n">
-        <v>6845094</v>
+        <v>6845417</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2303,11 +2308,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2322,22 +2322,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125735304</v>
+        <v>125733851</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,21 +2345,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2369,10 +2369,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523580</v>
+        <v>523470</v>
       </c>
       <c r="R19" t="n">
-        <v>6845417</v>
+        <v>6845106</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2431,10 +2431,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125733851</v>
+        <v>125755719</v>
       </c>
       <c r="B20" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,37 +2442,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523470</v>
+        <v>523554</v>
       </c>
       <c r="R20" t="n">
-        <v>6845106</v>
+        <v>6845068</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2516,12 +2516,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2625,32 +2625,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125755657</v>
+        <v>125755634</v>
       </c>
       <c r="B22" t="n">
-        <v>91403</v>
+        <v>78736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>523463</v>
+        <v>523498</v>
       </c>
       <c r="R22" t="n">
-        <v>6845211</v>
+        <v>6845404</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2722,32 +2722,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125755545</v>
+        <v>125755657</v>
       </c>
       <c r="B23" t="n">
-        <v>79595</v>
+        <v>91403</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>1503</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2757,10 +2757,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>523465</v>
+        <v>523463</v>
       </c>
       <c r="R23" t="n">
-        <v>6845109</v>
+        <v>6845211</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2819,7 +2819,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125755549</v>
+        <v>125755545</v>
       </c>
       <c r="B24" t="n">
         <v>79595</v>
@@ -2854,10 +2854,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>523541</v>
+        <v>523465</v>
       </c>
       <c r="R24" t="n">
-        <v>6845054</v>
+        <v>6845109</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2916,10 +2916,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125755634</v>
+        <v>125755549</v>
       </c>
       <c r="B25" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2927,21 +2927,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2951,10 +2951,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>523498</v>
+        <v>523541</v>
       </c>
       <c r="R25" t="n">
-        <v>6845404</v>
+        <v>6845054</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125755539</v>
+        <v>125734860</v>
       </c>
       <c r="B30" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,37 +3412,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523924</v>
+        <v>523673</v>
       </c>
       <c r="R30" t="n">
-        <v>6845215</v>
+        <v>6845294</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3486,22 +3486,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125755544</v>
+        <v>125735540</v>
       </c>
       <c r="B31" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,37 +3509,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523483</v>
+        <v>523479</v>
       </c>
       <c r="R31" t="n">
-        <v>6845181</v>
+        <v>6845406</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125734860</v>
+        <v>125755544</v>
       </c>
       <c r="B32" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,37 +3606,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523673</v>
+        <v>523483</v>
       </c>
       <c r="R32" t="n">
-        <v>6845294</v>
+        <v>6845181</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3680,22 +3680,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B33" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3703,37 +3703,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R33" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3777,44 +3777,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125755658</v>
+        <v>125755626</v>
       </c>
       <c r="B34" t="n">
-        <v>91403</v>
+        <v>78736</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1503</v>
+        <v>228912</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3824,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>523487</v>
+        <v>523759</v>
       </c>
       <c r="R34" t="n">
-        <v>6845098</v>
+        <v>6845238</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3886,10 +3886,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125735128</v>
+        <v>125737014</v>
       </c>
       <c r="B35" t="n">
-        <v>79595</v>
+        <v>78736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3897,34 +3897,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>523627</v>
+        <v>523854</v>
       </c>
       <c r="R35" t="n">
-        <v>6845420</v>
+        <v>6845289</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -3983,48 +3983,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125737014</v>
+        <v>125755658</v>
       </c>
       <c r="B36" t="n">
-        <v>78736</v>
+        <v>91403</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>523854</v>
+        <v>523487</v>
       </c>
       <c r="R36" t="n">
-        <v>6845289</v>
+        <v>6845098</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4068,12 +4068,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4376,10 +4376,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>125755626</v>
+        <v>125735128</v>
       </c>
       <c r="B40" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4387,37 +4387,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>523759</v>
+        <v>523627</v>
       </c>
       <c r="R40" t="n">
-        <v>6845238</v>
+        <v>6845420</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4461,12 +4461,12 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -4764,58 +4764,48 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125736061</v>
+        <v>125755636</v>
       </c>
       <c r="B44" t="n">
-        <v>56848</v>
+        <v>78736</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523643</v>
+        <v>523511</v>
       </c>
       <c r="R44" t="n">
-        <v>6845391</v>
+        <v>6845102</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4859,19 +4849,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755636</v>
+        <v>125755627</v>
       </c>
       <c r="B45" t="n">
         <v>78736</v>
@@ -4906,10 +4896,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523511</v>
+        <v>523755</v>
       </c>
       <c r="R45" t="n">
-        <v>6845102</v>
+        <v>6845251</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4968,7 +4958,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755627</v>
+        <v>125755628</v>
       </c>
       <c r="B46" t="n">
         <v>78736</v>
@@ -5003,10 +4993,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523755</v>
+        <v>523728</v>
       </c>
       <c r="R46" t="n">
-        <v>6845251</v>
+        <v>6845279</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5065,48 +5055,58 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125755628</v>
+        <v>125736061</v>
       </c>
       <c r="B47" t="n">
-        <v>78736</v>
+        <v>56848</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523728</v>
+        <v>523643</v>
       </c>
       <c r="R47" t="n">
-        <v>6845279</v>
+        <v>6845391</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5150,60 +5150,69 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>125735337</v>
+        <v>125755647</v>
       </c>
       <c r="B48" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>523593</v>
+        <v>523408</v>
       </c>
       <c r="R48" t="n">
-        <v>6845417</v>
+        <v>6845401</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5247,12 +5256,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5550,57 +5559,48 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>125755647</v>
+        <v>125735337</v>
       </c>
       <c r="B52" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>523408</v>
+        <v>523593</v>
       </c>
       <c r="R52" t="n">
-        <v>6845401</v>
+        <v>6845417</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -5644,22 +5644,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>125755788</v>
+        <v>125755709</v>
       </c>
       <c r="B53" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5667,21 +5667,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5691,10 +5691,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>523460</v>
+        <v>523598</v>
       </c>
       <c r="R53" t="n">
-        <v>6845221</v>
+        <v>6845380</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5753,45 +5753,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>125755598</v>
+        <v>125755761</v>
       </c>
       <c r="B54" t="n">
-        <v>97227</v>
+        <v>57656</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>523351</v>
+        <v>523387</v>
       </c>
       <c r="R54" t="n">
-        <v>6845393</v>
+        <v>6845410</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5850,7 +5855,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>125755630</v>
+        <v>125734739</v>
       </c>
       <c r="B55" t="n">
         <v>78736</v>
@@ -5881,17 +5886,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>523671</v>
+        <v>523608</v>
       </c>
       <c r="R55" t="n">
-        <v>6845353</v>
+        <v>6845309</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -5935,22 +5940,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>125755629</v>
+        <v>125755788</v>
       </c>
       <c r="B56" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5958,21 +5963,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -5982,10 +5987,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>523679</v>
+        <v>523460</v>
       </c>
       <c r="R56" t="n">
-        <v>6845347</v>
+        <v>6845221</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6044,32 +6049,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125755709</v>
+        <v>125755598</v>
       </c>
       <c r="B57" t="n">
-        <v>78977</v>
+        <v>97230</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6079,10 +6084,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>523598</v>
+        <v>523351</v>
       </c>
       <c r="R57" t="n">
-        <v>6845380</v>
+        <v>6845393</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6141,10 +6146,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125755761</v>
+        <v>125755630</v>
       </c>
       <c r="B58" t="n">
-        <v>57656</v>
+        <v>78736</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6152,39 +6157,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>523387</v>
+        <v>523671</v>
       </c>
       <c r="R58" t="n">
-        <v>6845410</v>
+        <v>6845353</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6243,7 +6243,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125734739</v>
+        <v>125755629</v>
       </c>
       <c r="B59" t="n">
         <v>78736</v>
@@ -6274,17 +6274,17 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>523608</v>
+        <v>523679</v>
       </c>
       <c r="R59" t="n">
-        <v>6845309</v>
+        <v>6845347</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6328,12 +6328,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6830,10 +6830,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>125755621</v>
+        <v>125755789</v>
       </c>
       <c r="B65" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6841,21 +6841,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6865,10 +6865,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>523920</v>
+        <v>523480</v>
       </c>
       <c r="R65" t="n">
-        <v>6845217</v>
+        <v>6845112</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>125732736</v>
+        <v>125755702</v>
       </c>
       <c r="B66" t="n">
-        <v>78735</v>
+        <v>78977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6938,37 +6938,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>523551</v>
+        <v>523829</v>
       </c>
       <c r="R66" t="n">
-        <v>6845080</v>
+        <v>6845308</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7012,22 +7012,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>125737510</v>
+        <v>125732736</v>
       </c>
       <c r="B67" t="n">
-        <v>78736</v>
+        <v>78735</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7035,21 +7035,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7059,10 +7059,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>523957</v>
+        <v>523551</v>
       </c>
       <c r="R67" t="n">
-        <v>6845190</v>
+        <v>6845080</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7121,10 +7121,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>125755789</v>
+        <v>125737510</v>
       </c>
       <c r="B68" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7132,37 +7132,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>523480</v>
+        <v>523957</v>
       </c>
       <c r="R68" t="n">
-        <v>6845112</v>
+        <v>6845190</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7206,22 +7206,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125755702</v>
+        <v>125755621</v>
       </c>
       <c r="B69" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7229,21 +7229,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7253,10 +7253,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>523829</v>
+        <v>523920</v>
       </c>
       <c r="R69" t="n">
-        <v>6845308</v>
+        <v>6845217</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,10 +7315,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125755700</v>
+        <v>125755783</v>
       </c>
       <c r="B70" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7326,21 +7326,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7350,10 +7350,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>523859</v>
+        <v>523644</v>
       </c>
       <c r="R70" t="n">
-        <v>6845221</v>
+        <v>6845379</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,10 +7412,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125755783</v>
+        <v>125755700</v>
       </c>
       <c r="B71" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>523644</v>
+        <v>523859</v>
       </c>
       <c r="R71" t="n">
-        <v>6845379</v>
+        <v>6845221</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,54 +7509,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125755654</v>
+        <v>125755697</v>
       </c>
       <c r="B72" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>523428</v>
+        <v>523948</v>
       </c>
       <c r="R72" t="n">
-        <v>6845361</v>
+        <v>6845177</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7615,32 +7606,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125755697</v>
+        <v>125755775</v>
       </c>
       <c r="B73" t="n">
-        <v>78977</v>
+        <v>92532</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7650,10 +7641,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>523948</v>
+        <v>523541</v>
       </c>
       <c r="R73" t="n">
-        <v>6845177</v>
+        <v>6845044</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7712,45 +7703,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125755775</v>
+        <v>125755654</v>
       </c>
       <c r="B74" t="n">
-        <v>92532</v>
+        <v>98352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>523541</v>
+        <v>523428</v>
       </c>
       <c r="R74" t="n">
-        <v>6845044</v>
+        <v>6845361</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7906,10 +7906,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125755624</v>
+        <v>125755781</v>
       </c>
       <c r="B76" t="n">
-        <v>78736</v>
+        <v>78644</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7917,21 +7917,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7941,10 +7941,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>523853</v>
+        <v>523958</v>
       </c>
       <c r="R76" t="n">
-        <v>6845279</v>
+        <v>6845195</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8100,10 +8100,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125755781</v>
+        <v>125755694</v>
       </c>
       <c r="B78" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8111,21 +8111,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8135,10 +8135,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>523958</v>
+        <v>523979</v>
       </c>
       <c r="R78" t="n">
-        <v>6845195</v>
+        <v>6845154</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8197,45 +8197,50 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>125755694</v>
+        <v>125755610</v>
       </c>
       <c r="B79" t="n">
-        <v>78977</v>
+        <v>8447</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>523979</v>
+        <v>523527</v>
       </c>
       <c r="R79" t="n">
-        <v>6845154</v>
+        <v>6845375</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8294,50 +8299,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>125755610</v>
+        <v>125755624</v>
       </c>
       <c r="B80" t="n">
-        <v>8447</v>
+        <v>78736</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>523527</v>
+        <v>523853</v>
       </c>
       <c r="R80" t="n">
-        <v>6845375</v>
+        <v>6845279</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8396,10 +8396,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>125734280</v>
+        <v>125755620</v>
       </c>
       <c r="B81" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8407,37 +8407,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>523482</v>
+        <v>523925</v>
       </c>
       <c r="R81" t="n">
-        <v>6845199</v>
+        <v>6845214</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -8481,12 +8481,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8590,10 +8590,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>125755550</v>
+        <v>125734280</v>
       </c>
       <c r="B83" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8601,37 +8601,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>523604</v>
+        <v>523482</v>
       </c>
       <c r="R83" t="n">
-        <v>6845013</v>
+        <v>6845199</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -8675,12 +8675,12 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
@@ -8784,7 +8784,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>125755547</v>
+        <v>125755550</v>
       </c>
       <c r="B85" t="n">
         <v>79595</v>
@@ -8819,10 +8819,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>523479</v>
+        <v>523604</v>
       </c>
       <c r="R85" t="n">
-        <v>6845112</v>
+        <v>6845013</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8881,10 +8881,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>125755620</v>
+        <v>125755547</v>
       </c>
       <c r="B86" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8892,21 +8892,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8916,10 +8916,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>523925</v>
+        <v>523479</v>
       </c>
       <c r="R86" t="n">
-        <v>6845214</v>
+        <v>6845112</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9269,45 +9269,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>125755635</v>
+        <v>125755651</v>
       </c>
       <c r="B90" t="n">
-        <v>78736</v>
+        <v>98352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>523464</v>
+        <v>523420</v>
       </c>
       <c r="R90" t="n">
-        <v>6845115</v>
+        <v>6845370</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9366,54 +9375,45 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>125755651</v>
+        <v>125755635</v>
       </c>
       <c r="B91" t="n">
-        <v>98349</v>
+        <v>78736</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>523420</v>
+        <v>523464</v>
       </c>
       <c r="R91" t="n">
-        <v>6845370</v>
+        <v>6845115</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9472,10 +9472,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>125755555</v>
+        <v>125755784</v>
       </c>
       <c r="B92" t="n">
-        <v>90280</v>
+        <v>78644</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9483,21 +9483,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1962</v>
+        <v>353</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9507,10 +9507,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>523480</v>
+        <v>523606</v>
       </c>
       <c r="R92" t="n">
-        <v>6845111</v>
+        <v>6845378</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -9569,10 +9569,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>125755601</v>
+        <v>125755555</v>
       </c>
       <c r="B93" t="n">
-        <v>92724</v>
+        <v>90280</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9580,21 +9580,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2079</v>
+        <v>1962</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -9604,10 +9604,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>523463</v>
+        <v>523480</v>
       </c>
       <c r="R93" t="n">
-        <v>6845230</v>
+        <v>6845111</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -9666,10 +9666,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>125755631</v>
+        <v>125755601</v>
       </c>
       <c r="B94" t="n">
-        <v>78736</v>
+        <v>92724</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9677,21 +9677,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>228912</v>
+        <v>2079</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>523636</v>
+        <v>523463</v>
       </c>
       <c r="R94" t="n">
-        <v>6845388</v>
+        <v>6845230</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -9763,7 +9763,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>125755619</v>
+        <v>125755631</v>
       </c>
       <c r="B95" t="n">
         <v>78736</v>
@@ -9798,10 +9798,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>523952</v>
+        <v>523636</v>
       </c>
       <c r="R95" t="n">
-        <v>6845185</v>
+        <v>6845388</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -9860,10 +9860,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>125755784</v>
+        <v>125755619</v>
       </c>
       <c r="B96" t="n">
-        <v>78644</v>
+        <v>78736</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9871,21 +9871,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>353</v>
+        <v>228912</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -9895,10 +9895,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>523606</v>
+        <v>523952</v>
       </c>
       <c r="R96" t="n">
-        <v>6845378</v>
+        <v>6845185</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10262,10 +10262,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>125734818</v>
+        <v>125755780</v>
       </c>
       <c r="B100" t="n">
-        <v>91262</v>
+        <v>78644</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10273,37 +10273,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5442</v>
+        <v>353</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>523643</v>
+        <v>523584</v>
       </c>
       <c r="R100" t="n">
-        <v>6845282</v>
+        <v>6845361</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10347,12 +10347,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -10456,10 +10456,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>125755780</v>
+        <v>125755715</v>
       </c>
       <c r="B102" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -10467,21 +10467,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10491,10 +10491,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>523584</v>
+        <v>523450</v>
       </c>
       <c r="R102" t="n">
-        <v>6845361</v>
+        <v>6845349</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10553,10 +10553,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>125755715</v>
+        <v>125734818</v>
       </c>
       <c r="B103" t="n">
-        <v>78977</v>
+        <v>91262</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -10564,37 +10564,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>523450</v>
+        <v>523643</v>
       </c>
       <c r="R103" t="n">
-        <v>6845349</v>
+        <v>6845282</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -10638,12 +10638,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -11038,45 +11038,49 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>125736051</v>
+        <v>125735595</v>
       </c>
       <c r="B108" t="n">
-        <v>78977</v>
+        <v>98352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>523418</v>
+        <v>523492</v>
       </c>
       <c r="R108" t="n">
-        <v>6845349</v>
+        <v>6845165</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11135,49 +11139,45 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125735595</v>
+        <v>125736051</v>
       </c>
       <c r="B109" t="n">
-        <v>98349</v>
+        <v>78977</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>523492</v>
+        <v>523418</v>
       </c>
       <c r="R109" t="n">
-        <v>6845165</v>
+        <v>6845349</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12012,10 +12012,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>125738012</v>
+        <v>125733520</v>
       </c>
       <c r="B118" t="n">
-        <v>57656</v>
+        <v>78977</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12023,39 +12023,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>523967</v>
+        <v>523552</v>
       </c>
       <c r="R118" t="n">
-        <v>6845175</v>
+        <v>6845072</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12114,7 +12109,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>125733520</v>
+        <v>125733632</v>
       </c>
       <c r="B119" t="n">
         <v>78977</v>
@@ -12149,10 +12144,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>523552</v>
+        <v>523458</v>
       </c>
       <c r="R119" t="n">
-        <v>6845072</v>
+        <v>6845126</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12211,10 +12206,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>125733632</v>
+        <v>125738012</v>
       </c>
       <c r="B120" t="n">
-        <v>78977</v>
+        <v>57656</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -12222,34 +12217,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>523458</v>
+        <v>523967</v>
       </c>
       <c r="R120" t="n">
-        <v>6845126</v>
+        <v>6845175</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12311,7 +12311,7 @@
         <v>125735686</v>
       </c>
       <c r="B121" t="n">
-        <v>98349</v>
+        <v>98352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -12898,10 +12898,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125736623</v>
+        <v>125732643</v>
       </c>
       <c r="B127" t="n">
-        <v>78977</v>
+        <v>79566</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -12909,21 +12909,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -12933,10 +12933,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>523689</v>
+        <v>523617</v>
       </c>
       <c r="R127" t="n">
-        <v>6845339</v>
+        <v>6845031</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -12995,10 +12995,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125732643</v>
+        <v>125736623</v>
       </c>
       <c r="B128" t="n">
-        <v>79566</v>
+        <v>78977</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -13006,21 +13006,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13030,10 +13030,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>523617</v>
+        <v>523689</v>
       </c>
       <c r="R128" t="n">
-        <v>6845031</v>
+        <v>6845339</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>

--- a/artfynd/A 9021-2025 artfynd.xlsx
+++ b/artfynd/A 9021-2025 artfynd.xlsx
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125755632</v>
+        <v>125755708</v>
       </c>
       <c r="B5" t="n">
-        <v>78736</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -977,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>523621</v>
+        <v>523626</v>
       </c>
       <c r="R5" t="n">
-        <v>6845375</v>
+        <v>6845380</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125755708</v>
+        <v>125755716</v>
       </c>
       <c r="B6" t="n">
         <v>78977</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>523626</v>
+        <v>523477</v>
       </c>
       <c r="R6" t="n">
-        <v>6845380</v>
+        <v>6845219</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1160,7 +1160,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125755716</v>
+        <v>125755698</v>
       </c>
       <c r="B7" t="n">
         <v>78977</v>
@@ -1195,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>523477</v>
+        <v>523867</v>
       </c>
       <c r="R7" t="n">
-        <v>6845219</v>
+        <v>6845227</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125755698</v>
+        <v>125755711</v>
       </c>
       <c r="B8" t="n">
         <v>78977</v>
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>523867</v>
+        <v>523443</v>
       </c>
       <c r="R8" t="n">
-        <v>6845227</v>
+        <v>6845363</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,7 +1354,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125755711</v>
+        <v>125734647</v>
       </c>
       <c r="B9" t="n">
         <v>78977</v>
@@ -1385,17 +1385,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>523443</v>
+        <v>523611</v>
       </c>
       <c r="R9" t="n">
-        <v>6845363</v>
+        <v>6845275</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1439,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125734647</v>
+        <v>125755632</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1462,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>523611</v>
+        <v>523621</v>
       </c>
       <c r="R10" t="n">
-        <v>6845275</v>
+        <v>6845375</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1536,22 +1536,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125733598</v>
+        <v>125755786</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1559,37 +1559,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>523483</v>
+        <v>523474</v>
       </c>
       <c r="R11" t="n">
-        <v>6845118</v>
+        <v>6845244</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1633,22 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125755693</v>
+        <v>125755785</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1656,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>523993</v>
+        <v>523467</v>
       </c>
       <c r="R12" t="n">
-        <v>6845158</v>
+        <v>6845333</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125755710</v>
+        <v>125755693</v>
       </c>
       <c r="B13" t="n">
         <v>78977</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>523572</v>
+        <v>523993</v>
       </c>
       <c r="R13" t="n">
-        <v>6845367</v>
+        <v>6845158</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125755786</v>
+        <v>125755710</v>
       </c>
       <c r="B14" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1850,21 +1850,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>523474</v>
+        <v>523572</v>
       </c>
       <c r="R14" t="n">
-        <v>6845244</v>
+        <v>6845367</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125755785</v>
+        <v>125733598</v>
       </c>
       <c r="B15" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1947,37 +1947,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>523467</v>
+        <v>523483</v>
       </c>
       <c r="R15" t="n">
-        <v>6845333</v>
+        <v>6845118</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2021,22 +2021,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125755790</v>
+        <v>125735304</v>
       </c>
       <c r="B16" t="n">
-        <v>78644</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2044,37 +2044,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>523486</v>
+        <v>523580</v>
       </c>
       <c r="R16" t="n">
-        <v>6845100</v>
+        <v>6845417</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2118,22 +2118,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125755593</v>
+        <v>125733851</v>
       </c>
       <c r="B17" t="n">
-        <v>57656</v>
+        <v>91262</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2141,42 +2141,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>523520</v>
+        <v>523470</v>
       </c>
       <c r="R17" t="n">
-        <v>6845094</v>
+        <v>6845106</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2206,11 +2201,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-06-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2225,19 +2215,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125735304</v>
+        <v>125755719</v>
       </c>
       <c r="B18" t="n">
         <v>78977</v>
@@ -2268,17 +2258,17 @@
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>523580</v>
+        <v>523554</v>
       </c>
       <c r="R18" t="n">
-        <v>6845417</v>
+        <v>6845068</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2322,22 +2312,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125733851</v>
+        <v>125755593</v>
       </c>
       <c r="B19" t="n">
-        <v>91262</v>
+        <v>57656</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2345,37 +2335,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>523470</v>
+        <v>523520</v>
       </c>
       <c r="R19" t="n">
-        <v>6845106</v>
+        <v>6845094</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2405,6 +2400,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-06-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack (tall)</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2419,22 +2419,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125755719</v>
+        <v>125755790</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>78644</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2442,21 +2442,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2466,10 +2466,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>523554</v>
+        <v>523486</v>
       </c>
       <c r="R20" t="n">
-        <v>6845068</v>
+        <v>6845100</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3013,10 +3013,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125755695</v>
+        <v>125755625</v>
       </c>
       <c r="B26" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3024,21 +3024,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3048,10 +3048,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>523990</v>
+        <v>523850</v>
       </c>
       <c r="R26" t="n">
-        <v>6845162</v>
+        <v>6845286</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3110,10 +3110,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125755565</v>
+        <v>125755695</v>
       </c>
       <c r="B27" t="n">
-        <v>91262</v>
+        <v>78977</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3121,21 +3121,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>523551</v>
+        <v>523990</v>
       </c>
       <c r="R27" t="n">
-        <v>6845103</v>
+        <v>6845162</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3207,10 +3207,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125755625</v>
+        <v>125755565</v>
       </c>
       <c r="B28" t="n">
-        <v>78736</v>
+        <v>91262</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3218,21 +3218,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3242,10 +3242,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>523850</v>
+        <v>523551</v>
       </c>
       <c r="R28" t="n">
-        <v>6845286</v>
+        <v>6845103</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3401,10 +3401,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125734860</v>
+        <v>125755544</v>
       </c>
       <c r="B30" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3412,37 +3412,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>523673</v>
+        <v>523483</v>
       </c>
       <c r="R30" t="n">
-        <v>6845294</v>
+        <v>6845181</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3486,22 +3486,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125735540</v>
+        <v>125755539</v>
       </c>
       <c r="B31" t="n">
-        <v>78977</v>
+        <v>79595</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3509,37 +3509,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>523479</v>
+        <v>523924</v>
       </c>
       <c r="R31" t="n">
-        <v>6845406</v>
+        <v>6845215</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3583,22 +3583,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125755544</v>
+        <v>125734860</v>
       </c>
       <c r="B32" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3606,37 +3606,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>523483</v>
+        <v>523673</v>
       </c>
       <c r="R32" t="n">
-        <v>6845181</v>
+        <v>6845294</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3680,22 +3680,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125755539</v>
+        <v>125735540</v>
       </c>
       <c r="B33" t="n">
-        <v>79595</v>
+        <v>78977</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3703,37 +3703,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>523924</v>
+        <v>523479</v>
       </c>
       <c r="R33" t="n">
-        <v>6845215</v>
+        <v>6845406</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -3777,12 +3777,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4473,10 +4473,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>125732709</v>
+        <v>125755542</v>
       </c>
       <c r="B41" t="n">
-        <v>78736</v>
+        <v>79595</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4484,37 +4484,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>523548</v>
+        <v>523670</v>
       </c>
       <c r="R41" t="n">
-        <v>6845076</v>
+        <v>6845353</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4558,19 +4558,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125755542</v>
+        <v>125755543</v>
       </c>
       <c r="B42" t="n">
         <v>79595</v>
@@ -4605,10 +4605,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>523670</v>
+        <v>523460</v>
       </c>
       <c r="R42" t="n">
-        <v>6845353</v>
+        <v>6845221</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,48 +4667,58 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125755543</v>
+        <v>125736061</v>
       </c>
       <c r="B43" t="n">
-        <v>79595</v>
+        <v>56848</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>523460</v>
+        <v>523643</v>
       </c>
       <c r="R43" t="n">
-        <v>6845221</v>
+        <v>6845391</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4752,19 +4762,19 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>125755636</v>
+        <v>125732709</v>
       </c>
       <c r="B44" t="n">
         <v>78736</v>
@@ -4795,17 +4805,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>523511</v>
+        <v>523548</v>
       </c>
       <c r="R44" t="n">
-        <v>6845102</v>
+        <v>6845076</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4849,19 +4859,19 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Philipp Weiss</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
+          <t>Anders Heggestad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>125755627</v>
+        <v>125755636</v>
       </c>
       <c r="B45" t="n">
         <v>78736</v>
@@ -4896,10 +4906,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>523755</v>
+        <v>523511</v>
       </c>
       <c r="R45" t="n">
-        <v>6845251</v>
+        <v>6845102</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4958,7 +4968,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>125755628</v>
+        <v>125755627</v>
       </c>
       <c r="B46" t="n">
         <v>78736</v>
@@ -4993,10 +5003,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>523728</v>
+        <v>523755</v>
       </c>
       <c r="R46" t="n">
-        <v>6845279</v>
+        <v>6845251</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5055,58 +5065,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>125736061</v>
+        <v>125755628</v>
       </c>
       <c r="B47" t="n">
-        <v>56848</v>
+        <v>78736</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>523643</v>
+        <v>523728</v>
       </c>
       <c r="R47" t="n">
-        <v>6845391</v>
+        <v>6845279</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5150,12 +5150,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Anders Heggestad</t>
+          <t>Philipp Weiss, Håkan Thenander, Anders Heggestad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5268,32 +5268,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>125734972</v>
+        <v>125735892</v>
       </c>
       <c r="B49" t="n">
-        <v>78736</v>
+        <v>92532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5303,10 +5303,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>523675</v>
+        <v>523608</v>
       </c>
       <c r="R49" t="n">
-        <v>6845339</v>
+        <v>6845376</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5365,45 +5365,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>125735892</v>
+        <v>125736672</v>
       </c>
       <c r="B50" t="n">
-        <v>92532</v>
+        <v>78977</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Mysingsån, Mysingsån, Hls</t>
+          <t>Förarstugan, Förarstugan, Hls</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>523608</v>
+        <v>523827</v>
       </c>
       <c r="R50" t="n">
-        <v>6845376</v>
+        <v>6845310</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5462,10 +5462,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>125736672</v>
+        <v>125735337</v>
       </c>
       <c r="B51" t="n">
-        <v>78977</v>
+        <v>78736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5473,34 +5473,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Förarstugan, Förarstugan, Hls</t>
+          <t>Mysingsån, Mysingsån, Hls</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>523827</v>
+        <v>523593</v>
       </c>
       <c r="R51" t="n">
-        <v>6845310</v>
+        <v>6845417</v>
       </c>
       <c r="S51" t="n">
